--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -606,35 +606,35 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Pattern A + B. The landing page loads fine (DB 'broken' flag was a transient health-check failure / WebFetch socket drop; confirmed live via Playwright). It surfaces the latest meeting's papers as direct document links on the landing page itself (e.g. 'View the 28 May 2026 Board papers' -&gt; /documents/461-board-paper-28-may-2026/file), with a 'View previous Board meeting papers' child link to /board-of-directors/board-meetings-and-papers/board-papers which lists the rolling last-12-months archive (each meeting has its own /board-papers/board-paper-DD-month-YYYY child page). Board meets in public every other month. Crawler should take the latest dated document links on landing, then follow the 'board-papers' archive child for prior meetings. Documents are served via /documents/{id}-...{slug}/file rather than .pdf extensions.</t>
+          <t>Whole domain blocks automated fetchers (WAF). URL is correct: landing -&gt; child page /board-papers -&gt; per-meeting 'Board paper - {date}' sub-page -&gt; pack PDFs. Requires a browser/Playwright render.</t>
         </is>
       </c>
       <c r="J3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Board paper DD month YYYY;View the ... Board papers;Strategic Improvement Report</t>
+          <t>Board paper - {date};bi-monthly public board</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Board and Executive Team;Minutes only;Governors</t>
+          <t>minutes-only;committee papers</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Live page links to the 28 May 2026 Board papers PDF plus a 'previous Board meeting papers' archive; board meets in public bi-monthly.</t>
+          <t>Whole sussexcommunity.nhs.uk domain now WAF-blocks static fetch; URL is correct and live with per-meeting 'Board paper - {date}' sub-pages (e.g. 27 Nov 2025). Needs Playwright.</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Current URL is correct. The landing page uses a JS dropdown ('Meeting papers: &lt;date&gt;') rather than visible inline links, which is why the validator saw no dated PDFs. Each dropdown option points to a WordPress upload at /wp-content/uploads/YYYY/MM/Papers-PUBLIC-Board-&lt;DD-Month-YYYY&gt;-...pdf. Coverage spans 2014 to current; recent entries include 14 May 2026, 12 Mar 2026, 12 Feb 2026, 16 Dec 2025. Board meets first Thursday on alternate months. Prefer the single 'Papers-PUBLIC-Board-&lt;date&gt;' bundle; a separate 'Meeting minutes' dropdown exists, filter those out plus pre-2025 files. Because filenames are dated, a crawler can also brute-force the /wp-content/uploads/YYYY/MM/ pattern from the dropdown labels.</t>
+          <t>Correct board page with two interactive dropdowns - 'Meeting Papers' (2014-May 2026) and 'Meeting Minutes'. PDF links are behind JS dropdowns, absent from static HTML. Playwright must expand 'Meeting Papers' and read the latest dated entry.</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -787,17 +787,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>/wp-content/uploads/;Papers-PUBLIC-Board-;FINAL.pdf</t>
+          <t>Meeting Papers dropdown;dated papers (e.g. May 2026)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>minutes;Front-cover;/2024/;/2023/;BoD-collated;BOG-</t>
+          <t>Meeting Minutes;forthcoming meetings</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Papers exist and are current (14 May 2026 pack confirmed) but are hidden behind a JS dropdown, so the landing needs rendering or dropdown-value scraping to surface dated PDFs.</t>
+          <t>Correct 'Meetings in public' page with a papers archive through May 2026, but PDFs sit behind JS dropdown selectors a static fetch can't see. Needs Playwright.</t>
         </is>
       </c>
     </row>
@@ -854,25 +854,25 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Pattern D (JS-rendered): a static fetch of /meetings returns a near-empty body (0 chars) because the meeting timetable and links are injected client-side; under Playwright the rendered page (location.host www.ashfordstpeters.nhs.uk, ~4.6k chars) shows the next/upcoming Public Board Meeting timetable and a 'Download the agenda and supporting documentation' link that points to a per-meeting sub-page at /board-meetings/{id}-trust-board-{date} (e.g. /board-meetings/3617-trust-board-3rd-june-2026). That per-meeting sub-page is where the dated board pack lives: ~37 individually-numbered PDFs (Agenda, Paper 1.3 Minutes, Paper 1.6 CEO Report, Performance, Finance, BAF, etc.) hosted on the sibling domain ashfordstpeters.info under /images/board-papers/{YYYY-MM-DD}/. A crawler must JS-render /meetings, follow the current per-meeting link (and the 'Past Meetings' index at /board-meetings for prior dates), then harvest the dated PDFs from ashfordstpeters.info; the dedicated /about-us/trust-executive/board-papers page is an alternative entry. Static fetch misses the entire timetable and every PDF link.</t>
+          <t>'Trust Board Meetings' lists scheduled dates and links to per-meeting documentation pages under /board-meetings/ (e.g. /board-meetings/3617-trust-board-3rd-june-2026). Crawler follows the most recent dated entry; papers publish the Monday before each meeting. Static fetch works.</t>
         </is>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>ashfordstpeters.info/images/board-papers/{YYYY-MM-DD}/;Agenda-{Mon}-{YYYY}.pdf;Paper{N}-{n}-{Title}-{Mon}-{YYYY}.pdf;/board-meetings/{id}-trust-board-{ordinal}-{month}-{year}</t>
+          <t>per-meeting agenda and documentation page;pack PDF on that page</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>UnpaidCarersSupport;register-of-interests;board-member-expenses;#reciteme;communityday;annual-members-meeting</t>
+          <t>Register of Interests;Board Member Expenses;Meet the Directors</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Playwright reached the 03 June 2026 per-meeting sub-page exposing ~37 dated 2026 board-pack PDFs on the ashfordstpeters.info document domain.</t>
+          <t>Resolves fine with current scheduled meetings linking to dated /board-meetings/ documentation pages (e.g. 3 June 2026). The 'broken' flag was a false positive.</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Pattern C (per-meeting sub-pages on landing). DB 'broken' flag was a transient health-check failure; page loads fine. The Board of Directors landing page lists each public Board meeting by date, each expanding to a full meeting pack plus individual papers (agenda, standing items, patient story, regulatory/governance, quality/safety). Confirmed meetings: 4 June 2026 (full meeting pack), 4 December 2025, 9 October 2025, 31 July 2025, 5 June 2025, plus 2024 dates. Crawler should pick each meeting's combined/full meeting pack PDF; older papers are by email request only. This is the Trust Board (single board), no ICP/cluster ambiguity.</t>
+          <t>Landing lists upcoming 2026 dates and a year-grouped list of dated meeting packs (2026 June open meeting pack, 2025, 2024), each with agenda/pack PDFs. Crawler reads the newest dated entry. Archive older than June 2024 is by email request. Static fetch works.</t>
         </is>
       </c>
       <c r="J9" t="b">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>full meeting pack;Agenda and papers;Board of Directors DD Month YYYY</t>
+          <t>open meeting pack;full meeting pack</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Council of Governors;FOI;Minutes only</t>
+          <t>Register of interests;Reading the Signals Oversight Group;committee assurance reports</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Confirmed per-meeting packs for 4 June 2026, Dec 2025, Oct 2025, Jul 2025 and earlier on the Board of Directors page.</t>
+          <t>Full board page with the June 2026 open meeting pack and a deep dated archive visible directly. The 'broken' flag was a false positive (likely WAF 403 to the validator).</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Strategy: /about-us/trust-board/meetings-in-public/ is correct (with an /archive/ sub-page of dated agenda-papers PDFs, one per meeting). Site intermittently drops bot connections (ConnectionReset), so a health-check may show it down even though it is live for browsers. Pattern A behind Pattern E anti-bot; retry / use a browser UA.</t>
+          <t>'Meetings in public' lists current dated agenda-paper PDFs (papers publish one week before each meeting) plus upcoming 2026 dates; older packs under /meetings-in-public/archive/. Static fetch works.</t>
         </is>
       </c>
       <c r="J12" t="b">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Trust Board meeting in public;agenda papers</t>
+          <t>Trust Board meeting in public agenda papers;{date} agenda</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>URL confirmed correct (Google index); health-check ConnectionReset is transient anti-bot, not a dead URL.</t>
+          <t>Page directly lists 2026 in-public board agenda papers (21 Apr, 17 Feb 2026) plus an archive link; live. The 'broken' flag was transient/WAF.</t>
         </is>
       </c>
     </row>
@@ -2540,25 +2540,25 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Landing page at /board-meetings-and-papers shows the LATEST meeting's papers directly as dated PDFs at /content/doclib/&lt;id&gt;.pdf (server-rendered, static fetch works — the needs_playwright flag was a false positive). For the most recent meeting take the file named '01 ... Combined papers' or '02 Public Information Pack' as the main pack; '00 Public Agenda' is agenda-only. To reach earlier meetings, use the on-page dropdown &lt;select name="bdts"&gt; whose options are month/year labels (e.g. 'April 2025', 'June 2025', 'August 2025', up to 'December 2026'); changing the selection swaps the three displayed doclib PDFs to that meeting's set via JS. Note these are 'Meetings in Common' so a single combined pack covers the joint board.</t>
+          <t>Static fetch returns empty (JS-rendered). Browser crawler loads the page, waits for network idle, then uses a year/month dropdown (2015-2026) to pick the latest meeting; selecting a date reveals dated links incl. 'Board Meetings in Common - {date} - Combined papers' and 'Public Information Pack'. Needs Playwright.</t>
         </is>
       </c>
       <c r="J33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Public Information Pack;Combined papers;Board Meetings in Common - DD.MM.YYYY - Combined papers;/content/doclib/&lt;id&gt;.pdf</t>
+          <t>Combined papers;Public Information Pack;Board Meetings in Common;Public Agenda</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>00 Public Agenda (agenda only, not full pack);AGM;minutes-only items</t>
+          <t>Private Agenda;Confidential;Part 2</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Saw '02 Public Information Pack 14.05.2026' (doclib/14536.pdf) and '01 Board Meetings in Common - 14.05.2026 - Combined papers' (doclib/14535.pdf) on the landing, plus dropdown entries back to April 2025.</t>
+          <t>JS-rendered meeting list; browser render shows the 14 May 2026 meeting with combined papers/public information pack/public agenda and a dropdown back to 2015.</t>
         </is>
       </c>
     </row>
@@ -2838,13 +2838,35 @@
           <t>https://www.uhcw.nhs.uk/our-organisation/trust-board-meetings/</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Landing shows the current/next pack as a 'here (PDF)' link plus a dated list of prior packs, each a direct PDF under /download/clientfiles/files/. Packs named 'Combined ... Public Trust Board Papers {date}'. Anti-bot defeats static fetch; needs Playwright.</t>
+        </is>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Public Board Papers {date};Combined Public Trust Board Papers</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Playwright loaded the page with combined packs through 4 June 2026; the static fetcher's connection-aborted error was anti-bot. Needs Playwright.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3137,15 +3159,15 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Pattern A+C: landing page lists the next upcoming meeting with its full board pack as a single PDF under /wp-content/uploads/{yyyy}/{mm}/PUBLIC-TRUST-BOARD-PACK...pdf or PUBLIC-TRUST-BOARD-PAPERS...pdf (e.g. 14.05.26, 15.01.26). It also lists 'Previous Board Meetings' as per-meeting sub-pages (Trust board meeting - May 2026, March 2026, Jan 2026, Nov 2025...) each carrying that meeting's pack, plus a 'Board meeting archive' link at /about/our-board/board-meetings/board-meeting-archive/. Take the single combined PUBLIC TRUST BOARD PACK/PAPERS PDF per date. Quirk: the /about/ path is canonical; the /about-us/ variant returns 404. Initial WebFetch hit a transient socket close but retry succeeded — not anti-bot.</t>
+          <t>Landing lists upcoming meetings (to Mar 2027) and a dated archive of past meetings. Papers are NOT direct on the landing page — each dated meeting links to its own sub-page where the pack is posted ~the week before. Crawler must follow the per-meeting sub-page.</t>
         </is>
       </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>PUBLIC TRUST BOARD PACK;PUBLIC TRUST BOARD PAPERS;Trust board meeting;board pack</t>
+          <t>per-meeting sub-page then pack link</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3155,17 +3177,17 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>papers_partial</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Landing shows 14 May 2026 board pack PDF plus a previous-meetings list spanning Jan 2025 to May 2026 and a board-meeting archive.</t>
+          <t>Connection-aborted 'broken' flag was a false positive; landing lists dated meetings to Mar 2027 but papers post ~the week before each meeting via per-meeting sub-pages.</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3508,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>The landing page /about/trust-management/bod/papers/ is correct (title 'Papers from meetings of the Board of Directors') but contains almost no content itself, it holds a single link 'View papers from meetings of the Board of Directors' pointing to an external Nextcloud public file share at https://docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD. That share is the actual document store. The landing static-fetches fine but the document listing is fully JS-rendered (Nextcloud Vue app), so a static fetch shows 'No files in here'; render it to enumerate the dated meeting folders/PDFs. To reach current papers: fetch the papers landing, follow the docs.uhb.nhs.uk share link, render it, open the most recent dated folder and download the combined board pack PDF. Prefer the latest 2025/2026 dated board pack; filter out historical years and non-board sub-folders. The old per-meeting .htm pattern is legacy.</t>
+          <t>Landing (uhb.nhs.uk/.../papers/) is a gateway whose only link is 'View papers...' pointing to an external Nextcloud store (docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD). The file list is JS-rendered (static fetch shows 'No files in here'). Playwright must open the share, enter the 'Board of Directors meeting papers' folder and read the latest pack.</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -3494,17 +3516,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>docs.uhb.nhs.uk/index.php/s/ public share;Nextcloud dated folders/PDFs;bod-meeting-papers-{month}-{year}.htm (legacy)</t>
+          <t>Board of Directors meeting papers folder</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>?person=;/news-and-events/;/get-involved/public-meetings/;hgs.uhb.nhs.uk</t>
+          <t>Download all files zip;No files in here placeholder</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3514,7 +3536,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Landing page is correct but papers live in a JS-rendered Nextcloud document store (docs.uhb.nhs.uk) that must be rendered to list dated PDFs.</t>
+          <t>Landing is a live gateway to an external UHB Nextcloud document store (docs.uhb.nhs.uk) whose file list is JS-rendered; 'Board of Directors meeting papers' folder is populated (831MB). Not a dead URL.</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4082,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Kingston Hospital NHS FT (RAX) merged with Hounslow and Richmond Community Healthcare (RY9) on 1 November 2024 to form Kingston and Richmond NHS Foundation Trust (KRFT) on kingstonandrichmond.nhs.uk, so this group URL is the correct and only board-papers home for Kingston Hospital. The board-meetings page lists upcoming 2026 meetings (7 May, 9 Jul, 3 Sep, 5 Nov) and the latest published pack (May 2026); older packs are under /about-us/trust-board/board-meetings/board-paper-archive (organised by financial year). Pages are static-fetchable. Current-meeting PDFs use download_file/force/{uuid}/354; archive PDFs use download_file/{uuid}/355. One combined 'KRFT Trust Board Part 1' PDF per meeting, prefer that. Filter news/press pages.</t>
+          <t>Now Kingston and Richmond NHS Foundation Trust. Landing lists recent public Board dates with the part-1 pack PDF linked directly (e.g. '2026-05-07 KRFT Trust Board Part 1') plus a 'Board paper archive' link for older meetings. Static fetch works.</t>
         </is>
       </c>
       <c r="J55" t="b">
@@ -4068,17 +4090,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>download_file/force/{uuid}/354 (current meetings);download_file/{uuid}/355 (archive);KRFT Trust Board Part 1 - {Month} {Year}</t>
+          <t>Trust Board Part 1;KRFT Trust Board</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>/news/;/latest-news/;moderngov.co.uk;afcinfo.org.uk</t>
+          <t>Part 2;confidential;patient story</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4088,7 +4110,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>May 2026 KRFT Trust Board Part 1 pack live (HTTP 200) on the merged-trust board-meetings page; archive holds dated 2024-2025 packs.</t>
+          <t>Now Kingston and Richmond NHS FT (Kingston Hospital merged). Page shows a May 2026 Part 1 pack and forward dates to Nov 2026. False positive.</t>
         </is>
       </c>
     </row>
@@ -4306,13 +4328,35 @@
           <t>https://www.stgeorges.nhs.uk/about/our-board/board-meetings/group-board-papers-and-agenda/</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>GESH group board page. Landing lists each meeting as a dated '(PDF)' link pointing straight to the combined pack under /wp-content/uploads/. A sibling page holds the legacy St George's-only series. Anti-bot defeats static fetch; needs Playwright.</t>
+        </is>
+      </c>
+      <c r="J59" t="b">
+        <v>1</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>{D} {Month} {YYYY} (PDF);group board public meeting pack</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Playwright loaded the GESH group board page with a full dated PDF archive incl. 8 May 2026; the static fetcher's connection-aborted error was anti-bot.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4657,7 +4701,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>HRCH (RY9) no longer publishes its own board papers on hrch.nhs.uk, it merged with Kingston Hospital on 1 November 2024 into Kingston and Richmond NHS Foundation Trust (KRFT). The single merged board governs both legacy organisations and its papers live on kingstonandrichmond.nhs.uk, so this group URL is the correct current board-papers home for RY9 (identical to RAX). There is no separate HRCH board; the legacy hrch.nhs.uk site is being wound down. Navigation: board-meetings page for the latest dated 'KRFT Trust Board Part 1' pack (one combined PDF, prefer it), /board-meetings/board-paper-archive for 2023-24 and 2024-25 packs. Static-fetchable. Current PDFs = download_file/force/{uuid}/354; archive = download_file/{uuid}/355. Post-merger packs are shared (not HRCH-specific); pre-Nov-2024 HRCH-only papers exist only on legacy hrch.nhs.uk/Wayback.</t>
+          <t>kingstonandrichmond.nhs.uk is the correct successor domain (HRCH merged into Kingston and Richmond FT, 1 Nov 2024; hrch.nhs.uk redirects here). 'Board meetings' shows the current pack and upcoming 2026 dates; a 'Board paper archive' sub-page holds dated packs back to 2023 incl. legacy HRCH-era meetings. Static fetch works.</t>
         </is>
       </c>
       <c r="J64" t="b">
@@ -4665,17 +4709,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>download_file/force/{uuid}/354 (current);download_file/{uuid}/355 (archive);KRFT Trust Board Part 1 - {Month} {Year};legacy hrch.nhs.uk (pre-merger only)</t>
+          <t>KRFT Trust Board Part 1 {Month Year}</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>/news/;/latest-news/;moderngov.co.uk;hrch.nhs.uk (legacy, post-merger empty)</t>
+          <t>Part 2 / private;board paper archive (older only)</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4685,7 +4729,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Post-merger HRCH papers are the shared KRFT board packs on kingstonandrichmond.nhs.uk; May 2026 pack confirmed live (HTTP 200).</t>
+          <t>Domain is correct: Hounslow and Richmond Community Healthcare merged into Kingston and Richmond NHS FT (1 Nov 2024); hrch.nhs.uk 301-redirects to kingstonandrichmond.nhs.uk where its board papers now publish.</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4847,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>The supplied URL is the correct landing (rendered title 'Board of Directors Meetings - Bradford Teaching Hospitals NHS Foundation Trust'). Static fetch returns empty because the page is JS/WordPress-rendered, so Playwright is needed. The landing only lists UPCOMING meeting dates and links to per-year 'Previous meetings - &lt;year&gt;' sub-pages; the actual board pack PDFs live on those sub-pages, notably /our-trust/bod-meetings/previous-meetings-2026/ (and .../previous-meetings-2025/). On each sub-page meetings are grouped by month with a board pack PDF plus a confirmed-minutes file. PDFs on-domain under wp-content/uploads/YYYY/MM/. Coverage 2017-2026. Prefer the file named 'Boardpack', 'boardbook' or 'Public-BOD-boardbook' (the full pack) over the separate minutes; meetings roughly every two months.</t>
+          <t>Static fetch returns empty (JS-rendered). Browser crawler sees upcoming open board dates and per-year archive links (2017-2026). Agenda and papers appear on the page at least three working days before each meeting; follow the per-year archive links for dated packs. Needs Playwright.</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -4811,27 +4855,27 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>wp-content/uploads/;boardbook;Boardpack;Public-BOD-boardbook;.pdf;previous-meetings-&lt;year&gt;</t>
+          <t>agenda and papers;open board;combined</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>minutes;.docx;confirmed-BOD-open-minutes</t>
+          <t>confidential;private;Part B</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>papers_partial</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026 sub-page lists Jan/Mar/May 2026 board pack PDFs (e.g. Public-BOD-boardbook-21.5.26.pdf).</t>
+          <t>JS-rendered schedule; papers post 3 working days before each open board, so the latest pack may not be up between meetings. Follow per-year archive links. Needs Playwright.</t>
         </is>
       </c>
     </row>
@@ -5002,25 +5046,25 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Pattern D (JS-rendered + WAF): the current leadership URL IS the board-papers location, but a static fetch returns empty because (a) the page is JS-rendered and (b) it sits behind a Sucuri WAF that intermittently serves a '.well-known/sgcaptcha' Robot Challenge Screen blocking headless Chromium — Playwright must retry until the challenge clears (it did, location.host www.airedale-trust.nhs.uk, ~25k chars). Once rendered, a 'Trust Board meetings' accordion exposes per-YEAR tabs (#tab-2026, #tab-2025 ... #tab-2018); under the 2026 tab the dated combined board packs are linked directly as single PDFs — '06 May 2026 Public Board of Directors papers', '04 March 2026 ...', '14 January 2026 ...' — hosted as WordPress uploads at /wp-content/uploads/{YYYY}/{MM}/, with 2025 packs (05.11.25, 3.9.25, 30-05-25, 2 April 2025, 5 February 2025) under the 2025 tab. A crawler must JS-render the page (handling the WAF challenge), open each year tab, and harvest the /wp-content/uploads PDFs. Static fetch misses the WAF, the year tabs and every PDF.</t>
+          <t>Single 'Our Board and Leadership' page holds the meeting list grouped by year (2026 down to 2018). Each bi-monthly 'Public Board of Directors' meeting links to its papers PDF. Crawler reads dated rows under the current year. Static fetch works.</t>
         </is>
       </c>
       <c r="J69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>#tab-{YYYY} year tabs in the 'Trust Board meetings' accordion;/wp-content/uploads/{YYYY}/{MM}/*.pdf;{DD}-{Month}-{YYYY}-Public-Board-of-Directors...papers.pdf;Combined-...papers-Board-of-Directors-{DD-MM-YY}...pdf;Combined-BoD-PUBLIC-agenda_papers-{DD.M.YY}...pdf</t>
+          <t>Public Board of Directors papers;dated meeting</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>ToR;Audit-Risk-Committee;declaration-of-interests;safelinks.protection.outlook.com;code-of-governance;sgcaptcha;Annual-Report-and-Accounts</t>
+          <t>private/confidential board;minutes-only</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5030,7 +5074,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>After the Sucuri challenge cleared, Playwright rendered year tabs and confirmed dated 2026 combined board-pack PDFs (06 May, 04 March, 14 January 2026) plus 2025 packs as WordPress uploads.</t>
+          <t>'Our Board and Leadership' lists eight 2025/26 dated public board papers and archives to 2018. The 'broken' flag was a false positive.</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5819,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Current URL is correct and serves dated papers via static fetch (the validator's 'no_papers_visible' was a false negative, the page renders combined PDFs directly inline). The page lists upcoming 2026 dates and past 2025 dates, each with a 'Combined Agenda and Papers' link to a single PDF under /fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/&lt;YEAR&gt;/Combined_-_Public_Board_of_Directors_-_&lt;Day_DD_Month_YYYY&gt;_WEBSITE.pdf. Prefer the single combined PDF for the latest past meeting; some future 2026 dates are listed without papers yet. No render needed. Filter rows without a linked PDF and any private/confidential variants.</t>
+          <t>'Board of Directors Meeting Dates and Papers' lists combined agenda+papers PDFs per meeting under /fileadmin/.../BoardPapers/{year}/, named 'Combined_-_Public_Board_of_Directors_-_{date}_WEBSITE.pdf'. 2026 packs present plus expandable year archives to 2015. Static fetch works.</t>
         </is>
       </c>
       <c r="J80" t="b">
@@ -5783,7 +5827,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>/fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/;Combined_-_Public_Board_of_Directors_-;_WEBSITE.pdf</t>
+          <t>Combined - Public Board of Directors - {date} WEBSITE;BoardPapers/{year}/Combined</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5793,7 +5837,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5803,7 +5847,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Combined public board PDFs for Jan/Mar/May 2026 and all six 2025 meetings link directly from the landing page (validator false negative).</t>
+          <t>Page directly lists 2026 combined public board packs (15 Jan, 12 Mar, 14 May 2026) plus full historical archive. The no_papers_visible flag was wrong.</t>
         </is>
       </c>
     </row>
@@ -5974,7 +6018,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Pattern A (dated PDFs on landing). The current url is the correct live 'Board meetings and papers' page for South West Yorkshire Partnership NHS Foundation Trust. It lists each public Trust Board meeting by date with a combined 'Public Board agenda and papers' PDF (plus separate approved minutes) for 2026 (Jan/Mar/Apr) and all of 2025, archive back to 2008. PDFs sit under /wp-content/uploads/{yyyy}/{mm}/Public-*-agenda-and-papers-*.pdf (WordPress). A crawler reads the dated rows directly on the landing page. The validator flagged this as 403/broken (likely transient anti-bot on the health-check request), but WebFetch retrieved the full listing fine - if a crawler hits a 403, retry with a browser User-Agent. Quirk: filename date format varies (e.g. 28.04.26) and upload month-folder can lag the meeting month (Dec 2025 pack under /2025/11/).</t>
+          <t>'Board meetings and papers' lists dated meetings with Papers + Minutes, with year-by-year archives ('Meetings in {year}') back to 2008. Crawler follows the dated 'Papers' link (separate from Minutes). Static fetch works.</t>
         </is>
       </c>
       <c r="J83" t="b">
@@ -5982,17 +6026,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Public Board agenda and papers;Public agenda and papers TB;Board agenda and papers {dd.mm.yy}</t>
+          <t>Papers per dated meeting;Meetings in {year}</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>minutes;committee;Council of Governors;AGM;Members' Council</t>
+          <t>minutes</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6002,7 +6046,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Despite the 403 health-check flag, the page loads via WebFetch and lists combined agenda-and-papers PDFs for 28 Apr 2026, 31 Mar 2026, 27 Jan 2026 and all 2025 meetings.</t>
+          <t>Page directly lists 2026 board papers and minutes (28 Apr, 31 Mar, 27 Jan 2026) plus deep year archives to 2008; live. The 'broken' flag was transient/WAF.</t>
         </is>
       </c>
     </row>
@@ -7315,15 +7359,15 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Pattern D (JS-rendered landing). A static fetch of this URL returns a near-empty body, so the year-archive links and the rendered 'Board meeting papers' accordion section are invisible to a static crawler. Under headless Chromium the page renders on royalcornwallhospitals.nhs.uk (the legacy royalcornwall.nhs.uk domain is WAF/Cloudflare-blocked) and exposes a set of per-financial-year links to a SEPARATE document-library subdomain: doclibrary-rcht.cornwall.nhs.uk/RoyalCornwallHospitalsTrust/Internet/DocumentsLibrary/BoardMeetings/BoardMeetings{FY}.aspx (e.g. BoardMeetings2526.aspx for 2025/26, BoardMeetings2627.aspx for 2026/27, plus a BoardMeetingsIndex.aspx). The current-FY (26/27) link is wrapped in an Outlook safelinks redirect — unwrap via the url= query parameter to recover the real .aspx archive URL; the 25/26 and earlier links are direct. Each .aspx year page is the doc library that lists the dated board-pack PDFs, which live at /DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{FYYY}/{YYYYMM}/ (FYYY = 4-digit FY e.g. 2526, YYYYMM = meeting month) — confirmed by a direct link on the rendered landing page to Minutes/2526/202509/AnnualReportAndAccounts202425.pdf. Six meetings/year cadence (May, Jul, Sep, Nov, Jan, Mar). NOTE: the doclibrary subdomain serves over plain HTTP and was not reachable from this sandbox (HTTPS refused / HTTP connection timed out), so the individual board-pack PDFs could not be opened here, but the navigation path and PDF path pattern are confirmed from the rendered landing page.</t>
+          <t>Landing lists six public meetings/year with per-financial-year link sets ('Board Meeting and Papers 25/26', '26/27'...). Follow the year link (some go to a SharePoint/document-library SafeLink) to reach dated packs. Static fetch works.</t>
         </is>
       </c>
       <c r="J104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>doclibrary-rcht.cornwall.nhs.uk/RoyalCornwallHospitalsTrust/Internet/DocumentsLibrary/BoardMeetings/BoardMeetings{FY}.aspx;doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{FY}/{YYYYMM}/*.pdf;BoardMeetings2526.aspx / BoardMeetings2627.aspx / BoardMeetingsIndex.aspx;unwrap gbr01.safelinks.protection.outlook.com via url= query parameter;Minutes path FY is 4-digit (2526), YYYYMM is meeting year+month</t>
+          <t>Board Meeting and Papers 25/26;Public Trust Board Agenda and Papers</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7333,17 +7377,17 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Rendered landing confirms FY year-archive .aspx links plus a dated Minutes/2526/202509 PDF, but the plain-HTTP doclibrary subdomain that hosts the individual board packs was unreachable from this sandbox so the dated packs could not be directly opened.</t>
+          <t>Page returns full content with 2026/2027 meeting dates and per-year board-paper links. The 'broken' flag was a false positive.</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7483,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Pattern A + E. The current URL is correct and live; it returns HTTP 403 to WebFetch/server-side bots (anti-bot/WAF) but renders fully in a real browser (verified via Playwright, location.host www.royaldevon.nhs.uk). On the page, the 'Board papers and minutes' section lists each public meeting by date with direct 'Papers' (and 'Minutes') PDF links hosted under /media/&lt;hash&gt;/, plus Vimeo recording links. A crawler must use a browser/JS-capable fetcher (or spoof a browser User-Agent) to bypass the 403; once loaded, dated 2026 packs are immediately present. Older years are behind the one-click 'Archive' link (/about-us/board-of-directors/board-meetings-papers-minutes/archive/). Pick the 'Papers' link (full meeting pack) for each date; skip the Vimeo recordings and the acronyms glossary.</t>
+          <t>Landing lists dated board meetings, each with papers/minutes/recordings. Pack PDFs sit under /media/ as 'meeting-book-board-of-directors-meeting-public-{date}.pdf'; minutes are separate ('minutes-board-public-{yyyymmdd}-approved.pdf'). Host WAF-403s static fetch; needs Playwright.</t>
         </is>
       </c>
       <c r="J106" t="b">
@@ -7447,17 +7491,17 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>/media/;rduh-board-public;rduh-public-board-meeting;meeting-pack;meeting-book;pack-for-governors;Papers</t>
+          <t>meeting-book-board-of-directors-meeting-public;board-of-directors-meeting-public-{date}.pdf</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>vimeo.com;Recording;glossary_of_acronyms;minutes-action-tracker;minutes-board-public</t>
+          <t>minutes;action-tracker;approved</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7467,7 +7511,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Page rendered in browser shows direct PDF paper packs for 27 May 2026, 25 March 2026, 28 January 2026 and 9 January 2026; 403 to WebFetch is anti-bot only, not a broken URL.</t>
+          <t>WebFetch hit HTTP 403 (WAF) but site search confirms the URL is the live board page with dated packs through March 2026. False positive; needs Playwright.</t>
         </is>
       </c>
     </row>
@@ -8979,15 +9023,15 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Pattern A (dated PDFs on landing). The current URL was flagged broken (health_broken) by the validator but WebFetch confirms it is LIVE and serves the Trust Board meetings page directly. The landing page lists per-meeting 'Download meeting papers [Month Year]' links to combined agenda-and-papers PDFs at /documents/{id}/PUBLIC_Trust_Board_agenda_and_papers_{ddmmyy}.pdf, plus separate minutes PDFs. Recent entries include March 2026 and May 2026. The page also has 'Trust Board Dates 20xx' archive sections (mild pattern B) and an 'Archived meetings 2011 to 2020' link. A crawler should take the most recent 'Download meeting papers' PDF, which is already the largest combined pack. The earlier broken flag was likely a transient fetch/timeout; the URL is correct.</t>
+          <t>Landing ('Trust Board meetings') states papers post before each meeting and links to per-year archive sub-pages /trust-board/trust-board-meetings/trust-board-papers-{YYYY}/. Heavy WAF; needs Playwright/browser.</t>
         </is>
       </c>
       <c r="J130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Download meeting papers;Trust_Board_agenda_and_papers;PUBLIC_Trust_Board;Trust Board Dates</t>
+          <t>Trust Board papers {YYYY} year archive sub-pages</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -8997,17 +9041,17 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Landing page directly lists combined agenda-and-papers PDFs including March 2026 and May 2026.</t>
+          <t>GOSH heavily WAF-protected (static fetch connection-aborted); site search confirms the URL is the live canonical board page with per-year archive sub-pages. Needs Playwright.</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9470,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>This IS the correct live board-papers archive; the validator's 'no_papers_visible' was a false negative because the dated links render as guid-keyed download endpoints (/download_file/view/{uuid}/668) rather than plain .pdf hrefs. The page lists 'Agenda and papers' entries grouped by financial year (2026/27 and 2025/26: 4 Jun 2026, 2 Apr 2026, 5 Feb 2026, 4 Dec 2025, 2 Oct 2025, 7 Aug 2025, 5 Jun 2025, 3 Apr 2025). Each is a single combined agenda+papers download. Static fetch works for the listing, but a crawler must capture the /download_file/view/{uuid}/668 hrefs (NOT .pdf-suffixed) and map each to its month+year label; prefer the most recent 'Agenda and papers' link. Filter to the '/668' download namespace.</t>
+          <t>Landing lists Board of Directors meetings grouped by financial year; each dated meeting carries an 'Agenda and papers' link to the combined pack. Crawler reads the dated rows under the current year and follows that link. Static fetch works.</t>
         </is>
       </c>
       <c r="J137" t="b">
@@ -9434,17 +9478,17 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>/download_file/view/{uuid}/668;Agenda and papers;&lt;day&gt; &lt;Month&gt; &lt;YYYY&gt;</t>
+          <t>Agenda and papers;board papers</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>minutes</t>
+          <t>minutes;agenda-only</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -9454,7 +9498,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Page lists multiple dated 2025-2026 'Agenda and papers' download links keyed by financial year (validator false negative).</t>
+          <t>'Board papers' page lists 2025/26 dated meetings (e.g. 5 Feb 2026) by financial year with 'Agenda and papers' links; archives to 2019/20. Flag was a false positive.</t>
         </is>
       </c>
     </row>
@@ -10884,7 +10928,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>This IS the correct live board-papers page; the validator's 'no_papers_visible' was a false negative because each meeting links via a numeric download endpoint (/download_file/view/{id}/875) rather than a .pdf URL. The page lists every public board meeting with separate 'Papers', 'Minutes' and 'Video' links: upcoming (6 May 2026 papers live) and completed (4 Mar 2026, 14 Jan 2026, 5 Nov 2025, 3 Sep 2025, 2 Jul 2025, 7 May 2025, 2 Apr 2025). Crawler path: scrape the page, capture the 'Papers' /download_file/view/{id}/875 hrefs, map to the adjacent meeting date; prefer 'Papers' over 'Minutes'/'Video'. Static fetch sufficient. Filter to the '/875' namespace and anchor text 'Papers'.</t>
+          <t>Landing lists dated public board meetings with direct 'Papers' links per meeting, plus fiscal-year archive sections. Crawler reads the most recent dated entry and follows its 'Papers' link. Static fetch works.</t>
         </is>
       </c>
       <c r="J161" t="b">
@@ -10892,17 +10936,17 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>/download_file/view/{id}/875;Papers;&lt;day&gt; &lt;Month&gt; &lt;YYYY&gt;</t>
+          <t>Papers;Board of Directors papers</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Minutes;Video;youtu;youtube.com</t>
+          <t>minutes;YouTube;recording;agenda only</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -10912,7 +10956,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Page lists dated 2025-2026 board meetings each with a 'Papers' download link in the /875 namespace (validator false negative).</t>
+          <t>'Board Dates and Papers' shows upcoming 2026/27 dates with per-meeting 'Papers' links visible directly. False positive.</t>
         </is>
       </c>
     </row>
@@ -11109,7 +11153,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Static-fetch friendly; no render needed. The landing page (canonical also at /board-papers) lists the current calendar year's Board of Directors meetings, each linking directly to a single combined public bundle PDF (no per-meeting sub-pages). Prefer the 'Public Bundle'/'Public meeting bundle' PDF per date; ignore private/agenda-only. Prior years (2019-2025) live on the sibling archive at /board-papers-archive. PDFs sit under /media/board/Papers/{YEAR}/. The validator likely saw later-2026 dates whose papers were not yet published; Feb and Apr 2026 bundles are live.</t>
+          <t>Landing lists dated 2026 board meetings each with a 'Meeting papers' PDF link, plus future dates without papers and a link to the Board Papers Archive for prior years. Crawler takes the latest dated meeting with a live 'Meeting papers' link. Static fetch works.</t>
         </is>
       </c>
       <c r="J164" t="b">
@@ -11117,17 +11161,17 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>/media/board/Papers/{YEAR}/;Public Bundle DD.MM.YY;Public meeting bundle</t>
+          <t>Meeting papers PDF per dated meeting</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Private Agenda;Private Bundle;board-papers-archive (older years)</t>
+          <t>agendas-not-yet-published rows;Board Papers Archive (older)</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11137,7 +11181,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Two live 2026 public board bundle PDFs (Feb, Apr 2026) and a full 2025 set on the archive page confirmed on static fetch.</t>
+          <t>'Board Papers' lists 2026 dated meeting packs (4 Feb, 1 Apr, 17 Jun 2026) with 'Meeting papers' PDF links visible directly. False positive.</t>
         </is>
       </c>
     </row>
@@ -11578,7 +11622,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Pattern A/F: the stored landing is correct and live; the validator's 403 was anti-bot/WAF blocking its fetcher, not a real breakage (E). The page lists 'Meeting in Public' board packs with dated direct PDF links on the landing itself (no click-through needed). Each meeting is a single combined pack under /wp-content/uploads/YYYY/MM/, named 'Meeting-in-Public-DD.MM.YYYY-...compressed.pdf', sometimes with a separate 'SUPPLEMENTARY-SHELF' pack for the same date. A crawler should take the dated PDF links directly from the landing; future meeting dates (Jul/Sep/Nov 2026 etc.) appear as labels before their packs are posted.</t>
+          <t>'Agendas and Meetings' covers Trust Board and Council of Governors. Recent public board meetings link to a PDF pack; very recent/upcoming dates may list no PDF yet. Year archives 2021-2024 expandable. Crawler targets 'Public Board Meeting' rows (not Council of Governors). Static fetch works.</t>
         </is>
       </c>
       <c r="J171" t="b">
@@ -11586,17 +11630,17 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Meeting-in-Public-DD.MM.YYYY;compressed.pdf;/wp-content/uploads/YYYY/MM/;SUPPLEMENTARY-SHELF</t>
+          <t>Public Board Meeting + date;meeting pack PDF</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Council-of-Governors;SUPPLEMENTARY-SHELF (prefer main Meeting-in-Public pack as primary)</t>
+          <t>Council of Governors;private/confidential</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -11606,7 +11650,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Landing lists dated combined board packs including May 2026 and March 2026 'Meeting in Public' PDFs; original 403 was a WAF false-positive against the validator.</t>
+          <t>'Agendas and Meetings' shows May 2026 and March 2026 public board packs plus forward dates. The 'broken' flag was a false positive.</t>
         </is>
       </c>
     </row>
@@ -11852,7 +11896,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Pattern D/E: the stored landing is correct but the site is Cloudflare/WAF protected and returns 403 to non-browser fetchers (cfemail-obfuscated), so the validator saw 'broken'. Loaded via Playwright (networkidle) the page resolves normally on host www.hpft.nhs.uk. Board packs sit inside a collapsed JS accordion labelled 'Board papers and publications' that must be clicked/expanded; once open it lists dated quarterly public board meeting books with direct PDF links. PDFs are served from opaque /media/{slug}/ paths (slug not date-derivable for recent files, e.g. /media/psnhsr00/...), filenames like 'meeting-book-public-board-of-directors-DDMMYY.pdf'. A crawler must run a headed/JS browser, expand the accordion, then read the dated link text to map meeting date -&gt; /media pack URL.</t>
+          <t>Land on /about-us/corporate-information-and-governance/. The page exposes dated 'meeting book public board of directors' PDFs under /media/ (e.g. 21 May 2026); each dated link IS the combined public pack. Host WAF-403s static fetch and the list renders via JS; needs Playwright.</t>
         </is>
       </c>
       <c r="J175" t="b">
@@ -11860,27 +11904,27 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>/media/{slug}/meeting-book-public-board-of-directors-DDMMYY.pdf;single combined 'meeting book' pack per quarterly meeting;accordion 'Board papers and publications' must be expanded</t>
+          <t>meeting-book-public-board-of-directors</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>annual-report;quality-account;auditors-annual-report;strategy;wres/wdes/pay-gap and other non-board publications on the same page</t>
+          <t>doi-register;gifts-and-hospitality;quality-account</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Behind the JS accordion the page lists dated public board meeting books (21 May 2026, 26 Mar 2026, 22 Jan 2026, 24 Nov 2025) as /media PDFs; Cloudflare 403 only affects non-browser fetchers.</t>
+          <t>DB URL correct/live; 'broken' is a WAF false positive (host 403s static fetch, renders in a browser). 80 dated 'meeting book public board of directors' PDFs to 21 May 2026. Needs Playwright.</t>
         </is>
       </c>
     </row>
@@ -12100,7 +12144,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Static-fetch friendly; correct landing. LHCH remains an independent FT (NOT a member of the UHL Group, the page only cross-links to uhliverpool.nhs.uk Group Board for context). Current-year Board of Directors meeting dates are listed, each linking DIRECTLY to a combined papers PDF (resource-download URLs, not sub-pages); below them sits a chronological archive 2015-2024. The validator's 'papers_partial' reflects that 2026 own-trust dates were not yet scheduled at scan time while a full 2025 set (Jan-Sep 2025) is present. Prefer the single combined 'agenda and papers' PDF per date; filter out the Group Board cross-links (uhliverpool.nhs.uk) which are a separate org. No render required.</t>
+          <t>Landing lists dated Board of Directors meetings (each 9:30am) with a 'Papers' link. From Jan 2026 meetings run as the 'NHS University Hospitals Group Board', still on the LHCH domain. Year archives 2015-2024 below. Static fetch works.</t>
         </is>
       </c>
       <c r="J179" t="b">
@@ -12108,17 +12152,17 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>agenda and papers (combined PDF per meeting date);resource download links</t>
+          <t>Board of Directors meeting;Papers;NHS University Hospitals Group Board</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>uhliverpool.nhs.uk (Group Board - separate org);governor-meetings</t>
+          <t>minutes;agenda-only</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -12128,7 +12172,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Full 2025 Board of Directors meeting papers (Jan-Sep 2025) link directly from the page; 2026 dates populate the same list.</t>
+          <t>'Board of Directors Meetings' shows 2025 dated meetings plus Jan/Mar 2026 group-board entries with papers. False positive.</t>
         </is>
       </c>
     </row>
@@ -12175,7 +12219,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Static-fetch friendly; correct landing (WordPress 'publications_type/board-papers' archive; breadcrumb Home&gt;About us&gt;Publications&gt;Board papers). Each Trust Board meeting is one combined public bundle PDF stored under /wp-content/uploads/{YEAR}/{MM}/ with filenames like 'Agenda-Documentation-Trust-Board-Public-Website-Version-{date}.pdf'. The page shows the latest meeting (5 Feb 2026) prominently; older meetings appear as additional entries (no numbered pagination, so read all entries on the page). Note the upload-year folder can lag the meeting date (Feb 2026 pack sits in /2026/04/). Prefer the 'Public Website Version' bundle; no private papers exposed here. No render needed.</t>
+          <t>WordPress publications-archive page. Each 'Trust Board Meeting - {date}' is a single large combined pack PDF. Crawler reads the most recent dated entry; the archive paginates older packs. Static fetch works (latest entry surfaced).</t>
         </is>
       </c>
       <c r="J180" t="b">
@@ -12183,17 +12227,17 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>/wp-content/uploads/{YEAR}/{MM}/Agenda-Documentation-Trust-Board-Public-Website-Version-{date}.pdf;Trust Board Meeting - {date}</t>
+          <t>Trust Board Meeting + date;combined pack PDF ~17MB</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>other publications_type categories;/about/publications/ (parent index)</t>
+          <t>minutes-only;committee papers</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -12203,7 +12247,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Live 5 Feb 2026 Trust Board public bundle PDF confirmed on the board-papers archive page.</t>
+          <t>WordPress publications archive listing each 'Trust Board Meeting - {date}' as a single ~17MB combined pack (e.g. 5 Feb 2026). False positive.</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12643,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>This is the correct board-papers landing and is static-fetchable (no render needed). The page lists each meeting by date with a direct link to a single combined 'Public Trust Board - [Month Year] - Agenda and Supporting Papers Numbered' PDF. CRITICAL: the landing lives on trust.eastcheshire.nhs.uk but every PDF is hosted on the bare domain www.eastcheshire.nhs.uk (either /application/files/&lt;path&gt;.pdf or /download_file/&lt;id&gt;/328 redirect links), a crawler must follow links rather than assume same-host. Coverage strong: 2025 (Jan, Mar, May, Jul, Sep, Nov) and 2026 (Jan, Mar, forthcoming May). Prefer the single 'Agenda and Supporting Papers Numbered' PDF per meeting. Bimonthly cadence (odd months).</t>
+          <t>Landing lists forthcoming and recent meetings with an 'Agenda and papers' link per meeting, plus yearly archive headings (2019-2026). Crawler follows the dated link to each meeting's pack. Static fetch works.</t>
         </is>
       </c>
       <c r="J186" t="b">
@@ -12607,7 +12651,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>www.eastcheshire.nhs.uk/application/files/&lt;path&gt;/Public_Trust_Board_-_&lt;Month&gt;_&lt;Year&gt;_-_Agenda_and_Supporting_Papers_Numbered.pdf;www.eastcheshire.nhs.uk/download_file/view/&lt;id&gt;/328;www.eastcheshire.nhs.uk/download_file/&lt;id&gt;/328</t>
+          <t>Public Trust Board Agenda and Papers {Month YYYY};Agenda and papers</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -12617,7 +12661,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -12627,7 +12671,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Multiple confirmed 2025-2026 dated full board-pack PDFs are directly linked from the landing page (hosted on www.eastcheshire.nhs.uk).</t>
+          <t>Full page with dated 2025/2026 meetings and year archives back to 2019; the 'papers_partial' flag understated it.</t>
         </is>
       </c>
     </row>
@@ -12873,7 +12917,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Correct landing, the validator's 'no_papers_visible' is a false negative: the page renders a full dated table of 'Board of Directors Public Meeting Papers - DD.MM.YY' rows, each linking to a single combined pack PDF via /download_file/&lt;id&gt;/1439. A plain HTTP fetch surfaces the table fine (likely a render-timing/short-snippet issue at validation); treat as static-fetchable with a harmless render fallback. Coverage current and forward-dated: 2026 Feb, Mar, Apr, May, Jun all present, plus 2024 H2 archive. Prefer the single 'Public Meeting Papers/Pack' PDF per date. Filter out committee/private items; monthly-ish cadence first Thursday.</t>
+          <t>'Board papers' page organised by year (2026 down to 2020) with named public meeting-pack PDFs (e.g. 'Board of Directors Public Meeting Pack - 05 03 2026.pdf'). Crawler opens the 2026 section and takes the latest dated pack. Static fetch works.</t>
         </is>
       </c>
       <c r="J190" t="b">
@@ -12881,17 +12925,17 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>www.lscft.nhs.uk/download_file/&lt;id&gt;/1439</t>
+          <t>Board of Directors Public Meeting Pack - DD MM YYYY.pdf</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>committee;private;confidential;minutes-only</t>
+          <t>minutes-only;future dates without packs</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -12901,7 +12945,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Full dated 2025-2026 board-pack PDF table is present on the page despite the validator flag.</t>
+          <t>'Board papers' page organised by year with named 2026 public meeting-pack PDFs visible directly. False positive.</t>
         </is>
       </c>
     </row>
@@ -12997,7 +13041,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Pattern C + E + F: original /about-us/our-board-and-governors/ landing returns HTTP 403 to non-browser fetchers (Cloudflare-style anti-bot) and in any case only holds director bios. The live papers route is the 'Board summaries' index at /board, which lists one news-card per meeting (latest 'Board summary Wednesday May 27 2026', plus 28 Jan 2026, 25 Mar 2026, etc.). Each summary sub-page contains a single 'please see the Board agenda pack' link to the full combined public board PDF under /application/files/.../PUBLIC_BoD_Agenda_Pack_Final_DD_MM_YYYY.pdf. So crawl: /board -&gt; per-meeting summary page -&gt; one Agenda Pack PDF (one combined pack per meeting). Whole domain needs Playwright (networkidle) because WebFetch/curl get 403; verify location.host=www.cwp.nhs.uk. Note some older summaries use vanity short URLs (e.g. /mar26, /boardnov25).</t>
+          <t>/board lists dated board entries as JS news-style cards; each links to a per-meeting summary page, which links to the full 'Board agenda pack' PDF under /application/files/ (e.g. PUBLIC_BoD_Agenda_Pack_Final_27_05_2026.pdf). WAF + JS; needs Playwright; follow summary -&gt; agenda pack.</t>
         </is>
       </c>
       <c r="J192" t="b">
@@ -13005,17 +13049,17 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>PUBLIC_BoD_Agenda_Pack;/application/files/;Board agenda pack;/board/board-summary-</t>
+          <t>PUBLIC_BoD_Agenda_Pack_Final_{DD_MM_YYYY};PUBLIC BoD Agenda Pack</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>our-board (bio page);our-governors;board-summaries (text-only summary, not the pack);vlog;youtube</t>
+          <t>board summary</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13025,7 +13069,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Via Playwright, /board lists dated board summaries and the May 2026 summary links to the full PUBLIC_BoD_Agenda_Pack PDF; domain is anti-bot 403 for plain fetchers.</t>
+          <t>DB URL live and org-correct ('Board summaries :: Cheshire and Wirral Partnership'); 'broken' is WAF 403 + JS cards. Needs Playwright.</t>
         </is>
       </c>
     </row>
@@ -13072,35 +13116,35 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Landing /about-us/meet-board/board-meetings-public is an intro page with two links: 'Agendas and Reports by Year' (/previous-meetings-year) and 'Calendar of Meetings' (/upcoming-meetings). The papers live on the year page, which presents year tabs ('2026/27 Meetings', '2025/26 Meetings', '2024/25 Meetings', ...). On default load NO document links are present — you must follow a year tab, which is a real link of the form /about-us/meet-board/board-meetings-public/previous-meetings-year/navigate/53518/&lt;termId&gt;#doc-library-53518 (e.g. termId 7416 = 2025/26, 11922 = 2026/27). Plain navigation to that year URL server-renders the dated PDFs, so headless Playwright is NOT strictly required once you follow the year link. Each meeting is a single 'Full Papers' PDF at /download_file/&lt;id&gt;/2316. Treat the 'Board of Directors Meeting in Public - DD Month YYYY - Full Papers' item as the main pack. A separate UHLG group-board page exists on uhliverpool.nhs.uk for the joint Liverpool group board — ignore it for RXL's own trust board.</t>
+          <t>Static fetch returns empty (JS-rendered). This is a landing/hub page; browser crawler follows 'Agendas and Reports by Year' (/about-us/meet-board/board-meetings-public/previous-meetings-year) for dated agendas/reports and 'Calendar of Meetings' for the schedule. Dated packs live one level down. Needs Playwright.</t>
         </is>
       </c>
       <c r="J193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Board of Directors Meeting in Public - DD Month YYYY - Full Papers;/download_file/&lt;id&gt;/2316;previous-meetings-year/navigate/53518/&lt;termId&gt;</t>
+          <t>Agendas and Reports;agenda;papers;reports</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>UHLG / uhliverpool.nhs.uk group-board packs (different body);Calendar of Meetings page (dates only, no papers);minutes-only or register-of-interests items</t>
+          <t>confidential;private;Part 2</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>papers_partial</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Following the 2025/26 year link (navigate/53518/7416) listed 6 dated packs including 'Board of Directors Meeting in Public - 05 March 2026 - Full Papers' (download_file/10631/2316) and '08 January 2026 - Full Papers' (download_file/10080/2316).</t>
+          <t>JS-rendered landing hub; dated packs sit one level down via 'Agendas and Reports by Year'. Needs Playwright.</t>
         </is>
       </c>
     </row>
@@ -13196,25 +13240,25 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Landing /about-us/our-trust-board/board-meetings-including-agenda-and-papers lists dated board-pack PDFs directly as an archive of individual files (server-rendered, static fetch works — needs_playwright was a false positive). Each meeting is one PDF at /download_file/&lt;id&gt;/191 with titles like 'Trust Board (Public Session) Papers - &lt;Month YYYY&gt;.pdf' or 'Trust Board Agenda and Papers - &lt;Month&gt; &lt;Year&gt;'. Take the 'Public'/'Open Session' 'Papers' file as the main pack. The page also lists future meeting dates (no PDFs yet) at the bottom for forward scanning. No year folders, no per-meeting sub-pages, no JS gating.</t>
+          <t>Static fetch returns empty (JS-rendered). Browser crawler sees dated public board packs ('Trust Board (Public) Papers - May 2026', etc.) plus upcoming dates. PDFs may flag accessibility warnings but the pack links are present. Needs Playwright.</t>
         </is>
       </c>
       <c r="J195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Trust Board (Public Session) Papers - Month YYYY.pdf;Trust Board (Public) Papers - Month YYYY.pdf;/download_file/&lt;id&gt;/191</t>
+          <t>Trust Board (Public) Papers;Trust Board (Public Session) Papers;Agenda and Papers;Open Session Papers</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>one-off response/report items;confidential/private session items;minutes-only items</t>
+          <t>Private Session;confidential;Part 2;Closed</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -13224,7 +13268,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Saw 'Trust Board (Public) Papers - May 2026.pdf' (download_file/30615/191) and 'Trust Board (Public Session) Papers - March 2026 1.pdf' (download_file/30554/191), plus future dates 8 Jul 2026 and 9 Sep 2026 listed without papers yet.</t>
+          <t>JS-rendered; browser render shows dated public Trust Board packs (latest May 2026) plus the 2026-27 schedule. Needs Playwright.</t>
         </is>
       </c>
     </row>
@@ -13894,15 +13938,15 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Pattern C. Landing /about-scas/our-board/board-meetings/ lists bi-monthly public board meetings by date; each links to a per-meeting page (e.g. /board-meeting-in-public-4-june/) holding the agenda plus the combined 'SCAS Public Board papers' PDF under /wp-content/uploads/YYYY/MM/ (e.g. SCASpublic-Board-papers_02042026a.pdf). The old DB URL /document-category/board-papers/ is a JS-rendered taxonomy returning an empty body to static fetch. Papers post shortly before each meeting; minutes appear in the next meeting's pack. Contact company.secretary@scas.nhs.uk for archive. URL fixed 2026-06-13.</t>
+          <t>Correct South Central Ambulance board page. Lists the FY2026/27 schedule and a 'Board paper archive' table (Title/Size/Link) that is JS-populated, so a static fetch sees it empty. Papers publish shortly before each meeting; older papers via company.secretary@scas.nhs.uk. Needs Playwright to read the archive table.</t>
         </is>
       </c>
       <c r="J205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>SCASpublic-Board-papers_DDMMYYYY.pdf;Public Board papers;Board meeting in public {date}</t>
+          <t>Board paper archive table</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -13912,17 +13956,17 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Board-meetings landing lists 2026 meetings (2 Apr, 4 Jun, 3 Sep); per-meeting pages host packs e.g. SCASpublic-Board-papers_02042026a.pdf.</t>
+          <t>Correct SCAS 'Our Board' page; the 'Board paper archive' table is JS-rendered and read empty to the static fetcher. Next meeting 3 Sep 2026; older papers by email. URL unchanged.</t>
         </is>
       </c>
     </row>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Whole domain blocks automated fetchers (WAF). URL is correct: landing -&gt; child page /board-papers -&gt; per-meeting 'Board paper - {date}' sub-page -&gt; pack PDFs. Requires a browser/Playwright render.</t>
+          <t>Current URL is live and correct but the whole sussexcommunity.nhs.uk domain sits behind a WAF (reCAPTCHA-protected) that returns HTTP 403 / 'Socket is closed' to WebFetch — Playwright IS required. Structure: the 'Board meetings and papers' landing links to a 'Board Papers' sub-page (/board-meetings-and-papers/board-papers) which lists one sub-page per meeting (/board-papers/board-paper-{dd-month-yyyy}); each meeting sub-page contains a single combined PDF served via a numbered document route /documents/{id}-{dd-month-yyyy}-board-paper (no .pdf extension). Crawl with Playwright: open board-papers index, follow each board-paper-{date} link, grab the /documents/ link. Papers retained for ~12 months only.</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -614,27 +614,27 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Board paper - {date};bi-monthly public board</t>
+          <t>/board-papers/board-paper-;/documents/;-board-paper</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>minutes-only;committee papers</t>
+          <t>council-of-governors;strategies-plans;quality-account</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Whole sussexcommunity.nhs.uk domain now WAF-blocks static fetch; URL is correct and live with per-meeting 'Board paper - {date}' sub-pages (e.g. 27 Nov 2025). Needs Playwright.</t>
+          <t>Confirmed via Playwright: '27 November 2025 board paper (15.59 MB)' combined PDF at /documents/434-27-november-2025-board-paper; next meeting 28 May 2026.</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Correct board page with two interactive dropdowns - 'Meeting Papers' (2014-May 2026) and 'Meeting Minutes'. PDF links are behind JS dropdowns, absent from static HTML. Playwright must expand 'Meeting Papers' and read the latest dated entry.</t>
+          <t>The meetings-in-public page is the correct QVH landing page but presents papers/minutes through two JavaScript dropdown selectors ('Meeting papers:' and 'Minutes:') going back to 2014, so plain HTTP fetch shows only labels and no hrefs — hence the earlier weak signal. Render with Playwright to expand the dropdowns, or harvest direct links via Google site:qvh.nhs.uk. Each paper entry resolves through a clean /download/meetings-in-public/{slug}/ permalink that points to a flat bundle PDF under /wp-content/uploads/YYYY/MM/ named Papers-PUBLIC-Board-{date}.pdf (sometimes -V2). Probing the /wp-content/uploads/ date path is the most reliable non-rendering route.</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -787,27 +787,27 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Meeting Papers dropdown;dated papers (e.g. May 2026)</t>
+          <t>/wp-content/uploads/YYYY/MM/Papers-PUBLIC-Board-{date}.pdf;/download/meetings-in-public/{slug}/ permalink redirecting to the PDF;filenames starting 'Papers-PUBLIC-Board'</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Meeting Minutes;forthcoming meetings</t>
+          <t>/about-us/board-of-directors/ (member bios);/for-members/public-meetings/ (members' AGM, not board);'Minutes:' dropdown when seeking full packs</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Correct 'Meetings in public' page with a papers archive through May 2026, but PDFs sit behind JS dropdown selectors a static fetch can't see. Needs Playwright.</t>
+          <t>Confirmed a valid 7.8MB 'Papers-PUBLIC-Board-14-May-2026' bundle PDF; a 2025 example resolves via the /download/ permalink to /wp-content/uploads/2025/09/.</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.ashfordstpeters.nhs.uk/meetings</t>
+          <t>https://www.ashfordstpeters.nhs.uk/board-meetings</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>'Trust Board Meetings' lists scheduled dates and links to per-meeting documentation pages under /board-meetings/ (e.g. /board-meetings/3617-trust-board-3rd-june-2026). Crawler follows the most recent dated entry; papers publish the Monday before each meeting. Static fetch works.</t>
+          <t>The /meetings page is an overview; the true archive is /board-meetings which lists every Trust Board meeting back to 2013 as month+year links (e.g. /board-meetings/3617-trust-board-3rd-june-2026). Each meeting page renders a numbered table of Agenda + Paper PDFs. Crucially the PDFs are hosted on the sister domain www.ashfordstpeters.info under /images/board-papers/YYYY-MM-DD/ (note .info not .nhs.uk). Static WebFetch works fine, no WAF; crawl /board-meetings, follow each meeting slug, scrape .info PDF links.</t>
         </is>
       </c>
       <c r="J7" t="b">
@@ -862,17 +862,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>per-meeting agenda and documentation page;pack PDF on that page</t>
+          <t>ashfordstpeters.info/images/board-papers/{YYYY-MM-DD}/Agenda-{Mon}-{YYYY}.pdf;ashfordstpeters.info/images/board-papers/{YYYY-MM-DD}/Paper{n}-{Title}-{Mon}-{YYYY}.pdf</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Register of Interests;Board Member Expenses;Meet the Directors</t>
+          <t>register-of-interests;board-member-expenses;meet-the-directors;Glossary-of-Terms</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Resolves fine with current scheduled meetings linking to dated /board-meetings/ documentation pages (e.g. 3 June 2026). The 'broken' flag was a false positive.</t>
+          <t>June 2026 meeting page lists ~35 board paper PDFs (agenda, CEO report, finance, quality) all live on ashfordstpeters.info.</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Landing lists upcoming 2026 dates and a year-grouped list of dated meeting packs (2026 June open meeting pack, 2025, 2024), each with agenda/pack PDFs. Crawler reads the newest dated entry. Archive older than June 2024 is by email request. Static fetch works.</t>
+          <t>Current URL is correct and live (static WebFetch works, no WAF). The Board of Directors page embeds the full meeting-pack archive organised by month back to June 2024, plus a 'Reading the Signals' oversight group archive. PDFs are served from a relative /s3/assets/files/board_of_directors_docs/bod-meeting-packs/{month}{year}/ path on-domain. Crawl the board-of-directors page and scrape /s3/assets/.../bod-meeting-packs/ links; note some recent meetings split the pack into multiple PDFs and a few items are .docx/.pptx rather than PDF.</t>
         </is>
       </c>
       <c r="J9" t="b">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>open meeting pack;full meeting pack</t>
+          <t>/s3/assets/files/board_of_directors_docs/bod-meeting-packs/{month}{year}/board-of-directors-open-meeting-pack-(DD.MM.YY).pdf;bod-meeting-pack;open-meeting-pack</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Register of interests;Reading the Signals Oversight Group;committee assurance reports</t>
+          <t>registers_of_interests;reading-the-signals;council-of-governors;annual-reports;/policies;/foi</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Full board page with the June 2026 open meeting pack and a deep dated archive visible directly. The 'broken' flag was a false positive (likely WAF 403 to the validator).</t>
+          <t>Live packs present for June 2026 (open-meeting-pack 04.06.26) and April/February 2026 plus full back-catalogue to 2024.</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>'Meetings in public' lists current dated agenda-paper PDFs (papers publish one week before each meeting) plus upcoming 2026 dates; older packs under /meetings-in-public/archive/. Static fetch works.</t>
+          <t>Current URL is live and correct; the reported 'broken' status was a transient/WAF block. WebFetch loaded fine. Page is titled 'Meetings in public' under Trust board, lists 2026 public meeting dates and a '2026 agenda papers' section with PDFs hosted at /wp-content/uploads/YYYY/MM/. Older papers under the 'Archive agenda papers' link. Standard WordPress site; retry WebFetch on 403, no JS rendering required.</t>
         </is>
       </c>
       <c r="J12" t="b">
@@ -1211,17 +1211,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Trust Board meeting in public agenda papers;{date} agenda</t>
+          <t>/wp-content/uploads/2026/;-Trust-Board-meeting-in-public.pdf;DD-Month-2026 in filename</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>register-of-interests;financial-transparency;corporate-publications</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Page directly lists 2026 in-public board agenda papers (21 Apr, 17 Feb 2026) plus an archive link; live. The 'broken' flag was transient/WAF.</t>
+          <t>Two 2026 agenda-paper PDFs (21 April, 17 February) linked directly plus an archive link.</t>
         </is>
       </c>
     </row>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Landing shows the current/next pack as a 'here (PDF)' link plus a dated list of prior packs, each a direct PDF under /download/clientfiles/files/. Packs named 'Combined ... Public Trust Board Papers {date}'. Anti-bot defeats static fetch; needs Playwright.</t>
+          <t>Landing page is protected by an aggressive WAF/bot filter — direct WebFetch returns HTTP 403 and a headless browser gets ERR_CONNECTION_RESET, so a crawler must present a real browser User-Agent and full TLS/cookie handshake (navigate like a human) to reach the HTML. The page is a static server-rendered list of Board of Directors meetings; each meeting links directly to a combined public board pack PDF hosted under /download/clientfiles/files/. There is no year-tab JavaScript — past meetings are listed inline on the same page. Prefer the single 'Combined papers' / 'Public Trust Board' PDF per meeting date rather than individual item attachments.</t>
         </is>
       </c>
       <c r="J37" t="b">
@@ -2848,13 +2848,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Public Board Papers {date};Combined Public Trust Board Papers</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+          <t>/download/clientfiles/files/;Combined papers;Public Trust Board;DD-MM-YY;_compressed.pdf</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>agenda-only;questions;private;confidential;council-of-governors;quality-account</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2864,7 +2868,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Playwright loaded the page with combined packs through 4 June 2026; the static fetcher's connection-aborted error was anti-bot. Needs Playwright.</t>
+          <t>Search-confirmed live 2026 pack (Combined papers Public Trust Board 02-04-26) under /download/clientfiles/files/; landing URL is the current canonical board-meetings page.</t>
         </is>
       </c>
     </row>
@@ -3154,40 +3158,40 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.combined.nhs.uk/about/our-board/board-meetings/</t>
+          <t>https://www.combined.nhs.uk/about-us/our-board/previous-board-meetings/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Landing lists upcoming meetings (to Mar 2027) and a dated archive of past meetings. Papers are NOT direct on the landing page — each dated meeting links to its own sub-page where the pack is posted ~the week before. Crawler must follow the per-meeting sub-page.</t>
+          <t>The trust restructured its 'Our Board' section under /about-us/ (the old /about/our-board/board-meetings/ path still resolves but the maintained pages are now under /about-us/our-board/). The 'Upcoming Board Meetings' page holds only the next meeting's papers, while the dated archive of completed packs lives on the 'Previous Board Meetings' page (archive from Jan 2014 onward) — use that as the landing for historical packs. Pages are static WordPress and crawl cleanly; each meeting links a single combined public pack PDF under /wp-content/uploads/YYYY/MM/. Prefer the file named PUBLIC-TRUST-BOARD-PAPERS-DD.MM.YY.pdf over agenda-only or CEO-report attachments.</t>
         </is>
       </c>
       <c r="J42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>per-meeting sub-page then pack link</t>
+          <t>/wp-content/uploads/;PUBLIC-TRUST-BOARD-PAPERS;DD.MM.YY;.pdf</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Ask the Board;AGM;Annual General Meeting;template/change date;Minutes only</t>
+          <t>agenda;ceo-report;annual-general-meeting;private;confidential</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Connection-aborted 'broken' flag was a false positive; landing lists dated meetings to Mar 2027 but papers post ~the week before each meeting via per-meeting sub-pages.</t>
+          <t>Confirmed live 2026 pack at /wp-content/uploads/2026/01/PUBLIC-TRUST-BOARD-PAPERS-15.01.26.pdf; both upcoming and previous board-meetings pages resolve on-domain.</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3512,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Landing (uhb.nhs.uk/.../papers/) is a gateway whose only link is 'View papers...' pointing to an external Nextcloud store (docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD). The file list is JS-rendered (static fetch shows 'No files in here'). Playwright must open the share, enter the 'Board of Directors meeting papers' folder and read the latest pack.</t>
+          <t>The current URL is correct and live (title 'Papers from meetings of the Board of Directors'), but it does NOT host PDFs inline — it contains a single 'View papers from meetings of the Board of Directors' link to an external Nextcloud document store at https://docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD. That store is a JS-rendered Nextcloud public share: WebFetch sees 'No files in here' (file list loads via XHR) yet exposes an 831.6 MB 'Download all' link, proving the folder is populated. The docs.uhb.nhs.uk host aborts headless browsers on some attempts, so harvesting individual dated PDFs requires Playwright (or the Nextcloud WebDAV/dav API) against the share token. Landing page itself needs no special handling.</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -3516,17 +3520,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Board of Directors meeting papers folder</t>
+          <t>docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD (Nextcloud public share token);Nextcloud share download-all: append /download to the share URL;individual files under /index.php/s/{token}/download?path=&amp;files={filename}</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Download all files zip;No files in here placeholder</t>
+          <t>'No files in here' empty-state text from non-JS fetch;privacy-policy and main-site nav links</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3536,7 +3540,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Landing is a live gateway to an external UHB Nextcloud document store (docs.uhb.nhs.uk) whose file list is JS-rendered; 'Board of Directors meeting papers' folder is populated (831MB). Not a dead URL.</t>
+          <t>Papers exist (831.6 MB download-all on the Nextcloud share) but the dated PDF list is JS-rendered and the docs host blocks headless WebFetch, so a real browser is needed to enumerate packs.</t>
         </is>
       </c>
     </row>
@@ -4082,7 +4086,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Now Kingston and Richmond NHS Foundation Trust. Landing lists recent public Board dates with the part-1 pack PDF linked directly (e.g. '2026-05-07 KRFT Trust Board Part 1') plus a 'Board paper archive' link for older meetings. Static fetch works.</t>
+          <t>Correct landing page for Kingston and Richmond NHS FT (formerly Kingston Hospital, RAX). The board-meetings page shows the current/latest Part 1 board pack as a force-download link, and links to a clean 'Board paper archive' at .../board-meetings/board-paper-archive listing prior years' packs in a Month/Year table. Both pages render links to plain HTTP fetch (no JS needed). Packs are served via opaque CMS download_file URLs of the form /download_file/force/{guid}/354 (current) or /download_file/{guid}/355 (archive), not human-readable filenames, so harvest the hrefs from the two pages rather than guessing paths.</t>
         </is>
       </c>
       <c r="J55" t="b">
@@ -4090,17 +4094,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Trust Board Part 1;KRFT Trust Board</t>
+          <t>/download_file/force/{guid}/354 (latest pack on board-meetings);/download_file/{guid}/355 (archive packs);'Board paper archive' subpage table by Month/Year;link text 'KRFT Trust Board Part 1 - {month year}'</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Part 2;confidential;patient story</t>
+          <t>Ethnicity/Gender Pay Gap Report links;'Former Trusts' report links;/about-us/trust-board (board member bios index);Part 2 / confidential papers</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4110,7 +4114,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Now Kingston and Richmond NHS FT (Kingston Hospital merged). Page shows a May 2026 Part 1 pack and forward dates to Nov 2026. False positive.</t>
+          <t>Page exposes the May 2026 Part 1 pack and a working archive subpage with multiple dated packs, all on the trust's own domain.</t>
         </is>
       </c>
     </row>
@@ -4330,21 +4334,25 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>GESH group board page. Landing lists each meeting as a dated '(PDF)' link pointing straight to the combined pack under /wp-content/uploads/. A sibling page holds the legacy St George's-only series. Anti-bot defeats static fetch; needs Playwright.</t>
+          <t>URL is current and correct. Since the GESH group formed (St George's + Epsom &amp; St Helier), the joint 'Group Board' replaces the single-trust board, and this page is the canonical Group Board papers/agenda archive. Static WordPress; agendas published the Friday before each meeting. Each meeting date links a combined public pack PDF under /wp-content/uploads/YYYY/MM/ (filenames inconsistent — sometimes a date string, sometimes export-YYYY-MM-DD, sometimes gesh-Group-Board-public). Prefer the largest 'Group Board public' pack per date; Epsom &amp; St Helier mirror the same packs. A sibling /board-papers/ page holds legacy single-trust St George's packs.</t>
         </is>
       </c>
       <c r="J59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>{D} {Month} {YYYY} (PDF);group board public meeting pack</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
+          <t>/wp-content/uploads/;gesh;Group-Board-public;Month-YYYY;.pdf</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>council-of-governors;private;confidential;agenda-only;part-2;minutes-only</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4354,7 +4362,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Playwright loaded the GESH group board page with a full dated PDF archive incl. 8 May 2026; the static fetcher's connection-aborted error was anti-bot.</t>
+          <t>Confirmed live 2026 Group Board packs (8 May 2026, 5 March 2026) linked from the group-board-papers-and-agenda page.</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4709,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>kingstonandrichmond.nhs.uk is the correct successor domain (HRCH merged into Kingston and Richmond FT, 1 Nov 2024; hrch.nhs.uk redirects here). 'Board meetings' shows the current pack and upcoming 2026 dates; a 'Board paper archive' sub-page holds dated packs back to 2023 incl. legacy HRCH-era meetings. Static fetch works.</t>
+          <t>RY9 (Hounslow and Richmond Community Healthcare NHS Trust, HRCH) was acquired by Kingston Hospital NHS FT on 1 November 2024; the merged body is Kingston and Richmond NHS Foundation Trust and there is no longer a separate HRCH board. hrch.nhs.uk now 301-redirects to kingstonandrichmond.nhs.uk, and the KRFT board-meetings page is the correct (and only) live board-papers source for RY9. HRCH appears on the KRFT site only as a 'Former Trusts' label on legacy pay-gap reports. Same crawl strategy and CMS download_file pack pattern as RAX; no JS needed. NOTE: RY9 and RAX now point at the same combined board — dedupe/flag in dataset.</t>
         </is>
       </c>
       <c r="J64" t="b">
@@ -4709,17 +4717,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>KRFT Trust Board Part 1 {Month Year}</t>
+          <t>/download_file/force/{guid}/354 (latest combined KRFT pack);/download_file/{guid}/355 (archive packs);'Board paper archive' subpage;hrch.nhs.uk -&gt; kingstonandrichmond.nhs.uk 301 redirect</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Part 2 / private;board paper archive (older only)</t>
+          <t>hrch.nhs.uk standalone paths (now redirect away);Ethnicity/Gender Pay Gap 'Former Trusts' reports;Part 2 / confidential papers;separate HRCH board archive (does not exist post-merger)</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4729,7 +4737,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Domain is correct: Hounslow and Richmond Community Healthcare merged into Kingston and Richmond NHS FT (1 Nov 2024); hrch.nhs.uk 301-redirects to kingstonandrichmond.nhs.uk where its board papers now publish.</t>
+          <t>No standalone HRCH board page post-merger (1 Nov 2024); board papers for RY9 are the combined Kingston and Richmond packs verified live on the trust's own domain.</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5054,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Single 'Our Board and Leadership' page holds the meeting list grouped by year (2026 down to 2018). Each bi-monthly 'Public Board of Directors' meeting links to its papers PDF. Crawler reads dated rows under the current year. Static fetch works.</t>
+          <t>Current URL is live and correct. The 'Our Board and Leadership' page uses a year-tabbed interface (2018-2026) listing each Public Board of Directors meeting; clicking a date reveals a single combined 'papers' PDF hosted in /wp-content/uploads/YYYY/MM/. Crawl the landing page, harvest all .pdf links under wp-content/uploads, and match on date or 'Board-of-Directors'/'Board' in filename. WebFetch works fine here (no WAF). Original failure was transient.</t>
         </is>
       </c>
       <c r="J69" t="b">
@@ -5054,17 +5062,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Public Board of Directors papers;dated meeting</t>
+          <t>wp-content/uploads/YYYY/MM/;Public-Board-of-Directors;Board-of-Directors;Combined;BoD-PUBLIC;Board-Papers</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>private/confidential board;minutes-only</t>
+          <t>Audit-Risk-Committee;ToR;Terms-of-Reference;Committee</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5074,7 +5082,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>'Our Board and Leadership' lists eight 2025/26 dated public board papers and archives to 2018. The 'broken' flag was a false positive.</t>
+          <t>Latest pack '06 May 2026 Public Board of Directors Meeting papers' plus full back-catalogue of combined PDFs visible on the live page.</t>
         </is>
       </c>
     </row>
@@ -5395,35 +5403,35 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Strategy: landing lists year archives (4 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+          <t>Landing page is live but WebFetch is WAF-blocked (HTTP 403 / connection reset); use Playwright. The landing page lists meeting dates and links to per-year 'Board Papers' pages at /about-us/{YEAR}-board-papers/. The current-year page is an accordion/tablist: each meeting date is a collapsed tab whose individual enclosure PDFs are only revealed when clicked, so Playwright is required to click each tab and harvest links. PDFs are NOT a single pack — each agenda enclosure is a separate PDF (lettered A, B, C...) served from /download/clientfiles/files/ or the older /clientfiles/File/ path with URL-encoded spaces.</t>
         </is>
       </c>
       <c r="J74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Board Papers;Public Board Pack</t>
+          <t>/about-us/{YYYY}-board-papers/;/download/clientfiles/files/*.pdf;/clientfiles/File/*.pdf;enclosure letter prefixes e.g. 'X - 20251125 - BOD'</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Observer notes;Q&amp;A;ICP Board;Minutes only;Addendum;Part B;Confidential</t>
+          <t>/2020-board-papers/;/2021-board-papers/;/2022-board-papers/;/2023-board-papers/;/2024-board-papers/;/2025-board-papers/;official-publications</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>papers_partial</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=0, year_archives=4, meeting_subpages=0.</t>
+          <t>Live 2026 board-papers page lists six 2026 meeting dates as accordion tabs; individual enclosure PDFs on clientfiles paths but require tab expansion to enumerate.</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5827,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>'Board of Directors Meeting Dates and Papers' lists combined agenda+papers PDFs per meeting under /fileadmin/.../BoardPapers/{year}/, named 'Combined_-_Public_Board_of_Directors_-_{date}_WEBSITE.pdf'. 2026 packs present plus expandable year archives to 2015. Static fetch works.</t>
+          <t>Current URL is correct and live (Calderdale and Huddersfield, cht.nhs.uk, TYPO3 site). Page renders server-side listing meeting dates for 2026 and prior years; each held/upcoming meeting with papers links to a single combined 'Agenda and Papers' PDF under /fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/{year}/. Filenames follow 'Combined_-_Public_Board_of_Directors_-_{Weekday}_{D}_{Month}_{YYYY}_WEBSITE.pdf'. Plain WebFetch works; no WAF/JS. Future dates show 'No papers linked' until published.</t>
         </is>
       </c>
       <c r="J80" t="b">
@@ -5827,17 +5835,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Combined - Public Board of Directors - {date} WEBSITE;BoardPapers/{year}/Combined</t>
+          <t>/fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/{YYYY}/;Combined_-_Public_Board_of_Directors_-_{Weekday}_{D}_{Month}_{YYYY}_WEBSITE.pdf;'Agenda and Papers' / 'Combined Papers' link text per dated meeting</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>papers not yet posted;upcoming Board meetings</t>
+          <t>meetings showing 'No papers linked';prior-year sections (2025 and earlier)</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5847,7 +5855,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Page directly lists 2026 combined public board packs (15 Jan, 12 Mar, 14 May 2026) plus full historical archive. The no_papers_visible flag was wrong.</t>
+          <t>2026 combined public board PDFs (15 Jan, 12 Mar, 14 May) are live large files on cht.nhs.uk.</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6026,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>'Board meetings and papers' lists dated meetings with Papers + Minutes, with year-by-year archives ('Meetings in {year}') back to 2008. Crawler follows the dated 'Papers' link (separate from Minutes). Static fetch works.</t>
+          <t>Current URL is live and correct; reported 'broken' was transient/WAF. WordPress site under About us &gt; How we're run &gt; Our Trust Board &gt; Meetings and papers. Page archives meetings chronologically back to 2008, each with agenda+papers PDF and minutes PDF hosted at /wp-content/uploads/YYYY/MM/. Next meeting 30 June 2026. Retry WebFetch on 403; no JS rendering needed.</t>
         </is>
       </c>
       <c r="J83" t="b">
@@ -6026,17 +6034,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Papers per dated meeting;Meetings in {year}</t>
+          <t>/wp-content/uploads/2026/;Public-agenda-and-papers-TB-DD.MM.YY;Public-Board-agenda-and-papers-DD.MM.YY</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>minutes</t>
+          <t>minutes;governance-documents;register</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6046,7 +6054,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Page directly lists 2026 board papers and minutes (28 Apr, 31 Mar, 27 Jan 2026) plus deep year archives to 2008; live. The 'broken' flag was transient/WAF.</t>
+          <t>Recent 2026 public board packs (30 June, 28 April, 31 March) linked as direct PDFs.</t>
         </is>
       </c>
     </row>
@@ -6662,13 +6670,39 @@
           <t>https://www.cuh.nhs.uk/about-us/board-directors/board-of-directors-meetings/</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Landing page is live but WebFetch hits a WAF/anti-bot block (socket closed); use Playwright/headless browser. The landing page itself holds no PDFs — it links to per-year archive sub-pages via a sidebar (2017-2026). Open the current year page /about-us/board-directors/board-of-directors-meetings/{YEAR}-board-of-directors-meetings/ which lists each meeting as an EVENT link (e.g. /events/board-of-directors-meeting-10-june-2026/); the full board pack PDF is inside the event page, served from the media.cuh.nhs.uk/documents/ subdomain. Alternatively Google site:media.cuh.nhs.uk Full_Pack to find packs directly.</t>
+        </is>
+      </c>
+      <c r="J93" t="b">
+        <v>1</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>media.cuh.nhs.uk/documents/Board_of_Directors_-_Full_Pack_{D}_{Month}_{YYYY}.pdf;media.cuh.nhs.uk/documents/*Full_Pack*.pdf;/events/board-of-directors-meeting-{day}-{month}-{year}/</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>/2017-;/2018-;/2019-;/2020-;/2021-;/2022-;/2023-;statement-of-purpose;council-of-governors</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Live 2026 archive sub-page lists four 2026 meetings and June 2026 full pack PDF confirmed on media subdomain.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7359,7 +7393,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Landing lists six public meetings/year with per-financial-year link sets ('Board Meeting and Papers 25/26', '26/27'...). Follow the year link (some go to a SharePoint/document-library SafeLink) to reach dated packs. Static fetch works.</t>
+          <t>Current landing URL is live and correct; it is an index page that links OUT to the separate document subdomain doclibrary-rcht.cornwall.nhs.uk, one .aspx page per financial year (BoardMeetings2627.aspx, BoardMeetings2526.aspx, etc., plus BoardMeetingsIndex.aspx for older). The actual dated PDFs live under doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/{2526}/{YYYYMM}/. Two-hop crawl: from landing page get the current-year .aspx, then harvest 'AgendaPack' PDFs (each monthly board has one combined Agenda Pack; alternate months carry only an IPR). WebFetch works on the doclibrary subdomain.</t>
         </is>
       </c>
       <c r="J104" t="b">
@@ -7367,17 +7401,17 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Board Meeting and Papers 25/26;Public Trust Board Agenda and Papers</t>
+          <t>doclibrary-rcht.cornwall.nhs.uk/DocumentsLibrary/RoyalCornwallHospitalsTrust/ChiefExecutive/TrustBoard/Minutes/;AgendaPack;TrustBoardPublic;AnnualPublicMeeting</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>royalcornwall.nhs.uk (legacy WAF-blocked domain);/board-members-and-committees/;DeclarationsOfInterest;GiftsHospitalitySponsorship;language/translate anchors (#);bit.ly join-the-meeting links</t>
+          <t>IPR;IntegratedPerformanceReport;AnnualReportAndAccounts;Strategy</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7387,7 +7421,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Page returns full content with 2026/2027 meeting dates and per-year board-paper links. The 'broken' flag was a false positive.</t>
+          <t>Current-year page (BoardMeetings2526.aspx) lists 'Agenda Pack Trust Board in Public March 2026' and full monthly back-catalogue of agenda packs.</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7517,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Landing lists dated board meetings, each with papers/minutes/recordings. Pack PDFs sit under /media/ as 'meeting-book-board-of-directors-meeting-public-{date}.pdf'; minutes are separate ('minutes-board-public-{yyyymmdd}-approved.pdf'). Host WAF-403s static fetch; needs Playwright.</t>
+          <t>Landing page is live and current but the site sits behind a WAF that returns HTTP 403 to WebFetch; use Playwright/headless browser, which loads it cleanly. The page lists the current calendar year's meetings inline with a 'Board papers and minutes' section giving, per meeting date, a meeting-pack PDF link plus a separate 'Minutes' PDF link, all served from the /media/{hash}/ path on the org domain. Older years live at .../board-meetings-papers-minutes/archive/. Match the meeting-pack PDF (filenames contain 'pack' or 'meeting-book' or 'meeting-pack'), not the minutes.</t>
         </is>
       </c>
       <c r="J106" t="b">
@@ -7491,17 +7525,17 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>meeting-book-board-of-directors-meeting-public;board-of-directors-meeting-public-{date}.pdf</t>
+          <t>/media/{hash}/rduh-*-pack*.pdf;/media/{hash}/*meeting-pack*.pdf;/media/{hash}/*meeting-book*.pdf;board-public-{YYYYMMDD}</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>minutes;action-tracker;approved</t>
+          <t>minutes;action-tracker;glossary_of_acronyms;/archive/</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7511,7 +7545,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>WebFetch hit HTTP 403 (WAF) but site search confirms the URL is the live board page with dated packs through March 2026. False positive; needs Playwright.</t>
+          <t>Three 2026 meeting packs (27 May, 25 Mar, 28 Jan) plus minutes listed inline on the live page, last updated June 2026.</t>
         </is>
       </c>
     </row>
@@ -9023,35 +9057,35 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Landing ('Trust Board meetings') states papers post before each meeting and links to per-year archive sub-pages /trust-board/trust-board-meetings/trust-board-papers-{YYYY}/. Heavy WAF; needs Playwright/browser.</t>
+          <t>Landing page is live and even loads via WebFetch (no WAF block observed). The page lists, per meeting date, a single combined 'Download meeting papers {Month YYYY}' PDF plus a 'final minutes' PDF; the combined agenda+papers pack is one file served from the media.gosh.nhs.uk/documents/ subdomain. Take the meeting-papers pack (filenames contain 'Trust_Board_agenda_and_papers_{DDMMYY}'), not the minutes. Older years have their own sub-pages (.../trust-board-papers-{YEAR}/).</t>
         </is>
       </c>
       <c r="J130" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Trust Board papers {YYYY} year archive sub-pages</t>
+          <t>media.gosh.nhs.uk/documents/*Trust_Board_agenda_and_papers_{DDMMYY}.pdf;media.gosh.nhs.uk/documents/Public_Trust_Board_agenda_and_papers_*.pdf;'Download meeting papers {Month} {Year}' link text</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>minutes;Archived meetings 2011 to 2020</t>
+          <t>minutes;trust-board-papers-2015;trust-board-papers-201;members-council;publication-scheme</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>GOSH heavily WAF-protected (static fetch connection-aborted); site search confirms the URL is the live canonical board page with per-year archive sub-pages. Needs Playwright.</t>
+          <t>Live page shows the 18 June 2026 combined papers pack (6.1MB) plus Jan/Mar/May 2026 papers and minutes; WebFetch read it successfully.</t>
         </is>
       </c>
     </row>
@@ -9470,7 +9504,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Landing lists Board of Directors meetings grouped by financial year; each dated meeting carries an 'Agenda and papers' link to the combined pack. Crawler reads the dated rows under the current year and follows that link. Static fetch works.</t>
+          <t>Current URL is live and correct; the 'no board papers visible' failure was a WAF/transient block — the page renders board papers organised by financial year (2019/20 through 2026/27). Breadcrumb: Home &gt; About us &gt; Our people &gt; Our board &gt; Board papers. PDFs are served via an indirected download endpoint /download_file/view/{uuid}/{id} rather than direct .pdf links, so link-detection must capture download_file/view hrefs, not just *.pdf. Retry WebFetch on 403; no JS rendering required.</t>
         </is>
       </c>
       <c r="J137" t="b">
@@ -9478,17 +9512,17 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Agenda and papers;board papers</t>
+          <t>/download_file/view/;financial-year groupings (e.g. 2026/27);agenda and papers per meeting date</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>minutes;agenda-only</t>
+          <t>board-meeting-dates;executive-directors;non-executive-directors</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -9498,7 +9532,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>'Board papers' page lists 2025/26 dated meetings (e.g. 5 Feb 2026) by financial year with 'Agenda and papers' links; archives to 2019/20. Flag was a false positive.</t>
+          <t>Most recent 2026/27 meetings (4 June, 2 April) each link to agenda and papers via download_file/view endpoints.</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10047,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.cntw.nhs.uk/about/publications/?filter_publication_type=344</t>
+          <t>https://www.cntw.nhs.uk/about/team/board/</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Pattern B/C: the old stored URL was a deep 2015 single agenda-item front-sheet page (long stale). The correct landing is the trust Publications archive filtered to the 'Board Papers' category via ?filter_publication_type=344 (https://www.cntw.nhs.uk/about/publications/?filter_publication_type=344). This lists per-meeting publication pages titled 'Board Papers - &lt;date&gt;' (e.g. /about/publications/board-papers-29-april-2026/), each linking to a combined board-papers PDF under /wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/ (e.g. CNTW-Board-of-Directors-Public-Papers-April-2026.pdf). The unfiltered /about/publications/ page also surfaces the same board entries near the top. Skip Council of Governors entries. Crawler should hit the filtered publications list, then per-meeting subpage, then the combined PDF.</t>
+          <t>The old publications library (/about/publications/ and the ?filter_publication_type=344 filter, plus per-meeting /about/publications/board-papers-DATE/ pages) has been decommissioned and now returns hard 404s. The current canonical board landing is /about/team/board/ (title 'Board and Governors'), which loads cleanly via static fetch and lists the latest meeting packs (Jan 2026, April 2026, plus Council of Governors packs) as download links of the form /download_file/{uuid}/258 rather than direct .pdf URLs. The trust holds quarterly public board meetings; this page surfaces the most recent few packs, so follow each download_file link. Raw /wp-content/uploads/*.pdf files exist on the CDN but return 403 to bots behind the WAF — prefer the on-page download_file links. Prefer 'Board of Directors PUBLIC papers' over Council of Governors items.</t>
         </is>
       </c>
       <c r="J145" t="b">
@@ -10026,17 +10060,17 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Board Papers - &lt;date&gt;;CNTW-Board-of-Directors-Public-Papers-&lt;month-year&gt;.pdf;/about/publications/board-papers-;filter_publication_type=344</t>
+          <t>/download_file/;Board of Directors;PUBLIC papers;/wp-content/uploads/;Month-YYYY</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>Council-of-Governors;council-of-governors;/news/;annual-report;green-plan;agenda-item-</t>
+          <t>council-of-governor;private;confidential;agenda-only;minutes</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10046,7 +10080,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Board Papers category filter (type 344) lists 2025-26 per-meeting pages with confirmed combined PDFs for 29 April 2026, 28 January 2026 and 5 November 2025.</t>
+          <t>/about/team/board/ lists 'CNTW Board of Directors Public Papers Jan 2026' and 'April 2026' (posted 17/06/2026) as download_file links; old publications pages return genuine 404.</t>
         </is>
       </c>
     </row>
@@ -10928,7 +10962,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Landing lists dated public board meetings with direct 'Papers' links per meeting, plus fiscal-year archive sections. Crawler reads the most recent dated entry and follows its 'Papers' link. Static fetch works.</t>
+          <t>Current URL is live and correct; 'no board papers visible' was a WAF/transient block. Page lists upcoming Board of Directors dates plus completed-meeting 'Meeting papers' links organised by financial year back to Sept 2021 (plus archival Committee in Common 2019-2021). PDFs use an indirected endpoint /download_file/view/{id}/{collection} rather than direct .pdf URLs, so capture download_file/view hrefs. Public sessions also have livestream/recording video links to ignore. Retry WebFetch on 403; no JS rendering required.</t>
         </is>
       </c>
       <c r="J161" t="b">
@@ -10936,17 +10970,17 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Papers;Board of Directors papers</t>
+          <t>/download_file/view/;financial-year groupings;'Meeting papers' link per completed date</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>minutes;YouTube;recording;agenda only</t>
+          <t>livestream;video;council-of-governors;annual-reports;quality-accounts</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -10956,7 +10990,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>'Board Dates and Papers' shows upcoming 2026/27 dates with per-meeting 'Papers' links visible directly. False positive.</t>
+          <t>Completed 2026 meetings (6 May, 4 March) each link to meeting papers via download_file/view endpoints.</t>
         </is>
       </c>
     </row>
@@ -11148,12 +11182,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.wwl.nhs.uk/about-us/board-papers/</t>
+          <t>https://www.wwl.nhs.uk/board-papers</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Landing lists dated 2026 board meetings each with a 'Meeting papers' PDF link, plus future dates without papers and a link to the Board Papers Archive for prior years. Crawler takes the latest dated meeting with a live 'Meeting papers' link. Static fetch works.</t>
+          <t>The old path /about-us/board-papers/ still 200s but the canonical current landing is /board-papers (title 'WWL Teaching Hospitals NHS Foundation Trust | Board Papers'). Both pages render server-side and list public meeting bundles by date under a '2026 Meetings' section, each with a 'Meeting papers' link to a single combined PDF in /media/board/Papers/{year}/. An older archive sits at /board-papers-archive. Plain WebFetch reads it fine; no WAF or JS needed. Filenames are not URL-stable; crawl by matching 'Public Bundle'/'Public meeting'/'meeting bundle' + DD.MM.YY in /media/board/Papers/2026/.</t>
         </is>
       </c>
       <c r="J164" t="b">
@@ -11161,17 +11195,17 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Meeting papers PDF per dated meeting</t>
+          <t>/media/board/Papers/{YYYY}/;Board of Directors - Public Bundle DD.MM.YY RFS.pdf;Board of Directors meeting bundle - Public meeting DD.MM.YY RFS.pdf</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>agendas-not-yet-published rows;Board Papers Archive (older)</t>
+          <t>/board-papers-archive (older years);upcoming meetings with agenda not yet published;Company.Secretary contact text</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11181,7 +11215,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>'Board Papers' lists 2026 dated meeting packs (4 Feb, 1 Apr, 17 Jun 2026) with 'Meeting papers' PDF links visible directly. False positive.</t>
+          <t>2026 public board bundles (04 Feb, 01 Apr, 17 Jun) present as live large PDFs on the wwl.nhs.uk domain.</t>
         </is>
       </c>
     </row>
@@ -11622,7 +11656,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>'Agendas and Meetings' covers Trust Board and Council of Governors. Recent public board meetings link to a PDF pack; very recent/upcoming dates may list no PDF yet. Year archives 2021-2024 expandable. Crawler targets 'Public Board Meeting' rows (not Council of Governors). Static fetch works.</t>
+          <t>Current URL is live and correct. 'Agendas and Meetings' page lists upcoming public board dates and, per meeting, a main 'Meeting in Public' compressed PDF plus an optional 'SUPPLEMENTARY SHELF' PDF, all under /wp-content/uploads/YYYY/MM/. A separate archive page (/about-us/our-structure/board-of-directors/trust-board-papers) holds older packs. Crawl landing page, harvest wp-content .pdf links matching 'Meeting-in-Public'. WebFetch works (no WAF). Original failure was transient.</t>
         </is>
       </c>
       <c r="J171" t="b">
@@ -11630,17 +11664,17 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Public Board Meeting + date;meeting pack PDF</t>
+          <t>wp-content/uploads/YYYY/MM/;Meeting-in-Public;compressed;0-Meeting-in-Public</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Council of Governors;private/confidential</t>
+          <t>SUPPLEMENTARY-SHELF;SUPPLEMENTARY</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -11650,7 +11684,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>'Agendas and Meetings' shows May 2026 and March 2026 public board packs plus forward dates. The 'broken' flag was a false positive.</t>
+          <t>Latest pack '0-Meeting-in-Public 02.07.2026 compressed' plus prior May/March 2026 packs visible on the live page.</t>
         </is>
       </c>
     </row>
@@ -11896,7 +11930,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Land on /about-us/corporate-information-and-governance/. The page exposes dated 'meeting book public board of directors' PDFs under /media/ (e.g. 21 May 2026); each dated link IS the combined public pack. Host WAF-403s static fetch and the list renders via JS; needs Playwright.</t>
+          <t>Cloudflare blocks WebFetch (403 on every hpft.nhs.uk URL incl. PDFs) so Playwright is required. The often-cited /about-us/board-of-directors-meetings/ and /our-board-papers-and-publications/ paths are 404. The real archive is a JS FAQ accordion titled 'Board papers and publications' on this corporate-information-and-governance page: the panel is initially collapsed (no anchors in static DOM) — click the .faq-panel-question whose text is 'Board papers and publications' to reveal a list of dated 'meeting book' PDF links back to 2021. PDFs are hosted on-domain under /media/{slug}/...meeting-book-public-board-of-directors-*.pdf.</t>
         </is>
       </c>
       <c r="J175" t="b">
@@ -11904,17 +11938,17 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>meeting-book-public-board-of-directors</t>
+          <t>/media/{slug}/meeting-book-public-board-of-directors-{DDMMYY}.pdf;/media/{slug}/meeting-book-board-of-directors-public-*.pdf;public-board-pack-*.pdf</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>doi-register;gifts-and-hospitality;quality-account</t>
+          <t>annual-report;auditors-annual-report;cog-meeting-book;council-of-governors;disclosure-log;equality-delivery-system</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -11924,7 +11958,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>DB URL correct/live; 'broken' is a WAF false positive (host 403s static fetch, renders in a browser). 80 dated 'meeting book public board of directors' PDFs to 21 May 2026. Needs Playwright.</t>
+          <t>Accordion reveals live 2026 meeting books for 21 May, 26 March and 22 January 2026 (plus full history to 2021).</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12178,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Landing lists dated Board of Directors meetings (each 9:30am) with a 'Papers' link. From Jan 2026 meetings run as the 'NHS University Hospitals Group Board', still on the LHCH domain. Year archives 2015-2024 below. Static fetch works.</t>
+          <t>Single landing page at /board-of-directors-meetings titled 'Board of Directors Meetings' listing meetings by year (2015-2025) each with a per-meeting download link. Crawl this one page and collect all hrefs matching /resources/download/lhch-*; each is a combined agenda+papers bundle for one meeting (date in adjacent link text). Note: from 2026 onward the trust joined NHS University Hospitals of Liverpool Group and 2026 board meetings are hosted off-domain on the group website (external links), so this page may stop adding new dates — watch for migration.</t>
         </is>
       </c>
       <c r="J179" t="b">
@@ -12152,17 +12186,17 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Board of Directors meeting;Papers;NHS University Hospitals Group Board</t>
+          <t>/resources/download/lhch-&lt;hex-id&gt;;link text contains weekday + day + month + year e.g. 'Tuesday 23rd September 2025'</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>minutes;agenda-only</t>
+          <t>mailto:;/resources/download/ items not labelled as board meeting papers;external group-website links (uhlg)</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -12172,7 +12206,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>'Board of Directors Meetings' shows 2025 dated meetings plus Jan/Mar 2026 group-board entries with papers. False positive.</t>
+          <t>Page lists 5 meetings for 2025 and 7 for 2024 each with a working agenda/papers download link on the trust's own domain; watch for 2026 migration to UHLG group site.</t>
         </is>
       </c>
     </row>
@@ -12219,7 +12253,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>WordPress publications-archive page. Each 'Trust Board Meeting - {date}' is a single large combined pack PDF. Crawler reads the most recent dated entry; the archive paginates older packs. Static fetch works (latest entry surfaced).</t>
+          <t>WordPress publications archive filtered to the 'board-papers' type; titled 'Board papers Archives'. It is paginated (12 pages confirmed via /page/2/ .. /page/12/) and displays roughly one Trust Board meeting per page newest-first. Crawl the base URL then iterate /page/N/ to enumerate all meetings; each meeting links to a single combined agenda+documentation PDF under /wp-content/uploads/YYYY/MM/. Filenames vary ('Agenda-Documentation-Trust-Board' or 'Trust-Board-Meeting') so match on the wp-content/uploads path plus date in title rather than a fixed filename.</t>
         </is>
       </c>
       <c r="J180" t="b">
@@ -12227,17 +12261,17 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Trust Board Meeting + date;combined pack PDF ~17MB</t>
+          <t>/wp-content/uploads/{YYYY}/{MM}/*Trust-Board*.pdf;title 'Trust Board Meeting - &lt;day&gt; &lt;month&gt; &lt;year&gt;';pagination /publications_type/board-papers/page/&lt;N&gt;/</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>minutes-only;committee papers</t>
+          <t>non-board publication types (quality reports, annual reports);mailto:</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -12247,7 +12281,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>WordPress publications archive listing each 'Trust Board Meeting - {date}' as a single ~17MB combined pack (e.g. 5 Feb 2026). False positive.</t>
+          <t>Latest meeting (5 Feb 2026) on page 1 and a 12-page back-catalogue of board PDFs confirmed on the trust's own domain.</t>
         </is>
       </c>
     </row>
@@ -12643,7 +12677,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Landing lists forthcoming and recent meetings with an 'Agenda and papers' link per meeting, plus yearly archive headings (2019-2026). Crawler follows the dated link to each meeting's pack. Static fetch works.</t>
+          <t>Single page titled 'Meetings :: East Cheshire NHS Trust' listing Trust Board meetings by year (2019-2026), each row offering an 'Agenda and papers' link. Crawl this one page and collect the hrefs; PDFs live on the main domain www.eastcheshire.nhs.uk in two formats - /application/files/&lt;ids&gt;/&lt;Name&gt;_Numbered.pdf (preferred, named with month+year) and legacy /download_file/view/&lt;id&gt;/&lt;id&gt;. Each is a combined agenda+supporting-papers bundle for one public Trust Board meeting. Match newest by the year headings and the month name embedded in the application/files filename.</t>
         </is>
       </c>
       <c r="J186" t="b">
@@ -12651,17 +12685,17 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>Public Trust Board Agenda and Papers {Month YYYY};Agenda and papers</t>
+          <t>https://www.eastcheshire.nhs.uk/application/files/&lt;id&gt;/*Trust_Board*Agenda*Papers*Numbered.pdf;link text 'Agenda and papers';filename contains month + year e.g. 'November_2025'</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>/non-exec;minutes-only;committee-;private;confidential</t>
+          <t>mailto:;committee/sub-board meetings if any (filter to Trust Board)</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -12671,7 +12705,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Full page with dated 2025/2026 meetings and year archives back to 2019; the 'papers_partial' flag understated it.</t>
+          <t>Two 2026 meetings (Mar 5, Jan 13) and full 2025 set each link to a working agenda+papers PDF on the trust's own eastcheshire.nhs.uk domain.</t>
         </is>
       </c>
     </row>
@@ -12917,7 +12951,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>'Board papers' page organised by year (2026 down to 2020) with named public meeting-pack PDFs (e.g. 'Board of Directors Public Meeting Pack - 05 03 2026.pdf'). Crawler opens the 2026 section and takes the latest dated pack. Static fetch works.</t>
+          <t>Current URL is correct and live. The page renders server-side and lists 'Public Board of Directors Meeting Papers' by date for 2026 back to 2020, grouped by year. Each entry links via an opaque numeric download endpoint /download_file/{id}/{key} (not a descriptive filename), so map packs by the visible link text (which carries the DD.MM.YY date and 'Public' label) rather than the URL. Plain WebFetch works; no WAF/JS. Crawl the 2026 block for 'Public Board of Directors Meeting Papers - DD.MM.YY' and resolve each to its /download_file/ URL.</t>
         </is>
       </c>
       <c r="J190" t="b">
@@ -12925,17 +12959,17 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Board of Directors Public Meeting Pack - DD MM YYYY.pdf</t>
+          <t>/download_file/{id}/{key} opaque download endpoint;link text: 'Public Board of Directors Meeting Papers - DD.MM.YY';link text: 'Board of Directors Public Meeting Pack - DD.MM.YY'</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>minutes-only;future dates without packs</t>
+          <t>years prior to current (2024/2023/2022/2021/2020 sections);'Back to Board of Directors' nav link</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -12945,7 +12979,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>'Board papers' page organised by year with named 2026 public meeting-pack PDFs visible directly. False positive.</t>
+          <t>2026 monthly public board packs (Feb-Jun) present as live /download_file/ PDFs on lscft.nhs.uk.</t>
         </is>
       </c>
     </row>
@@ -13041,7 +13075,7 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>/board lists dated board entries as JS news-style cards; each links to a per-meeting summary page, which links to the full 'Board agenda pack' PDF under /application/files/ (e.g. PUBLIC_BoD_Agenda_Pack_Final_27_05_2026.pdf). WAF + JS; needs Playwright; follow summary -&gt; agenda pack.</t>
+          <t>Cloudflare blocks WebFetch (403) so Playwright is needed. The original /board URL is correct — it is the 'Board summaries' index listing each meeting (e.g. 27 May 2026, 25 Mar 2026, 28 Jan 2026) as links to per-meeting HTML summary pages (some via short slugs like /mar26, /boardnov25). The /board landing page itself has NO PDFs; you must open each board-summary page, which contains a single 'Board agenda pack' link to the full PDF hosted on-domain at /application/files/{path}/PUBLIC_BoD_Agenda_Pack_Final_{DD_MM_YYYY}.pdf. Crawl /board, follow each summary link, scrape the agenda-pack PDF.</t>
         </is>
       </c>
       <c r="J192" t="b">
@@ -13049,17 +13083,17 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>PUBLIC_BoD_Agenda_Pack_Final_{DD_MM_YYYY};PUBLIC BoD Agenda Pack</t>
+          <t>/application/files/{ids}/PUBLIC_BoD_Agenda_Pack_Final_{DD_MM_YYYY}.pdf;PUBLIC_BoD_Agenda_Pack;board-summary-{month}-{day}-{year}</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>board summary</t>
+          <t>/our-governors;easyread;/events;publication-scheme</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13069,7 +13103,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>DB URL live and org-correct ('Board summaries :: Cheshire and Wirral Partnership'); 'broken' is WAF 403 + JS cards. Needs Playwright.</t>
+          <t>27 May 2026 board summary links to a live full agenda-pack PDF (PUBLIC_BoD_Agenda_Pack_Final_27_05_2026.pdf).</t>
         </is>
       </c>
     </row>
@@ -13938,7 +13972,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Correct South Central Ambulance board page. Lists the FY2026/27 schedule and a 'Board paper archive' table (Title/Size/Link) that is JS-populated, so a static fetch sees it empty. Papers publish shortly before each meeting; older papers via company.secretary@scas.nhs.uk. Needs Playwright to read the archive table.</t>
+          <t>The /about-scas/our-board/board-meetings/ landing page lists the meeting schedule and a 'Board paper archive' table, but the archive table and paper links are rendered by JavaScript and invisible to plain HTTP fetch (only the meeting dates and a contact email show). To get actual papers, crawl the dedicated WordPress document-category archive at /document-category/board-papers/ and the per-meeting announcement pages (e.g. /board-meeting-in-public-3-september-2026/), which link to bundle PDFs; both are also JS-driven so use Playwright or harvest direct PDF URLs from Google site:scas.nhs.uk. Final PDFs are flat files under /wp-content/uploads/YYYY/MM/ named SCAS...Board-papers_DDMMYYYY.pdf, so a path/date probe works without rendering. Papers publish shortly before each meeting.</t>
         </is>
       </c>
       <c r="J205" t="b">
@@ -13946,27 +13980,27 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Board paper archive table</t>
+          <t>/wp-content/uploads/YYYY/MM/SCAS...Board-papers_DDMMYYYY.pdf;/wp-content/uploads/ filename containing 'Board-papers';per-meeting pages at /board-meeting-in-public-{date}/;document-category/board-papers/ archive listing</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>agenda-only PDF;minutes only;Annual Members Meeting</t>
+          <t>/about-scas/our-board/scas-board-members/;/registers-of-interests/;/council-of-governors/;/news/</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Correct SCAS 'Our Board' page; the 'Board paper archive' table is JS-rendered and read empty to the static fetcher. Next meeting 3 Sep 2026; older papers by email. URL unchanged.</t>
+          <t>Confirmed a valid 7.5MB public board papers bundle PDF (2 April 2026) downloads from the /wp-content/uploads/ path containing 2025-2026 BAF documents.</t>
         </is>
       </c>
     </row>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -624,17 +624,17 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Confirmed via Playwright: '27 November 2025 board paper (15.59 MB)' combined PDF at /documents/434-27-november-2025-board-paper; next meeting 28 May 2026.</t>
+          <t>Landing correct but whole sussexcommunity.nhs.uk domain behind reCAPTCHA WAF (403/socket-closed to automated fetch); Playwright required.</t>
         </is>
       </c>
     </row>
@@ -797,17 +797,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Confirmed a valid 7.8MB 'Papers-PUBLIC-Board-14-May-2026' bundle PDF; a 2025 example resolves via the /download/ permalink to /wp-content/uploads/2025/09/.</t>
+          <t>QVH meetings-in-public page live; papers behind JS dropdown selectors back to 2014 - needs browser; PDFs Papers-PUBLIC-Board-{date}.pdf under /wp-content/uploads.</t>
         </is>
       </c>
     </row>
@@ -2558,17 +2558,17 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>JS-rendered meeting list; browser render shows the 14 May 2026 meeting with combined papers/public information pack/public agenda and a dropdown back to 2015.</t>
+          <t>Confirmed JS-rendered (empty static body); browser crawler uses year/month dropdown 2015-2026. Access notes current.</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Confirmed live 2026 pack at /wp-content/uploads/2026/01/PUBLIC-TRUST-BOARD-PAPERS-15.01.26.pdf; both upcoming and previous board-meetings pages resolve on-domain.</t>
+          <t>Previous-board-meetings archive confirmed live via search (PUBLIC-TRUST-BOARD-PAPERS-15.01.26.pdf present); direct/automated fetch now hits anti-bot (404/connection-reset) though page serves to browsers.</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Papers exist (831.6 MB download-all on the Nextcloud share) but the dated PDF list is JS-rendered and the docs host blocks headless WebFetch, so a real browser is needed to enumerate packs.</t>
+          <t>Landing correct; papers on external JS-rendered Nextcloud store (docs.uhb.nhs.uk) - needs browser/WebDAV, not inline PDFs.</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Page exposes the May 2026 Part 1 pack and a working archive subpage with multiple dated packs, all on the trust's own domain.</t>
+          <t>Kingston &amp; Richmond board meetings page live; latest 7 May 2026 Part 1 pack + board paper archive link.</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Confirmed live 2026 Group Board packs (8 May 2026, 5 March 2026) linked from the group-board-papers-and-agenda page.</t>
+          <t>GESH Group Board papers/agenda archive live; latest 8 May 2026 pack linked. Automated fetch intermittently hits connection reset (WAF).</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>No standalone HRCH board page post-merger (1 Nov 2024); board papers for RY9 are the combined Kingston and Richmond packs verified live on the trust's own domain.</t>
+          <t>HRCH merged into Kingston &amp; Richmond (RAX) 1 Nov 2024; same combined board/URL as RAX (dedupe). Latest 7 May 2026.</t>
         </is>
       </c>
     </row>
@@ -4873,17 +4873,17 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>JS-rendered schedule; papers post 3 working days before each open board, so the latest pack may not be up between meetings. Follow per-year archive links. Needs Playwright.</t>
+          <t>Confirmed JS-rendered; browser sees open board dates + per-year archives 2017-2026. Access notes current.</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026 combined public board PDFs (15 Jan, 12 Mar, 14 May) are live large files on cht.nhs.uk.</t>
+          <t>Calderdale &amp; Huddersfield board dates/papers page live; combined Agenda and Papers PDFs under /fileadmin (latest shown 15 Jan 2026). Validator PDF-detection miss.</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Live 2026 archive sub-page lists four 2026 meetings and June 2026 full pack PDF confirmed on media subdomain.</t>
+          <t>CUH board meetings page live; links to per-year archive sub-pages 2017-2026 (packs on media.cuh.nhs.uk). Step-1 error was transient WAF.</t>
         </is>
       </c>
     </row>
@@ -7267,13 +7267,33 @@
           <t>https://www.ruh.nhs.uk/about/trustboard/index.asp</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>RUH Bath uses a classic .asp CMS. The stored /about/trustboard/index.asp is the dates INDEX listing each Board of Directors meeting; each meeting links to a per-meeting sub-page /about/trustboard/{YYYY_MM}/index.asp whose /documents/ folder holds a single Combined_paper_pack.pdf (e.g. /about/trustboard/2026_06/documents/Combined_paper_pack.pdf for 3 June 2026). The index page itself has no inline PDFs (hence 'no papers visible' from validators) - follow the dated sub-pages. Static fetch works; prefer Combined_paper_pack.pdf over individual item PDFs. Public questions to ruh-tr.trustboard@nhs.net.</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Combined_paper_pack;Public Board of Directors;Bundle Public Board</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>RUH Bath .asp board index lists meeting dates linking to per-meeting sub-pages holding Combined_paper_pack.pdf; latest 3 June 2026 confirmed. Index has no inline PDFs (validator miss).</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9075,7 +9095,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9085,7 +9105,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Live page shows the 18 June 2026 combined papers pack (6.1MB) plus Jan/Mar/May 2026 papers and minutes; WebFetch read it successfully.</t>
+          <t>GOSH trust board meetings page live; latest 18 June 2026 'Download meeting papers' pack linked. Step-1 error was transient connection reset.</t>
         </is>
       </c>
     </row>
@@ -9300,12 +9320,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://tavistockandportman.nhs.uk/publications/?publication-types=board-papers</t>
+          <t>https://www.northlondonmentalhealth.nhs.uk/meetings-and-papers/</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Pattern C/F (per-meeting sub-pages; wrong-url-fixed). Old URL was the /about-us/our-board/ profile page which only links out and has no dated papers. New URL is the publications listing filtered to board-papers, which lists per-meeting entries 'Board papers - {Month Year}' each linking to a sub-page (e.g. /publications/board-papers-march-2026/) that holds the combined pack PDF. Most recent entries: March 2026, January 2026 (plus an Extraordinary board papers - January 2026), November 2025. IMPORTANT QUIRK: Tavistock and Portman NHS FT merged into North London NHS Foundation Trust on 1 April 2026 and this website is now archived (banner: 'This website has been archived'); historical board papers remain accessible here but future packs will move to the North London FT site. A crawler should follow the latest 'Board papers' entry to its sub-page and take the combined pack; skip 'Extraordinary' unless that is the only recent meeting.</t>
+          <t>MERGER: Tavistock and Portman NHS FT dissolved into North London NHS Foundation Trust (ODS G6V2S) on 1 April 2026; the old tavistockandportman.nhs.uk site is retired and 301-redirects to the successor homepage. URL repointed 2026-07-04 to the successor's board papers at northlondonmentalhealth.nhs.uk/meetings-and-papers/ (current packs; archive at /board-papers-archive/). NOTE: this now duplicates the North London NHS FT row (G6V2S) - this legacy Tavistock ODS code should be reconciled/removed by hand. Board meets bi-monthly; click a meeting date to open the combined agenda/papers PDF. Static fetch works.</t>
         </is>
       </c>
       <c r="J134" t="b">
@@ -9323,7 +9343,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9333,7 +9353,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Publications board-papers filter lists dated meeting sub-pages through March 2026 (site archived post-merger but papers still live).</t>
+          <t>MERGER: Tavistock &amp; Portman dissolved into North London NHS FT (ODS G6V2S) on 1 Apr 2026; old site retired (301 to successor). URL repointed to successor board papers. Duplicates row G6V2S - flag for reconciliation.</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9542,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -9532,7 +9552,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Most recent 2026/27 meetings (4 June, 2 April) each link to agenda and papers via download_file/view endpoints.</t>
+          <t>South Tyneside &amp; Sunderland board papers page live; Agenda and papers by financial year (latest 5 Feb 2026) via download_file endpoints. Validator miss was transient/WAF.</t>
         </is>
       </c>
     </row>
@@ -10980,7 +11000,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -10990,7 +11010,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Completed 2026 meetings (6 May, 4 March) each link to meeting papers via download_file/view endpoints.</t>
+          <t>Northern Care Alliance board dates &amp; papers live; meeting papers by FY (upcoming 8 July 2026) via download_file endpoints. Validator miss was transient/WAF.</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11225,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11215,7 +11235,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>2026 public board bundles (04 Feb, 01 Apr, 17 Jun) present as live large PDFs on the wwl.nhs.uk domain.</t>
+          <t>WWL /board-papers live; combined public bundles under /media/board/Papers (latest 17 June 2026). Validator PDF-detection miss.</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11818,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -11808,7 +11828,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>The /board-papers child page lists dated combined packs for May 2026, March 2026 and January 2026 via /download_file/{uuid}/368 endpoints.</t>
+          <t>West Herts board-papers archive live; per-meeting combined packs via download_file (latest July 2026). Validator weak-signal was thin static body.</t>
         </is>
       </c>
     </row>
@@ -12196,17 +12216,17 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>papers_partial</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Page lists 5 meetings for 2025 and 7 for 2024 each with a working agenda/papers download link on the trust's own domain; watch for 2026 migration to UHLG group site.</t>
+          <t>LHCH board meetings page live; per-meeting bundles (latest 23 Sept 2025). 2026 meetings moving to UHL Group site - watch for migration.</t>
         </is>
       </c>
     </row>
@@ -12271,7 +12291,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -12281,7 +12301,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Latest meeting (5 Feb 2026) on page 1 and a 12-page back-catalogue of board PDFs confirmed on the trust's own domain.</t>
+          <t>Alder Hey board papers archive live (paginated newest-first); combined PDFs under wp-content (latest 2 April 2026).</t>
         </is>
       </c>
     </row>
@@ -12969,7 +12989,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -12979,7 +12999,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>2026 monthly public board packs (Feb-Jun) present as live /download_file/ PDFs on lscft.nhs.uk.</t>
+          <t>Lancashire &amp; South Cumbria board papers live; public packs by year via opaque download_file links (latest 5 Feb 2026). Validator PDF-detection miss.</t>
         </is>
       </c>
     </row>
@@ -13168,17 +13188,17 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>JS-rendered landing hub; dated packs sit one level down via 'Agendas and Reports by Year'. Needs Playwright.</t>
+          <t>Confirmed JS-rendered hub; browser follows 'Agendas and Reports by Year'. Access notes current.</t>
         </is>
       </c>
     </row>
@@ -13292,17 +13312,17 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>JS-rendered; browser render shows dated public Trust Board packs (latest May 2026) plus the 2026-27 schedule. Needs Playwright.</t>
+          <t>Confirmed JS-rendered; dated public board packs (e.g. 'Trust Board (Public) Papers - May 2026'). Access notes current.</t>
         </is>
       </c>
     </row>
@@ -13990,17 +14010,17 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Confirmed a valid 7.5MB public board papers bundle PDF (2 April 2026) downloads from the /wp-content/uploads/ path containing 2025-2026 BAF documents.</t>
+          <t>SCAS board meetings page live (schedule to Mar 2027); paper archive table JS-rendered/invisible to static fetch - needs browser; PDFs under /wp-content/uploads.</t>
         </is>
       </c>
     </row>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -606,35 +606,35 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Current URL is live and correct but the whole sussexcommunity.nhs.uk domain sits behind a WAF (reCAPTCHA-protected) that returns HTTP 403 / 'Socket is closed' to WebFetch — Playwright IS required. Structure: the 'Board meetings and papers' landing links to a 'Board Papers' sub-page (/board-meetings-and-papers/board-papers) which lists one sub-page per meeting (/board-papers/board-paper-{dd-month-yyyy}); each meeting sub-page contains a single combined PDF served via a numbered document route /documents/{id}-{dd-month-yyyy}-board-paper (no .pdf extension). Crawl with Playwright: open board-papers index, follow each board-paper-{date} link, grab the /documents/ link. Papers retained for ~12 months only.</t>
+          <t>The current landing IS the live archive; the shallow check only failed due to an intermittent WAF (connection-reset/403 against datacenter IPs) - a browser User-Agent plus retry gets clean static HTML, no JS needed. Board packs are Joomla-style download links /documents/{id}-{slug}/file that 302 to the actual PDF; the page lists the last ~12 months with dates spanning May/June/July 2026 (bi-monthly public board). Crawl the landing, collect /documents/*/file hrefs, prefer the one slugged plainly 'board-paper-{DD-month-YYYY}' as the main pack and treat extra-descriptor siblings as supplementary. A child page /board-meetings-and-papers/board-papers also exists but the landing already surfaces the dated links.</t>
         </is>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>/board-papers/board-paper-;/documents/;-board-paper</t>
+          <t>/documents/ path;slug 'board-paper-{date}';'/file' suffix;application/pdf;large (&gt;10MB) file size</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>council-of-governors;strategies-plans;quality-account</t>
+          <t>facebook.com/sharer;mailto:;slugs with extra descriptors (strategic-improvement-report, appendix, supplementary, register-of-interests)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Landing correct but whole sussexcommunity.nhs.uk domain behind reCAPTCHA WAF (403/socket-closed to automated fetch); Playwright required.</t>
+          <t>Current URL returns HTTP 200, title 'Board Meetings and Papers | Sussex Community NHS Trust', links directly to dated 2026 board packs (e.g. board-paper-28-may-2026); shallow-check failure was an intermittent WAF connection reset.</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The meetings-in-public page is the correct QVH landing page but presents papers/minutes through two JavaScript dropdown selectors ('Meeting papers:' and 'Minutes:') going back to 2014, so plain HTTP fetch shows only labels and no hrefs — hence the earlier weak signal. Render with Playwright to expand the dropdowns, or harvest direct links via Google site:qvh.nhs.uk. Each paper entry resolves through a clean /download/meetings-in-public/{slug}/ permalink that points to a flat bundle PDF under /wp-content/uploads/YYYY/MM/ named Papers-PUBLIC-Board-{date}.pdf (sometimes -V2). Probing the /wp-content/uploads/ date path is the most reliable non-rendering route.</t>
+          <t>The landing URL is correct but the meeting list is a JS-rendered &lt;select&gt; dropdown whose options carry no hrefs in static HTML, so a plain fetch sees dates but cannot reach the PDFs - Playwright (or the onchange handler) is needed. Alternatively a crawler can hit the predictable pack pattern directly: /wp-content/uploads/YYYY/MM/Papers-PUBLIC-Board-{DD-Month-YYYY}.pdf (single combined public board pack per meeting). Prefer the 'Papers-PUBLIC-Board-...' bundle; filter out Council of Governors packs. Coverage mid-2025 to mid-2026.</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -787,27 +787,27 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>/wp-content/uploads/YYYY/MM/Papers-PUBLIC-Board-{date}.pdf;/download/meetings-in-public/{slug}/ permalink redirecting to the PDF;filenames starting 'Papers-PUBLIC-Board'</t>
+          <t>/wp-content/uploads/YYYY/MM/;filename starts 'Papers-PUBLIC-Board';contains meeting date;may end -V2;single combined bundle PDF</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>/about-us/board-of-directors/ (member bios);/for-members/public-meetings/ (members' AGM, not board);'Minutes:' dropdown when seeking full packs</t>
+          <t>Papers-PUBLIC-CoG;Council of Governors;private/confidential board;accessible-format request mailto</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>QVH meetings-in-public page live; papers behind JS dropdown selectors back to 2014 - needs browser; PDFs Papers-PUBLIC-Board-{date}.pdf under /wp-content/uploads.</t>
+          <t>The 'Meetings in public' page lists meeting dates 8 May 2025 through 9 July 2026 in a JS dropdown with no static hrefs, but the underlying public board-pack PDFs exist under /wp-content/uploads/ (14 May 2026, 12 March 2026 confirmed).</t>
         </is>
       </c>
     </row>
@@ -1592,16 +1592,42 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.nottinghamshirehealthcare.nhs.uk/board-of-directors-and-meetings</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+          <t>https://www.nottinghamshirehealthcare.nhs.uk/board-papers/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Papers live in a JS-rendered 'SharpMyBrowser' document library at /board-papers/ that static fetch cannot read (folders render but show 0-file counts; file rows load client-side). Navigation is a three-level folder tree driven by ?smbfolder=&lt;id&gt; query params: root then year folder (2024=1245, 2025=1749, 2026=1973, Archive=961) then per-meeting date sub-folder then the PDF. Each meeting sub-folder holds a single combined 'Public Board of Directors &lt;date&gt;.pdf'. The PDFs themselves are served from a stable directly-fetchable endpoint /download.cfm?doc=&lt;docid&gt;.pdf&amp;ver=&lt;n&gt; (plain GET works once discovered). Recommended crawl: Playwright to open /board-papers/, enter current-year folder, then each meeting sub-folder, collect the download.cfm link. Coverage 2024-2026 plus an Archive folder.</t>
+        </is>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>download.cfm?doc=;Public Board of Directors &lt;date&gt;.pdf;smbfolder date sub-folders</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>smba2z (A-Z index links);Integrated Performance Report indicator-definition blurb;folder count 0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Old /board-of-directors-and-meetings overview page has no paper links; live dated packs are in a JS document library at /board-papers/ (year folder then per-meeting date sub-folder), confirmed Public Board pack 28 May 2026 via browser.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2540,11 +2566,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Static fetch returns empty (JS-rendered). Browser crawler loads the page, waits for network idle, then uses a year/month dropdown (2015-2026) to pick the latest meeting; selecting a date reveals dated links incl. 'Board Meetings in Common - {date} - Combined papers' and 'Public Information Pack'. Needs Playwright.</t>
+          <t>UPDATE 2026-07-11: the listing is now server-rendered - a plain HTTP fetch returns the July 2026 pack and the full month dropdown, so Playwright is NO LONGER required. Static fetch returns empty (JS-rendered). Browser crawler loads the page, waits for network idle, then uses a year/month dropdown (2015-2026) to pick the latest meeting; selecting a date reveals dated links incl. 'Board Meetings in Common - {date} - Combined papers' and 'Public Information Pack'. Needs Playwright.</t>
         </is>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2558,17 +2584,17 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Confirmed JS-rendered (empty static body); browser crawler uses year/month dropdown 2015-2026. Access notes current.</t>
+          <t>Re-checked 2026-07-11 via Playwright then plain fetch: landing now server-rendered, July 2026 pack plus month dropdown (2015-2026) present in raw HTML; static fetch reaches the listing so Playwright no longer required.</t>
         </is>
       </c>
     </row>
@@ -2840,25 +2866,25 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Landing page is protected by an aggressive WAF/bot filter — direct WebFetch returns HTTP 403 and a headless browser gets ERR_CONNECTION_RESET, so a crawler must present a real browser User-Agent and full TLS/cookie handshake (navigate like a human) to reach the HTML. The page is a static server-rendered list of Board of Directors meetings; each meeting links directly to a combined public board pack PDF hosted under /download/clientfiles/files/. There is no year-tab JavaScript — past meetings are listed inline on the same page. Prefer the single 'Combined papers' / 'Public Trust Board' PDF per meeting date rather than individual item attachments.</t>
+          <t>The URL is correct and live; the shallow check failed only because uhcw.nhs.uk sits behind an aggressive WAF that resets connections from datacenter IPs (curl/Playwright both got ERR_CONNECTION_RESET intermittently, but the landing eventually returns 200). Content is static HTML, not JS-gated - a browser UA with a few retries suffices; Playwright not required but would harden against resets. Board packs are single combined PDFs at /download/clientfiles/files/ named 'Combined Public Trust Board Papers {date}' or 'Public Board Papers v{n} {date}_compressed'; crawl the landing and follow those download links. Coverage late-2025 through mid-2026 (roughly bi-monthly).</t>
         </is>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>/download/clientfiles/files/;Combined papers;Public Trust Board;DD-MM-YY;_compressed.pdf</t>
+          <t>/download/clientfiles/files/ path;'Public Trust Board Papers';'Public Board Papers';'Combined';'_compressed';.pdf</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>agenda-only;questions;private;confidential;council-of-governors;quality-account</t>
+          <t>confidential;private;committee;minutes-only;agenda-only</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2868,7 +2894,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Search-confirmed live 2026 pack (Combined papers Public Trust Board 02-04-26) under /download/clientfiles/files/; landing URL is the current canonical board-meetings page.</t>
+          <t>Current URL /our-organisation/trust-board-meetings/ returns HTTP 200 and is the canonical 'Trust Board Meetings' page; 2026 combined public board packs (2 April 2026, 4 June 2026) are indexed under the site's own /download/clientfiles/files/ path. Shallow-check failure was a WAF connection reset.</t>
         </is>
       </c>
     </row>
@@ -3158,12 +3184,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.combined.nhs.uk/about-us/our-board/previous-board-meetings/</t>
+          <t>https://www.combined.nhs.uk/about/our-board/board-meetings/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>The trust restructured its 'Our Board' section under /about-us/ (the old /about/our-board/board-meetings/ path still resolves but the maintained pages are now under /about-us/our-board/). The 'Upcoming Board Meetings' page holds only the next meeting's papers, while the dated archive of completed packs lives on the 'Previous Board Meetings' page (archive from Jan 2014 onward) — use that as the landing for historical packs. Pages are static WordPress and crawl cleanly; each meeting links a single combined public pack PDF under /wp-content/uploads/YYYY/MM/. Prefer the file named PUBLIC-TRUST-BOARD-PAPERS-DD.MM.YY.pdf over agenda-only or CEO-report attachments.</t>
+          <t>WordPress site; board packs are single combined PDFs under /wp-content/uploads/YYYY/MM/ named PUBLIC-TRUST-BOARD-PAPERS-DD.MM.YY.pdf (sometimes prefixed FINAL-). The board-meetings page is static HTML - crawl it and harvest wp-content/uploads/*.pdf hrefs; the newest pack sits at the top. Static fetch works with a browser UA, though an intermittent connection-reset WAF affects this domain (retry on ERR_CONNECTION_RESET). Note both /about-us/our-board/board-meetings/ and the old /previous-board-meetings/ now 404, so only the /about/ path is canonical; public board meets roughly bi-monthly with Jan/Mar/May/Jul 2026 dates present.</t>
         </is>
       </c>
       <c r="J42" t="b">
@@ -3171,17 +3197,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>/wp-content/uploads/;PUBLIC-TRUST-BOARD-PAPERS;DD.MM.YY;.pdf</t>
+          <t>/wp-content/uploads/YYYY/MM/ path;PUBLIC-TRUST-BOARD-PAPERS;FINAL- prefix;DD.MM.YY date;.pdf</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>agenda;ceo-report;annual-general-meeting;private;confidential</t>
+          <t>.webp;favicon;-150x150 / -300x300 thumbnails;committee;extraordinary;/about-us/ legacy paths (404)</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3217,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Previous-board-meetings archive confirmed live via search (PUBLIC-TRUST-BOARD-PAPERS-15.01.26.pdf present); direct/automated fetch now hits anti-bot (404/connection-reset) though page serves to browsers.</t>
+          <t>Old /about-us/our-board/previous-board-meetings/ now 404s (site migrated /about-us/ to /about/); canonical page /about/our-board/board-meetings/ links latest pack FINAL-PUBLIC-TRUST-BOARD-PAPERS-09.07.26.pdf plus 2025-2026 coverage.</t>
         </is>
       </c>
     </row>
@@ -3507,12 +3533,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.uhb.nhs.uk/about/trust-management/bod/papers/</t>
+          <t>https://docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>The current URL is correct and live (title 'Papers from meetings of the Board of Directors'), but it does NOT host PDFs inline — it contains a single 'View papers from meetings of the Board of Directors' link to an external Nextcloud document store at https://docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD. That store is a JS-rendered Nextcloud public share: WebFetch sees 'No files in here' (file list loads via XHR) yet exposes an 831.6 MB 'Download all' link, proving the folder is populated. The docs.uhb.nhs.uk host aborts headless browsers on some attempts, so harvesting individual dated PDFs requires Playwright (or the Nextcloud WebDAV/dav API) against the share token. Landing page itself needs no special handling.</t>
+          <t>The old landing page is a near-empty wrapper whose only content is one anchor to a Nextcloud document store; that is why static validators find no paper evidence. The real archive is a JS-rendered Nextcloud instance at docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD; static fetch returns 'No files in here' and requires Playwright/headless render. Navigation is folder-based: root shows year folders, append ?path=%2F%2F2026 (double-slash before year at root) or ?path=%2F2026%2FJune to descend; each recent month folder holds 2 PDFs (main pack + a 'background reading' pack). Navigate directly to current year/month rather than crawling all 18 year folders. Download via appending /download to the share (.../download?path=/2026/June&amp;files=&lt;filename&gt;).</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -3520,17 +3546,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD (Nextcloud public share token);Nextcloud share download-all: append /download to the share URL;individual files under /index.php/s/{token}/download?path=&amp;files={filename}</t>
+          <t>Board of Directors meeting pack, &lt;Month&gt; &lt;Year&gt;.pdf;filename contains 'meeting pack'</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>'No files in here' empty-state text from non-JS fetch;privacy-policy and main-site nav links</t>
+          <t>(background reading);background reading pack</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3540,7 +3566,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Landing correct; papers on external JS-rendered Nextcloud store (docs.uhb.nhs.uk) - needs browser/WebDAV, not inline PDFs.</t>
+          <t>Old uhb.nhs.uk/about/trust-management/bod/papers/ is a near-empty wrapper linking one Nextcloud share; the share holds 18 year folders (2008-2026) and 2026/June contains 'Board of Directors meeting pack, June 2026.pdf' (confirmed via browser).</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4360,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>URL is current and correct. Since the GESH group formed (St George's + Epsom &amp; St Helier), the joint 'Group Board' replaces the single-trust board, and this page is the canonical Group Board papers/agenda archive. Static WordPress; agendas published the Friday before each meeting. Each meeting date links a combined public pack PDF under /wp-content/uploads/YYYY/MM/ (filenames inconsistent — sometimes a date string, sometimes export-YYYY-MM-DD, sometimes gesh-Group-Board-public). Prefer the largest 'Group Board public' pack per date; Epsom &amp; St Helier mirror the same packs. A sibling /board-papers/ page holds legacy single-trust St George's packs.</t>
+          <t>Static fetch works fully - no JS. Papers grouped by fiscal year (2025-26, 2026-27) with each meeting date linking a single combined board-pack PDF under /wp-content/uploads/YYYY/MM/. Prefer direct .pdf links whose filename encodes the meeting date (e.g. '8-May-2026-2.pdf') or 'Group-Board-Public-{date}.pdf'; this is now a GROUP board (St George's + Epsom &amp; St Helier), so a single group-board pack per date is expected. Coverage back to early 2025. Occasional exported-bundle filenames (export-2026-...pdf) - date by the surrounding label, not the filename.</t>
         </is>
       </c>
       <c r="J59" t="b">
@@ -4342,17 +4368,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>/wp-content/uploads/;gesh;Group-Board-public;Month-YYYY;.pdf</t>
+          <t>/wp-content/uploads/;filename contains meeting date (e.g. 8-May-2026);Group-Board-Public;single large combined PDF per meeting</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>council-of-governors;private;confidential;agenda-only;part-2;minutes-only</t>
+          <t>committee/;council-of-governors;minutes-only;agenda-only single-page files</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4362,7 +4388,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>GESH Group Board papers/agenda archive live; latest 8 May 2026 pack linked. Automated fetch intermittently hits connection reset (WAF).</t>
+          <t>Page titled 'Group Board Papers and Agenda' lists dated group-board PDFs May 2025 through July 2026 as direct hyperlinks; static fetch resolves every href.</t>
         </is>
       </c>
     </row>
@@ -4855,11 +4881,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Static fetch returns empty (JS-rendered). Browser crawler sees upcoming open board dates and per-year archive links (2017-2026). Agenda and papers appear on the page at least three working days before each meeting; follow the per-year archive links for dated packs. Needs Playwright.</t>
+          <t>UPDATE 2026-07-11: static fetch now reaches the dated packs - navigate from the landing to the per-year Previous meetings subpage (e.g. /previous-meetings-2026/), which is static HTML; Playwright NO LONGER required. Static fetch returns empty (JS-rendered). Browser crawler sees upcoming open board dates and per-year archive links (2017-2026). Agenda and papers appear on the page at least three working days before each meeting; follow the per-year archive links for dated packs. Needs Playwright.</t>
         </is>
       </c>
       <c r="J66" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -4873,17 +4899,17 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Confirmed JS-rendered; browser sees open board dates + per-year archives 2017-2026. Access notes current.</t>
+          <t>Re-checked 2026-07-11: landing shows upcoming dates and links to per-year Previous meetings pages; dated 2026 packs (29 Jan, 31 Mar, 21 May 2026) live on the static /previous-meetings-2026/ subpage - target the year subpage; plain fetch reaches them so Playwright no longer required.</t>
         </is>
       </c>
     </row>
@@ -5827,7 +5853,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Current URL is correct and live (Calderdale and Huddersfield, cht.nhs.uk, TYPO3 site). Page renders server-side listing meeting dates for 2026 and prior years; each held/upcoming meeting with papers links to a single combined 'Agenda and Papers' PDF under /fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/{year}/. Filenames follow 'Combined_-_Public_Board_of_Directors_-_{Weekday}_{D}_{Month}_{YYYY}_WEBSITE.pdf'. Plain WebFetch works; no WAF/JS. Future dates show 'No papers linked' until published.</t>
+          <t>Static fetch works fully - no JS. The single landing page lists all meetings chronologically (2026 down to 2015) with each meeting linking a combined 'Agenda and Papers' PDF on the trust's own domain under /fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/{year}/. One combined pack per meeting; filenames 'Combined_-_Public_Board_of_Directors_-_Thursday_{D}_{Month}_{Year}_WEBSITE.pdf' (2025 onward). Prefer the 'Combined' file per meeting; older years also have separate 'Agenda' and 'Items for Assurance' files to filter out. Live domain is cht.nhs.uk (not chft). Coverage 2015-2026.</t>
         </is>
       </c>
       <c r="J80" t="b">
@@ -5835,17 +5861,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>/fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/{YYYY}/;Combined_-_Public_Board_of_Directors_-_{Weekday}_{D}_{Month}_{YYYY}_WEBSITE.pdf;'Agenda and Papers' / 'Combined Papers' link text per dated meeting</t>
+          <t>Combined_-_Public_Board_of_Directors;Combined_Public_Board_of_Directors;_WEBSITE.pdf;/BoardPapers/{year}/</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>meetings showing 'No papers linked';prior-year sections (2025 and earlier)</t>
+          <t>Agenda (standalone);Items_for_Assurance;Minutes</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5855,7 +5881,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Calderdale &amp; Huddersfield board dates/papers page live; combined Agenda and Papers PDFs under /fileadmin (latest shown 15 Jan 2026). Validator PDF-detection miss.</t>
+          <t>The cht.nhs.uk page renders as static HTML listing dated 'Agenda and Papers' combined PDFs from 2015 through the 2026 schedule (Jan, Mar, May, Jul, Sep, Nov), confirmed via raw hrefs.</t>
         </is>
       </c>
     </row>
@@ -7269,19 +7295,25 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>RUH Bath uses a classic .asp CMS. The stored /about/trustboard/index.asp is the dates INDEX listing each Board of Directors meeting; each meeting links to a per-meeting sub-page /about/trustboard/{YYYY_MM}/index.asp whose /documents/ folder holds a single Combined_paper_pack.pdf (e.g. /about/trustboard/2026_06/documents/Combined_paper_pack.pdf for 3 June 2026). The index page itself has no inline PDFs (hence 'no papers visible' from validators) - follow the dated sub-pages. Static fetch works; prefer Combined_paper_pack.pdf over individual item PDFs. Public questions to ruh-tr.trustboard@nhs.net.</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr"/>
+          <t>Static fetch works fully - no JS despite the old .asp CMS. The landing (index.asp) lists forthcoming and (via a dropdown back to Jan 2020) historical meetings, each linking a per-meeting sub-page at /about/trustboard/{YYYY_MM}/index.asp. That sub-page holds one combined 'Agenda &amp; Papers' PDF (also surfaced as a 'Reading Room' link to the same file), under that month folder's documents/ directory. Crawl: read index.asp for dates, follow each {YYYY_MM}/index.asp, extract the combined PDF href. Papers now branded 'BSW Hospitals Group Board PUBLIC' (RUH sits within the BSW Hospitals Group joint board) - still the RUH statutory board. Coverage Jan 2020 to present.</t>
+        </is>
+      </c>
+      <c r="J102" t="b">
+        <v>0</v>
+      </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Combined_paper_pack;Public Board of Directors;Bundle Public Board</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr"/>
+          <t>Combined Paper Pack;BSW_Hospitals_Group_Board_PUBLIC_Agenda_and_Papers;{YYYY_MM_DD}_..._Agenda_and_Papers.pdf</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Reading Room (duplicate link to same file);Minutes</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7291,7 +7323,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>RUH Bath .asp board index lists meeting dates linking to per-meeting sub-pages holding Combined_paper_pack.pdf; latest 3 June 2026 confirmed. Index has no inline PDFs (validator miss).</t>
+          <t>The legacy .asp landing renders statically, lists dated board meetings through March 2027, and each month links a per-meeting sub-page (e.g. /about/trustboard/2026_07/index.asp) carrying a single 'Combined Paper Pack' PDF.</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9556,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Current URL is live and correct; the 'no board papers visible' failure was a WAF/transient block — the page renders board papers organised by financial year (2019/20 through 2026/27). Breadcrumb: Home &gt; About us &gt; Our people &gt; Our board &gt; Board papers. PDFs are served via an indirected download endpoint /download_file/view/{uuid}/{id} rather than direct .pdf links, so link-detection must capture download_file/view hrefs, not just *.pdf. Retry WebFetch on 403; no JS rendering required.</t>
+          <t>The landing is server-rendered and lists every meeting by financial year with a single 'Agenda and papers' link per meeting. Each link is a Concrete5 download endpoint /download_file/view/{uuid}/668 (NO .pdf extension in the URL - almost certainly why the deep validator scored 'no evidence', as it filtered for .pdf). Following the endpoint serves the combined board-pack PDF. Static fetch works; no JS. Prefer the 'Agenda and papers' link per dated meeting row; coverage May 2019 through June 2026 (~50+ packs). One bundled PDF per meeting.</t>
         </is>
       </c>
       <c r="J137" t="b">
@@ -9532,17 +9564,17 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>/download_file/view/;financial-year groupings (e.g. 2026/27);agenda and papers per meeting date</t>
+          <t>/download_file/view/;'Agenda and papers';trailing /668 context id;financial-year headings (2026/27, 2025/26)</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>board-meeting-dates;executive-directors;non-executive-directors</t>
+          <t>minutes-only links (packs and minutes share the endpoint - match on 'Agenda and papers'/'papers' link text, not 'minutes')</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -9552,7 +9584,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>South Tyneside &amp; Sunderland board papers page live; Agenda and papers by financial year (latest 5 Feb 2026) via download_file endpoints. Validator miss was transient/WAF.</t>
+          <t>Static fetch returns a full financial-year-grouped archive (2026/27 back to 2019/20) with dated 'Agenda and papers' download links, e.g. 5 February 2026 and 4 December 2025.</t>
         </is>
       </c>
     </row>
@@ -10982,7 +11014,7 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Current URL is live and correct; 'no board papers visible' was a WAF/transient block. Page lists upcoming Board of Directors dates plus completed-meeting 'Meeting papers' links organised by financial year back to Sept 2021 (plus archival Committee in Common 2019-2021). PDFs use an indirected endpoint /download_file/view/{id}/{collection} rather than direct .pdf URLs, so capture download_file/view hrefs. Public sessions also have livestream/recording video links to ignore. Retry WebFetch on 403; no JS rendering required.</t>
+          <t>The current URL IS the correct live archive; the validator's 'no evidence' is a false negative from (1) the site edge intermittently returning HTTP 502 to non-browser user agents (WebFetch 502'd every attempt; Playwright loaded every time), and (2) 'papers'/'minutes' links using the extensionless endpoint /download_file/view/{id}/875 which 302-redirects to the real PDF under /application/files/{path}/YYYY-MM-DD_..._papers_pack.pdf. Content is server-rendered (links in initial DOM, no click-to-expand), so a static crawler that retries past the 502 and does not filter on .pdf will work; Playwright is the reliable fallback. Upcoming meetings carry an inline 'Meeting papers here' link; previous meetings are grouped by financial year each with 'papers' and 'minutes'. Match on 'papers' (not 'minutes'). Ignore historic Committee-in-Common (pre-Oct 2021) folders.</t>
         </is>
       </c>
       <c r="J161" t="b">
@@ -10990,17 +11022,17 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>/download_file/view/;financial-year groupings;'Meeting papers' link per completed date</t>
+          <t>/download_file/view/{id}/875;redirect target /application/files/.../*_papers_pack.pdf;link text 'papers' or 'Meeting papers here';'Part 1' / 'Public'</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>livestream;video;council-of-governors;annual-reports;quality-accounts</t>
+          <t>'minutes' links;CiC Papers 2019/2020/2021 (pre-2021 legacy);Council of Governors</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11010,7 +11042,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Northern Care Alliance board dates &amp; papers live; meeting papers by FY (upcoming 8 July 2026) via download_file endpoints. Validator miss was transient/WAF.</t>
+          <t>Browser render shows upcoming meetings (08 July 2026, 6 May 2026) with inline 'Meeting papers here' links plus financial-year accordions of previous meetings; the 08 July 2026 link resolves to a real PDF pack.</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11239,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>The old path /about-us/board-papers/ still 200s but the canonical current landing is /board-papers (title 'WWL Teaching Hospitals NHS Foundation Trust | Board Papers'). Both pages render server-side and list public meeting bundles by date under a '2026 Meetings' section, each with a 'Meeting papers' link to a single combined PDF in /media/board/Papers/{year}/. An older archive sits at /board-papers-archive. Plain WebFetch reads it fine; no WAF or JS needed. Filenames are not URL-stable; crawl by matching 'Public Bundle'/'Public meeting'/'meeting bundle' + DD.MM.YY in /media/board/Papers/2026/.</t>
+          <t>The landing is server-rendered and lists current-year board meetings, each row a date/time plus a 'Meeting papers' link pointing to a direct .pdf under /media/board/Papers/{year}/ (filenames like 'Board of Directors - Public Bundle DD.MM.YY RFS.pdf'). These are true .pdf URLs so a static fetch works with no JS; prefer the current-year page for live meetings and follow /board-papers-archive for historical years. Filter to the 'Public' bundle. Main-page coverage is the current year (2026); older years at /board-papers-archive.</t>
         </is>
       </c>
       <c r="J164" t="b">
@@ -11215,17 +11247,17 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>/media/board/Papers/{YYYY}/;Board of Directors - Public Bundle DD.MM.YY RFS.pdf;Board of Directors meeting bundle - Public meeting DD.MM.YY RFS.pdf</t>
+          <t>/media/board/Papers/2026/;'Public Bundle' / 'Public meeting';RFS.pdf;'Meeting papers'</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>/board-papers-archive (older years);upcoming meetings with agenda not yet published;Company.Secretary contact text</t>
+          <t>Confidential;Private;agenda-only documents</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11235,7 +11267,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>WWL /board-papers live; combined public bundles under /media/board/Papers (latest 17 June 2026). Validator PDF-detection miss.</t>
+          <t>Static fetch returns dated 2026 meetings each with a 'Meeting papers' link to a direct public bundle PDF (04 Feb 2026, 01 Apr 2026, 17 Jun 2026), plus a link to a separate Board Papers Archive.</t>
         </is>
       </c>
     </row>
@@ -11800,7 +11832,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Pattern C/F: the previously stored landing (/our-board/board-meetings) only describes the meeting cycle and links onward to the 'Board papers' child page, which is the real archive. The board-papers page lists per-meeting entries by month/year (May 2026, Mar 2026, Jan 2026, Nov 2025, etc.), each pointing to a single combined board-papers pack served through an opaque CMS download endpoint of the form /download_file/{uuid}/368 (no .pdf extension, UUID not date-derivable). A crawler must read the dated link text on this page to map month-&gt;download URL; there is also a 'Previous board papers' folder link for earlier years.</t>
+          <t>Static fetch works - no JS. The landing (…/our-board/board-papers) shows only the most recent meeting's pack as a direct download plus an 'Acronyms and abbreviations' glossary; older meetings live one click deeper in the 'Previous board papers' folder at /about-us/our-board/board-papers/navigate/758/9379 (2022-2026 archived). All packs are opaque GUID download URLs /download_file/{uuid}/368 with the month/year given only in the visible link text, so scrape the anchor label for dating. Prefer the single large (10-40 MB) monthly 'Board Papers' download; one combined pack per meeting.</t>
         </is>
       </c>
       <c r="J173" t="b">
@@ -11808,17 +11840,17 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>/download_file/{uuid}/368;month + year link text maps to pack;single combined board-papers pack per meeting</t>
+          <t>/download_file/{uuid}/368;link text '{Month YYYY} Board Papers';large single PDF (~10-40 MB)</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>Previous board papers (archive folder, older years)</t>
+          <t>'Acronyms and abbreviations' glossary download;/navigate/ folder links (folders not PDFs)</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -11828,7 +11860,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>West Herts board-papers archive live; per-meeting combined packs via download_file (latest July 2026). Validator weak-signal was thin static body.</t>
+          <t>Domain has NOT moved - page title 'Board papers :: West Hertfordshire Teaching Hospitals NHS Trust' on westhertshospitals.nhs.uk; landing shows latest (July 2026) pack and 'Previous board papers' folder lists monthly packs Feb 2025 to May 2026.</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12230,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Single landing page at /board-of-directors-meetings titled 'Board of Directors Meetings' listing meetings by year (2015-2025) each with a per-meeting download link. Crawl this one page and collect all hrefs matching /resources/download/lhch-*; each is a combined agenda+papers bundle for one meeting (date in adjacent link text). Note: from 2026 onward the trust joined NHS University Hospitals of Liverpool Group and 2026 board meetings are hosted off-domain on the group website (external links), so this page may stop adding new dates — watch for migration.</t>
+          <t>Static fetch works fully - no JS. The landing lists meetings by date under 'Upcoming Meetings' and year-grouped archive sections (2015-2025), each row with a 'download the papers' link. Papers are single combined packs served via the CMS download endpoint /resources/download/lhch-&lt;hash&gt; rather than named PDFs, so follow each dated row's download link. Coverage deep (2015 onward). NOTE the page also links to 'NHS University Hospitals of Liverpool Group Board Meetings' - a separate group body, not LHCH's own trust board.</t>
         </is>
       </c>
       <c r="J179" t="b">
@@ -12206,27 +12238,27 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>/resources/download/lhch-&lt;hex-id&gt;;link text contains weekday + day + month + year e.g. 'Tuesday 23rd September 2025'</t>
+          <t>/resources/download/lhch-;dated row text 'Board of Directors' + month + year;'download the papers'</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>mailto:;/resources/download/ items not labelled as board meeting papers;external group-website links (uhlg)</t>
+          <t>University Hospitals of Liverpool Group;UHLG;group board</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>LHCH board meetings page live; per-meeting bundles (latest 23 Sept 2025). 2026 meetings moving to UHL Group site - watch for migration.</t>
+          <t>Current URL is a live dated archive listing Board of Directors meetings with downloadable papers for 2025 (Jan, Mar, Apr, Jun, Sep) plus year archives back to 2015.</t>
         </is>
       </c>
     </row>
@@ -12273,7 +12305,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>WordPress publications archive filtered to the 'board-papers' type; titled 'Board papers Archives'. It is paginated (12 pages confirmed via /page/2/ .. /page/12/) and displays roughly one Trust Board meeting per page newest-first. Crawl the base URL then iterate /page/N/ to enumerate all meetings; each meeting links to a single combined agenda+documentation PDF under /wp-content/uploads/YYYY/MM/. Filenames vary ('Agenda-Documentation-Trust-Board' or 'Trust-Board-Meeting') so match on the wp-content/uploads path plus date in title rather than a fixed filename.</t>
+          <t>Static fetch works - this is a WordPress custom-post-type/taxonomy archive (publications_type/board-papers/). Each entry is a single combined board pack PDF at /wp-content/uploads/YYYY/MM/…pdf, linked with the meeting title and date. The archive surfaces only the most recent pack(s) at a time, so coverage of older meetings is thin on this view - take the newest dated entry as the current pack and re-scan after each meeting. Filenames follow 'Trust-board-meeting-&lt;day&gt;-&lt;month&gt;-&lt;year&gt;.pdf'. Packs are large (~26MB).</t>
         </is>
       </c>
       <c r="J180" t="b">
@@ -12281,17 +12313,13 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>/wp-content/uploads/{YYYY}/{MM}/*Trust-Board*.pdf;title 'Trust Board Meeting - &lt;day&gt; &lt;month&gt; &lt;year&gt;';pagination /publications_type/board-papers/page/&lt;N&gt;/</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>non-board publication types (quality reports, annual reports);mailto:</t>
-        </is>
-      </c>
+          <t>/wp-content/uploads/;Trust-board-meeting-;'Trust Board Meeting' + date;large PDF (~20MB+)</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -12301,7 +12329,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Alder Hey board papers archive live (paginated newest-first); combined PDFs under wp-content (latest 2 April 2026).</t>
+          <t>The publications_type/board-papers/ taxonomy page is live and surfaces a genuine dated board pack - 'Trust Board Meeting - 2nd April 2026' (26MB PDF), uploaded July 2026 to the trust's own domain.</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12999,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Current URL is correct and live. The page renders server-side and lists 'Public Board of Directors Meeting Papers' by date for 2026 back to 2020, grouped by year. Each entry links via an opaque numeric download endpoint /download_file/{id}/{key} (not a descriptive filename), so map packs by the visible link text (which carries the DD.MM.YY date and 'Public' label) rather than the URL. Plain WebFetch works; no WAF/JS. Crawl the 2026 block for 'Public Board of Directors Meeting Papers - DD.MM.YY' and resolve each to its /download_file/ URL.</t>
+          <t>Static fetch works fully - no JS. The landing is a self-contained archive listing dated board packs as direct download links /download_file/{id}/1439, grouped into per-year sections (2026 down to 2020) each with pagination. Read the page, take the newest-dated rows in the 2026 section, follow the download_file links (these serve the PDF directly). Titles carry the meeting date in DD.MM.YY/DD.MM.YYYY form so extract date from link text. Coverage 2020-2026.</t>
         </is>
       </c>
       <c r="J190" t="b">
@@ -12979,17 +13007,17 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>/download_file/{id}/{key} opaque download endpoint;link text: 'Public Board of Directors Meeting Papers - DD.MM.YY';link text: 'Board of Directors Public Meeting Pack - DD.MM.YY'</t>
+          <t>'Board of Directors';'Meeting Papers' / 'Meeting Pack';'Public Board';DD.MM.YYYY in title;/download_file/ path;large file size (4-14 MB)</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>years prior to current (2024/2023/2022/2021/2020 sections);'Back to Board of Directors' nav link</t>
+          <t>Part 2;private;confidential;Council of Governors;AGM;committee;minutes-only</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -12999,7 +13027,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Lancashire &amp; South Cumbria board papers live; public packs by year via opaque download_file links (latest 5 Feb 2026). Validator PDF-detection miss.</t>
+          <t>Static fetch lists dated board packs for Feb-Jul 2026 (e.g. 'Board of Directors Meeting Papers - 02.07.2026.pdf') plus year archives back to 2020.</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13216,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -13198,7 +13226,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Confirmed JS-rendered hub; browser follows 'Agendas and Reports by Year'. Access notes current.</t>
+          <t>Re-checked 2026-07-11 via Playwright: same Agendas-and-Reports-by-Year JS document library; must click the 2026/27 Meetings folder to reveal dated packs (02.07.26, 04.06.26, 07.05.26 seen); plain fetch of the folder URL returns empty, so Playwright genuinely required.</t>
         </is>
       </c>
     </row>
@@ -13294,11 +13322,11 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Static fetch returns empty (JS-rendered). Browser crawler sees dated public board packs ('Trust Board (Public) Papers - May 2026', etc.) plus upcoming dates. PDFs may flag accessibility warnings but the pack links are present. Needs Playwright.</t>
+          <t>UPDATE 2026-07-11: packs are listed inline on the main board-meetings page and a plain HTTP fetch returns them, so Playwright is NO LONGER required. Static fetch returns empty (JS-rendered). Browser crawler sees dated public board packs ('Trust Board (Public) Papers - May 2026', etc.) plus upcoming dates. PDFs may flag accessibility warnings but the pack links are present. Needs Playwright.</t>
         </is>
       </c>
       <c r="J195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -13312,17 +13340,17 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Confirmed JS-rendered; dated public board packs (e.g. 'Trust Board (Public) Papers - May 2026'). Access notes current.</t>
+          <t>Re-checked 2026-07-11: dated packs listed inline on the main board-meetings page (Trust Board Papers (Public) - July 2026.pdf etc.); plain fetch returns the same list so Playwright no longer required.</t>
         </is>
       </c>
     </row>
@@ -13987,12 +14015,12 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://www.scas.nhs.uk/about-scas/our-board/board-meetings/</t>
+          <t>https://www.scas.nhs.uk/about-scas/our-board/</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>The /about-scas/our-board/board-meetings/ landing page lists the meeting schedule and a 'Board paper archive' table, but the archive table and paper links are rendered by JavaScript and invisible to plain HTTP fetch (only the meeting dates and a contact email show). To get actual papers, crawl the dedicated WordPress document-category archive at /document-category/board-papers/ and the per-meeting announcement pages (e.g. /board-meeting-in-public-3-september-2026/), which link to bundle PDFs; both are also JS-driven so use Playwright or harvest direct PDF URLs from Google site:scas.nhs.uk. Final PDFs are flat files under /wp-content/uploads/YYYY/MM/ named SCAS...Board-papers_DDMMYYYY.pdf, so a path/date probe works without rendering. Papers publish shortly before each meeting.</t>
+          <t>The old board-meetings path redirects to /about-scas/our-board/, which should be the tracked URL. That page holds a jQuery DataTables 'Board paper archive' whose rows load via a client-side AJAX call, so a static fetch sees an empty table body ('No matching documents') - Playwright is required, and you must wait ~3-5s for the table to populate before scraping. Each populated row's link points to a direct PDF under /wp-content/uploads/YYYY/MM/... with the meeting date in the row title (DD Mon YYYY). Prefer the main 'SCAS public Board papers - &lt;date&gt;' rows; bi-monthly, so ~6 packs/year. Coverage 2025-2026 on the live table (older on request from company.secretary@scas.nhs.uk).</t>
         </is>
       </c>
       <c r="J205" t="b">
@@ -14000,17 +14028,17 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>/wp-content/uploads/YYYY/MM/SCAS...Board-papers_DDMMYYYY.pdf;/wp-content/uploads/ filename containing 'Board-papers';per-meeting pages at /board-meeting-in-public-{date}/;document-category/board-papers/ archive listing</t>
+          <t>SCAS public Board papers;Public-Board-Papers;wp-content/uploads/YYYY/MM/ path;date in title;~7-17 MB file size</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>/about-scas/our-board/scas-board-members/;/registers-of-interests/;/council-of-governors/;/news/</t>
+          <t>Supporting / SupportingInformation;Council of Governors / CoG;Joint Committee;Terms of Reference;Nominations/Remuneration/Audit Committee;Constitution</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14020,7 +14048,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>SCAS board meetings page live (schedule to Mar 2027); paper archive table JS-rendered/invisible to static fetch - needs browser; PDFs under /wp-content/uploads.</t>
+          <t>Old /board-meetings/ 301-redirects to /about-scas/our-board/, whose 'Board paper archive' DataTable is empty on static fetch but populates via AJAX to 25 rows once JS runs (SCAS public Board papers 3 June 2026, 2 April 2026, 5 Feb 2026 confirmed).</t>
         </is>
       </c>
     </row>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -779,25 +779,25 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The landing URL is correct but the meeting list is a JS-rendered &lt;select&gt; dropdown whose options carry no hrefs in static HTML, so a plain fetch sees dates but cannot reach the PDFs - Playwright (or the onchange handler) is needed. Alternatively a crawler can hit the predictable pack pattern directly: /wp-content/uploads/YYYY/MM/Papers-PUBLIC-Board-{DD-Month-YYYY}.pdf (single combined public board pack per meeting). Prefer the 'Papers-PUBLIC-Board-...' bundle; filter out Council of Governors packs. Coverage mid-2025 to mid-2026.</t>
+          <t>The live landing /about-us/board-of-directors/meetings-in-public/ lists one entry per meeting ('Meeting papers: &lt;date&gt;') as sub-pages, newest first, spanning 2025 and 2026 in a single flat list (no per-year archives). Each sub-page links to the single combined public board pack PDF. Packs also live at a predictable direct path www.qvh.nhs.uk/wp-content/uploads/YYYY/MM/Papers-PUBLIC-Board-&lt;...&gt;.pdf, so a crawler can grab those directly. WebFetch renders the full meeting list statically, so Playwright is not required; prefer the one large combined 'Papers-PUBLIC-Board' PDF per meeting and skip individual annexes.</t>
         </is>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>/wp-content/uploads/YYYY/MM/;filename starts 'Papers-PUBLIC-Board';contains meeting date;may end -V2;single combined bundle PDF</t>
+          <t>Papers-PUBLIC-Board;PUBLIC Board &lt;month&gt; &lt;year&gt;;Bundle Public Board</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Papers-PUBLIC-CoG;Council of Governors;private/confidential board;accessible-format request mailto</t>
+          <t>Q&amp;A;Observer note;FOI;Minutes only;Agenda only;private/confidential board</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>The 'Meetings in public' page lists meeting dates 8 May 2025 through 9 July 2026 in a JS dropdown with no static hrefs, but the underlying public board-pack PDFs exist under /wp-content/uploads/ (14 May 2026, 12 March 2026 confirmed).</t>
+          <t>Landing lists per-meeting pages through 23 July 2026; direct combined-pack PDFs for May 2026, Feb 2026 and Dec 2025 confirmed on the org domain.</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>UPDATE 2026-07-11: the listing is now server-rendered - a plain HTTP fetch returns the July 2026 pack and the full month dropdown, so Playwright is NO LONGER required. Static fetch returns empty (JS-rendered). Browser crawler loads the page, waits for network idle, then uses a year/month dropdown (2015-2026) to pick the latest meeting; selecting a date reveals dated links incl. 'Board Meetings in Common - {date} - Combined papers' and 'Public Information Pack'. Needs Playwright.</t>
+          <t>Despite the prior needs_playwright flag, the current board pack renders server-side and is reachable by a plain static fetch: the landing shows the latest 'Board in Common' set (agenda, meeting papers, public information pack) as direct PDF links. What static fetch misses is only the historical archive: older meetings (2015 onward) are selected via a JavaScript dropdown/postback that swaps the visible links, so Playwright is only needed to enumerate prior years -- load the page, select a year, wait for the link list to re-render, then harvest the /content/doclib/&lt;id&gt;.pdf links. The most recent packs need no JS.</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -2574,17 +2574,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Combined papers;Public Information Pack;Board Meetings in Common;Public Agenda</t>
+          <t>/content/doclib/&lt;number&gt;.pdf;'Board in Common' agenda / meeting papers / public information pack triplet;year dropdown selector for archive</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Private Agenda;Confidential;Part 2</t>
+          <t>public questions / submission-procedure text;governance boilerplate</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Re-checked 2026-07-11 via Playwright then plain fetch: landing now server-rendered, July 2026 pack plus month dropdown (2015-2026) present in raw HTML; static fetch reaches the listing so Playwright no longer required.</t>
+          <t>Latest July 2026 Board in Common pack (agenda + papers + info pack) present as direct PDFs on the static page.</t>
         </is>
       </c>
     </row>
@@ -3184,30 +3184,30 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.combined.nhs.uk/about/our-board/board-meetings/</t>
+          <t>https://www.combined.nhs.uk/about-us/our-board/previous-board-meetings/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>WordPress site; board packs are single combined PDFs under /wp-content/uploads/YYYY/MM/ named PUBLIC-TRUST-BOARD-PAPERS-DD.MM.YY.pdf (sometimes prefixed FINAL-). The board-meetings page is static HTML - crawl it and harvest wp-content/uploads/*.pdf hrefs; the newest pack sits at the top. Static fetch works with a browser UA, though an intermittent connection-reset WAF affects this domain (retry on ERR_CONNECTION_RESET). Note both /about-us/our-board/board-meetings/ and the old /previous-board-meetings/ now 404, so only the /about/ path is canonical; public board meets roughly bi-monthly with Jan/Mar/May/Jul 2026 dates present.</t>
+          <t>The old /about/our-board/board-meetings/ path moved to the /about-us/ tree. /about-us/our-board/board-meetings/ lists UPCOMING dates; /about-us/our-board/previous-board-meetings/ is the dated-pack ARCHIVE (papers from Jan 2014 onward), linking to per-meeting board-pack PDFs. Packs are single combined PDFs under wp-content/uploads/YYYY/MM/ named PUBLIC-TRUST-BOARD-PAPERS-DD.MM.YY.pdf or FINAL-...; some served via WP File Download (/wpfd_file/&lt;slug&gt;/). CRITICAL: the whole www.combined.nhs.uk origin resets the TCP connection (ERR_CONNECTION_RESET) for direct fetch, WebFetch AND headless Playwright from datacenter IPs -- a WAF block, not a moved page. Needs a residential/browser fetch; prefer deriving month PDFs from the wp-content/uploads/YYYY/MM/ pattern when the page can't render.</t>
         </is>
       </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>/wp-content/uploads/YYYY/MM/ path;PUBLIC-TRUST-BOARD-PAPERS;FINAL- prefix;DD.MM.YY date;.pdf</t>
+          <t>PUBLIC TRUST BOARD PAPERS;FINAL PUBLIC TRUST BOARD PAPERS;DD.MM.YY date in filename</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>.webp;favicon;-150x150 / -300x300 thumbnails;committee;extraordinary;/about-us/ legacy paths (404)</t>
+          <t>Ask the Board archive;Annual General Meetings;FOI publication scheme;confidential/private board papers;video recording links</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Old /about-us/our-board/previous-board-meetings/ now 404s (site migrated /about-us/ to /about/); canonical page /about/our-board/board-meetings/ links latest pack FINAL-PUBLIC-TRUST-BOARD-PAPERS-09.07.26.pdf plus 2025-2026 coverage.</t>
+          <t>Live 2026 board packs (15 Jan 2026, 9 Jul 2026) confirmed via search-indexed PDF URLs on the org domain; origin WAF-blocks automated fetching.</t>
         </is>
       </c>
     </row>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>The old landing page is a near-empty wrapper whose only content is one anchor to a Nextcloud document store; that is why static validators find no paper evidence. The real archive is a JS-rendered Nextcloud instance at docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD; static fetch returns 'No files in here' and requires Playwright/headless render. Navigation is folder-based: root shows year folders, append ?path=%2F%2F2026 (double-slash before year at root) or ?path=%2F2026%2FJune to descend; each recent month folder holds 2 PDFs (main pack + a 'background reading' pack). Navigate directly to current year/month rather than crawling all 18 year folders. Download via appending /download to the share (.../download?path=/2026/June&amp;files=&lt;filename&gt;).</t>
+          <t>The human landing www.uhb.nhs.uk/about/trust-management/bod/papers/ links to the Nextcloud public share at docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD. The share is JS-rendered (static fetch shows 'No files in here' -- the no_papers_visible false-negative), so Playwright is required. Navigate via ?path= query params: root lists year folders (2008-2026); each year has month folders; each month contains 'Board of Directors meeting pack, &lt;Month&gt; &lt;Year&gt;.pdf' plus sometimes a '(background reading)' variant. Direct deep-links work, e.g. ?path=%2F2026%2FJune. PDFs download via /download?path=...&amp;files=... .</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -3546,27 +3546,27 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Board of Directors meeting pack, &lt;Month&gt; &lt;Year&gt;.pdf;filename contains 'meeting pack'</t>
+          <t>Board of Directors meeting pack, &lt;Month&gt; &lt;Year&gt;;(background reading) variant PDF;Year folder &gt; Month folder structure</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>(background reading);background reading pack</t>
+          <t>register of board members interests;terms of appointment;council of governors;'No files in here' static-render placeholder</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Old uhb.nhs.uk/about/trust-management/bod/papers/ is a near-empty wrapper linking one Nextcloud share; the share holds 18 year folders (2008-2026) and 2026/June contains 'Board of Directors meeting pack, June 2026.pdf' (confirmed via browser).</t>
+          <t>Playwright enumeration confirmed 2026 month folders each containing dated 'Board of Directors meeting pack' PDFs (e.g. June 2026).</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>UPDATE 2026-07-11: static fetch now reaches the dated packs - navigate from the landing to the per-year Previous meetings subpage (e.g. /previous-meetings-2026/), which is static HTML; Playwright NO LONGER required. Static fetch returns empty (JS-rendered). Browser crawler sees upcoming open board dates and per-year archive links (2017-2026). Agenda and papers appear on the page at least three working days before each meeting; follow the per-year archive links for dated packs. Needs Playwright.</t>
+          <t>The board-papers landing /our-trust/bod-meetings/ renders server-side (no JS required): it lists upcoming public board meetings plus 'Previous meetings' links grouped by year (2017-2026). Individual board packs are single combined 'boardbook' PDFs under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler does not need Playwright for the landing page; follow the per-year 'previous meetings' links (or hit the wp-content/uploads path pattern directly) to reach dated packs. Static fetch reaches the index but the actual dated PDFs sit one click deeper on the year sub-pages.</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -4889,17 +4889,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>agenda and papers;open board;combined</t>
+          <t>/wp-content/uploads/&lt;yyyy&gt;/&lt;mm&gt;/*Boardbook*.pdf;filenames like 'public-BOD-25.9.25-FINAL-Boardbook.pdf','open-BOD-boardbook-31.3.26.pdf';'Previous meetings' year links</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>confidential;private;Part B</t>
+          <t>Council of Governors packs;confirmed minutes PDFs (not the board pack);bthft.nhs.uk contact/email links</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Re-checked 2026-07-11: landing shows upcoming dates and links to per-year Previous meetings pages; dated 2026 packs (29 Jan, 31 Mar, 21 May 2026) live on the static /previous-meetings-2026/ subpage - target the year subpage; plain fetch reaches them so Playwright no longer required.</t>
+          <t>Landing confirmed on own domain with 2025 and 2026 boardbook PDFs (Sep 2025, Mar 2026).</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5853,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Static fetch works fully - no JS. The single landing page lists all meetings chronologically (2026 down to 2015) with each meeting linking a combined 'Agenda and Papers' PDF on the trust's own domain under /fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/{year}/. One combined pack per meeting; filenames 'Combined_-_Public_Board_of_Directors_-_Thursday_{D}_{Month}_{Year}_WEBSITE.pdf' (2025 onward). Prefer the 'Combined' file per meeting; older years also have separate 'Agenda' and 'Items for Assurance' files to filter out. Live domain is cht.nhs.uk (not chft). Coverage 2015-2026.</t>
+          <t>Static server-rendered TYPO3 page; no Playwright needed. Upcoming-meeting table at top lists each 2026 Board of Directors meeting with a direct 'Agenda and Papers' link to a single combined PDF (visible in raw HTML). Past years (2025 back to 2015) sit in collapsed 'Show+' accordions that expand client-side; to enumerate historic packs click the year header or derive from the folder pattern. Prefer this /publications/ landing over the /about-us/board-of-directors bio page. PDF pattern: /fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/&lt;YEAR&gt;/Combined_-_Public_Board_of_Directors_-_&lt;Weekday&gt;_&lt;D&gt;_&lt;Month&gt;_&lt;YYYY&gt;_WEBSITE.pdf</t>
         </is>
       </c>
       <c r="J80" t="b">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Combined_-_Public_Board_of_Directors;Combined_Public_Board_of_Directors;_WEBSITE.pdf;/BoardPapers/{year}/</t>
+          <t>One combined PDF per meeting (agenda+papers merged);Filenames use underscores, often end _WEBSITE.pdf</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Agenda (standalone);Items_for_Assurance;Minutes</t>
+          <t>/about-us/board-of-directors (director bios);pre-2020 BoardPapers/BOD_2017/;Annual Reports under Publications/Annual_Reports/</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>The cht.nhs.uk page renders as static HTML listing dated 'Agenda and Papers' combined PDFs from 2015 through the 2026 schedule (Jan, Mar, May, Jul, Sep, Nov), confirmed via raw hrefs.</t>
+          <t>2026 meetings table links directly to combined board-pack PDFs; May 2026, July 2026, March 2025 all return HTTP 200 application/pdf.</t>
         </is>
       </c>
     </row>
@@ -6698,25 +6698,25 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Landing page is live but WebFetch hits a WAF/anti-bot block (socket closed); use Playwright/headless browser. The landing page itself holds no PDFs — it links to per-year archive sub-pages via a sidebar (2017-2026). Open the current year page /about-us/board-directors/board-of-directors-meetings/{YEAR}-board-of-directors-meetings/ which lists each meeting as an EVENT link (e.g. /events/board-of-directors-meeting-10-june-2026/); the full board pack PDF is inside the event page, served from the media.cuh.nhs.uk/documents/ subdomain. Alternatively Google site:media.cuh.nhs.uk Full_Pack to find packs directly.</t>
+          <t>The current landing URL is correct; the ERR_CONNECTION_RESET on direct fetch and Playwright is a WAF/anti-bot block, not a moved page -- WebFetch (different infra) reaches it fine, so prefer plain static fetch/WebFetch and skip headless Playwright (also reset). The landing is an index of year links (2017-2026); no PDFs on it. Drill down: index -&gt; year page (e.g. /2026-board-of-directors-meetings/) lists meeting dates -&gt; each links to an /events/board-of-directors-meeting-DD-month-YYYY/ page -&gt; that event page holds the single 'Meeting papers' full-pack PDF. A scan must follow two hops.</t>
         </is>
       </c>
       <c r="J93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>media.cuh.nhs.uk/documents/Board_of_Directors_-_Full_Pack_{D}_{Month}_{YYYY}.pdf;media.cuh.nhs.uk/documents/*Full_Pack*.pdf;/events/board-of-directors-meeting-{day}-{month}-{year}/</t>
+          <t>year sub-pages /board-of-directors-meetings/{YYYY}-board-of-directors-meetings/;event pages /events/board-of-directors-meeting-{DD}-{month}-{YYYY}/;'Full Pack' / 'Meeting papers' labels;meetings ~quarterly (Mar, Jun, Sep, Dec)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>/2017-;/2018-;/2019-;/2020-;/2021-;/2022-;/2023-;statement-of-purpose;council-of-governors</t>
+          <t>Google cache / Wayback / news domains;/council-governors-meetings;director profile pages;annual report and accounts PDFs</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>CUH board meetings page live; links to per-year archive sub-pages 2017-2026 (packs on media.cuh.nhs.uk). Step-1 error was transient WAF.</t>
+          <t>Confirmed a 2026 full board pack plus two 2025 packs via index-&gt;year-&gt;event drill-down on cuh.nhs.uk / media.cuh.nhs.uk.</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Static fetch works fully - no JS despite the old .asp CMS. The landing (index.asp) lists forthcoming and (via a dropdown back to Jan 2020) historical meetings, each linking a per-meeting sub-page at /about/trustboard/{YYYY_MM}/index.asp. That sub-page holds one combined 'Agenda &amp; Papers' PDF (also surfaced as a 'Reading Room' link to the same file), under that month folder's documents/ directory. Crawl: read index.asp for dates, follow each {YYYY_MM}/index.asp, extract the combined PDF href. Papers now branded 'BSW Hospitals Group Board PUBLIC' (RUH sits within the BSW Hospitals Group joint board) - still the RUH statutory board. Coverage Jan 2020 to present.</t>
+          <t>Legacy ASP CMS but fully live and current. The landing /about/trustboard/index.asp lists forthcoming meetings and a month dropdown (Jan 2020 through the latest 2026 meeting). Each meeting has its own month page /about/trustboard/YYYY_MM/index.asp linking a single combined PDF at /about/trustboard/YYYY_MM/documents/Combined_paper_pack.pdf. All pages render statically -- no Playwright. To find the newest pack, read the landing for the latest YYYY_MM then hit that month's Combined_paper_pack.pdf. Papers carry a press embargo until after the meeting.</t>
         </is>
       </c>
       <c r="J102" t="b">
@@ -7303,17 +7303,17 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Combined Paper Pack;BSW_Hospitals_Group_Board_PUBLIC_Agenda_and_Papers;{YYYY_MM_DD}_..._Agenda_and_Papers.pdf</t>
+          <t>/about/trustboard/YYYY_MM/index.asp per-meeting page;/about/trustboard/YYYY_MM/documents/Combined_paper_pack.pdf single combined pack;month dropdown enumerates all meetings</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Reading Room (duplicate link to same file);Minutes</t>
+          <t>/about/trustboard/Archive/ (pre-2020);BSW Group Board packs on gwh.nhs.uk;pdffiller.com and other aggregator copies</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>The legacy .asp landing renders statically, lists dated board meetings through March 2027, and each month links a per-meeting sub-page (e.g. /about/trustboard/2026_07/index.asp) carrying a single 'Combined Paper Pack' PDF.</t>
+          <t>Landing lists meetings to July 2026; 2026_06 Combined_paper_pack.pdf downloaded as a valid 8.6MB PDF.</t>
         </is>
       </c>
     </row>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>The landing is server-rendered and lists every meeting by financial year with a single 'Agenda and papers' link per meeting. Each link is a Concrete5 download endpoint /download_file/view/{uuid}/668 (NO .pdf extension in the URL - almost certainly why the deep validator scored 'no evidence', as it filtered for .pdf). Following the endpoint serves the combined board-pack PDF. Static fetch works; no JS. Prefer the 'Agenda and papers' link per dated meeting row; coverage May 2019 through June 2026 (~50+ packs). One bundled PDF per meeting.</t>
+          <t>Static HTML page, no Playwright and no 403. Full archive grouped by fiscal year (2026/27 back to 2019/20); each meeting date links directly to a single combined agenda-and-papers PDF via the trust's /download_file/view/&lt;uuid&gt;/668 handler. WebFetch renders fine; prefer plain static fetch. Separate legacy governor/predecessor-trust pages (South Tyneside STFT, Sunderland CHSFT) under /meeting-times-agendas-and-papers are council-of-governors, not the main Board -- skip.</t>
         </is>
       </c>
       <c r="J137" t="b">
@@ -9564,17 +9564,17 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>/download_file/view/;'Agenda and papers';trailing /668 context id;financial-year headings (2026/27, 2025/26)</t>
+          <t>Board meetings bimonthly, first-of-alternate-months;Each date links to one combined PDF /download_file/view/&lt;uuid&gt;/668;download_file suffix /668 is the board-papers collection id</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>minutes-only links (packs and minutes share the endpoint - match on 'Agenda and papers'/'papers' link text, not 'minutes')</t>
+          <t>/meeting-times-agendas-and-papers/south-tyneside (legacy STFT);sunderland legacy CHSFT governor pages;council-of-governors pages</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Static fetch returns a full financial-year-grouped archive (2026/27 back to 2019/20) with dated 'Agenda and papers' download links, e.g. 5 February 2026 and 4 December 2025.</t>
+          <t>Archive lists board packs from 3 April 2025 through 4 June 2026; one confirmed as a 7.3MB PDF pack.</t>
         </is>
       </c>
     </row>
@@ -10346,13 +10346,39 @@
           <t>https://www.fhft.nhs.uk/about-us/how-we-are-run/trust-board</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>The URL is valid, but the near-empty body is NOT client-side JS -- the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to non-human traffic. Plain static fetch returns the challenge shell (empty), and headless Playwright is ALSO blocked (snapshot shows only the Imperva hCaptcha iframe). A standard Playwright crawler cannot reach the packs; it needs a captcha-solving/residential session or an allowlisted IP. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk).</t>
+        </is>
+      </c>
+      <c r="J149" t="b">
+        <v>1</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings;'Previous meetings' archive by year</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>frimley.icb.nhs.uk (the ICB, not the acute trust);Imperva/hCaptcha challenge shell</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>needs_playwright</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Landing URL confirmed live and correct, but board packs are hidden behind an Imperva/hCaptcha wall that blocks both static fetch and headless Playwright.</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -11014,25 +11040,25 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>The current URL IS the correct live archive; the validator's 'no evidence' is a false negative from (1) the site edge intermittently returning HTTP 502 to non-browser user agents (WebFetch 502'd every attempt; Playwright loaded every time), and (2) 'papers'/'minutes' links using the extensionless endpoint /download_file/view/{id}/875 which 302-redirects to the real PDF under /application/files/{path}/YYYY-MM-DD_..._papers_pack.pdf. Content is server-rendered (links in initial DOM, no click-to-expand), so a static crawler that retries past the 502 and does not filter on .pdf will work; Playwright is the reliable fallback. Upcoming meetings carry an inline 'Meeting papers here' link; previous meetings are grouped by financial year each with 'papers' and 'minutes'. Match on 'papers' (not 'minutes'). Ignore historic Committee-in-Common (pre-Oct 2021) folders.</t>
+          <t>The DB URL is correct and live (title 'Board Dates and Papers :: Northern Care Alliance'). Upcoming/recent packs appear as direct 'Meeting papers here' links under 'Watch the Board of Directors Meetings', using a /download_file/view/&lt;id&gt;/875 pattern (single combined PDF pack). Older packs live inside JS-collapsible year-range accordions that must be clicked to expand, plus a document-library table for pre-2021. WebFetch returned HTTP 502 (bot-block), while Playwright rendered cleanly -- prefer Playwright; expand year accordions for historical packs.</t>
         </is>
       </c>
       <c r="J161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>/download_file/view/{id}/875;redirect target /application/files/.../*_papers_pack.pdf;link text 'papers' or 'Meeting papers here';'Part 1' / 'Public'</t>
+          <t>/download_file/view/&lt;fileID&gt;/875 links labelled 'Meeting papers here';listed under 'Watch the Board of Directors Meetings' with date + livestream;year-range accordions e.g. 'Board of Directors - April 2025 - March 2026'</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>'minutes' links;CiC Papers 2019/2020/2021 (pre-2021 legacy);Council of Governors</t>
+          <t>youtu.be/ livestream links;mailto: addresses;/navigate/19297/&lt;id&gt; CiC pre-2021 folders;?occurrenceID= calendar permalinks</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11042,7 +11068,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Browser render shows upcoming meetings (08 July 2026, 6 May 2026) with inline 'Meeting papers here' links plus financial-year accordions of previous meetings; the 08 July 2026 link resolves to a real PDF pack.</t>
+          <t>Two 2026 board packs confirmed as direct PDF links (08 Jul 2026, 06 May 2026).</t>
         </is>
       </c>
     </row>
@@ -11239,7 +11265,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>The landing is server-rendered and lists current-year board meetings, each row a date/time plus a 'Meeting papers' link pointing to a direct .pdf under /media/board/Papers/{year}/ (filenames like 'Board of Directors - Public Bundle DD.MM.YY RFS.pdf'). These are true .pdf URLs so a static fetch works with no JS; prefer the current-year page for live meetings and follow /board-papers-archive for historical years. Filter to the 'Public' bundle. Main-page coverage is the current year (2026); older years at /board-papers-archive.</t>
+          <t>Static HTML landing on the org domain; WebFetch renders fully, no Playwright. Lists Board of Directors public meetings grouped by year, each dated meeting exposing a 'Meeting papers' link to a single combined PDF bundle under /media/board/Papers/&lt;year&gt;/. Upcoming meetings appear without links until the bundle is published. An archive section links prior years. Prefer WebFetch then follow the media PDF hrefs directly.</t>
         </is>
       </c>
       <c r="J164" t="b">
@@ -11247,17 +11273,17 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>/media/board/Papers/2026/;'Public Bundle' / 'Public meeting';RFS.pdf;'Meeting papers'</t>
+          <t>/media/board/Papers/&lt;YYYY&gt;/ path;filename contains 'Board of Directors' + 'Public' + DD.MM.YY + 'RFS';single combined bundle PDF per meeting</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Confidential;Private;agenda-only documents</t>
+          <t>/media/corporate/Trust Reports/ (annual reports);pre-2020 archive under /2019/;upcoming dates without a linked PDF</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11267,7 +11293,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Static fetch returns dated 2026 meetings each with a 'Meeting papers' link to a direct public bundle PDF (04 Feb 2026, 01 Apr 2026, 17 Jun 2026), plus a link to a separate Board Papers Archive.</t>
+          <t>Landing lists 2026 meetings (04 Feb, 01 Apr, 17 Jun) each with a working combined PDF bundle plus an archive link.</t>
         </is>
       </c>
     </row>
@@ -11832,7 +11858,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Static fetch works - no JS. The landing (…/our-board/board-papers) shows only the most recent meeting's pack as a direct download plus an 'Acronyms and abbreviations' glossary; older meetings live one click deeper in the 'Previous board papers' folder at /about-us/our-board/board-papers/navigate/758/9379 (2022-2026 archived). All packs are opaque GUID download URLs /download_file/{uuid}/368 with the month/year given only in the visible link text, so scrape the anchor label for dating. Prefer the single large (10-40 MB) monthly 'Board Papers' download; one combined pack per meeting.</t>
+          <t>Static HTML, renders fine via plain fetch -- no Playwright. The landing shows the current/latest month's combined board pack (currently 'July 2026 Board Papers') plus an acronyms glossary. Older meetings sit under a 'Previous board papers' folder at /about-us/our-board/board-papers/navigate/758/9379, one combined PDF per meeting (bi-monthly) back to 2022. Each pack is a single large combined PDF (20MB+) served from an opaque /download_file/&lt;uuid&gt;/368 URL with no dated filename -- this opacity is why the validator saw weak evidence. Prefer the landing for the newest pack and the navigate/758/9379 folder for the dated archive.</t>
         </is>
       </c>
       <c r="J173" t="b">
@@ -11840,17 +11866,17 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>/download_file/{uuid}/368;link text '{Month YYYY} Board Papers';large single PDF (~10-40 MB)</t>
+          <t>'&lt;Month&gt; &lt;Year&gt; Board Papers' link text on landing;download_file URLs /download_file/&lt;uuid&gt;/368;single combined PDF per meeting (~20MB);'Previous board papers' folder /navigate/758/9379</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>'Acronyms and abbreviations' glossary download;/navigate/ folder links (folders not PDFs)</t>
+          <t>/about-us/news/ pages;/about-us/foi;legacy /about/board_meetings/*/default.asp;acronyms glossary download</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -11860,7 +11886,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Domain has NOT moved - page title 'Board papers :: West Hertfordshire Teaching Hospitals NHS Trust' on westhertshospitals.nhs.uk; landing shows latest (July 2026) pack and 'Previous board papers' folder lists monthly packs Feb 2025 to May 2026.</t>
+          <t>Landing serves the current combined board pack and links a dated archive folder with confirmed 2025-2026 packs.</t>
         </is>
       </c>
     </row>
@@ -12230,7 +12256,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Static fetch works fully - no JS. The landing lists meetings by date under 'Upcoming Meetings' and year-grouped archive sections (2015-2025), each row with a 'download the papers' link. Papers are single combined packs served via the CMS download endpoint /resources/download/lhch-&lt;hash&gt; rather than named PDFs, so follow each dated row's download link. Coverage deep (2015 onward). NOTE the page also links to 'NHS University Hospitals of Liverpool Group Board Meetings' - a separate group body, not LHCH's own trust board.</t>
+          <t>Static HTML -- no Playwright; WebFetch retrieves the full dated links list. Live archive landing: lists each 2025 meeting date each linking a single combined agenda+papers PDF, plus collapsible year archive sections back to 2015 (2024 and earlier under /about-lhch/our-board-of-directors/board-of-directors-meetings-YYYY). Board packs served from opaque /resources/download/lhch-&lt;hash&gt; URLs with no .pdf extension or date -- this is why the validator saw weak evidence. Prefer this page as entry point; skip /about-lhch/our-board-of-directors/ (membership only).</t>
         </is>
       </c>
       <c r="J179" t="b">
@@ -12238,17 +12264,17 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>/resources/download/lhch-;dated row text 'Board of Directors' + month + year;'download the papers'</t>
+          <t>Board pack PDFs from /resources/download/lhch-&lt;hex-hash&gt; (no .pdf, no date);One combined PDF per meeting date; large files (&gt;10MB);Meeting dates rendered as static HTML text</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>University Hospitals of Liverpool Group;UHLG;group board</t>
+          <t>uhliverpool.nhs.uk (group parent, not RBQ's own archive);/about-lhch/our-board-of-directors/ (membership only);/governor-meetings (Council of Governors)</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -12258,7 +12284,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Current URL is a live dated archive listing Board of Directors meetings with downloadable papers for 2025 (Jan, Mar, Apr, Jun, Sep) plus year archives back to 2015.</t>
+          <t>Landing lists five 2025 dated board packs with working links; most recent confirmed 23 September 2025 (&gt;10MB download).</t>
         </is>
       </c>
     </row>
@@ -12305,7 +12331,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Static fetch works - this is a WordPress custom-post-type/taxonomy archive (publications_type/board-papers/). Each entry is a single combined board pack PDF at /wp-content/uploads/YYYY/MM/…pdf, linked with the meeting title and date. The archive surfaces only the most recent pack(s) at a time, so coverage of older meetings is thin on this view - take the newest dated entry as the current pack and re-scan after each meeting. Filenames follow 'Trust-board-meeting-&lt;day&gt;-&lt;month&gt;-&lt;year&gt;.pdf'. Packs are large (~26MB).</t>
+          <t>Live WordPress publications_type archive, statically readable via WebFetch (no Playwright, no 403). Landing lists the most recent Trust Board pack (currently 2 April 2026) and paginates via /publications_type/board-papers/page/N/ (currently 12 pages, ~one pack per page reverse-chronological). Each entry links directly to a single combined agenda+papers PDF under /wp-content/uploads/YYYY/MM/. Prefer the landing for the newest pack; walk /page/2/ etc. for older meetings.</t>
         </is>
       </c>
       <c r="J180" t="b">
@@ -12313,13 +12339,17 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>/wp-content/uploads/;Trust-board-meeting-;'Trust Board Meeting' + date;large PDF (~20MB+)</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr"/>
+          <t>heading 'Trust Board Meeting - &lt;day month year&gt;';filenames contain 'Trust-Board'/'Agenda-Documentation-Trust-Board' often 'Website-Version';PDFs at /wp-content/uploads/YYYY/MM/;large single combined PDFs (18-26MB)</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>/about/trust/board/meeting/ (informational only);/about/trust/board/ overview;legacy Concrete5 publications listing;FOI disclosure-log PDFs</t>
+        </is>
+      </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -12329,7 +12359,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>The publications_type/board-papers/ taxonomy page is live and surfaces a genuine dated board pack - 'Trust Board Meeting - 2nd April 2026' (26MB PDF), uploaded July 2026 to the trust's own domain.</t>
+          <t>Landing shows the live 2 April 2026 pack and paginates (Page 1 of 12) to older dated packs, all on the org domain.</t>
         </is>
       </c>
     </row>
@@ -12999,7 +13029,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Static fetch works fully - no JS. The landing is a self-contained archive listing dated board packs as direct download links /download_file/{id}/1439, grouped into per-year sections (2026 down to 2020) each with pagination. Read the page, take the newest-dated rows in the 2026 section, follow the download_file links (these serve the PDF directly). Titles carry the meeting date in DD.MM.YY/DD.MM.YYYY form so extract date from link text. Coverage 2020-2026.</t>
+          <t>Static HTML archive titled 'Board papers' under the Board of Directors section; rendered fully via plain WebFetch, no Playwright. Packs listed newest-first with dated labels (e.g. 'Board of Directors Meeting Papers - 02.07.2026'), each linking a single combined meeting-pack PDF via numeric /download_file/&lt;id&gt;/1439. Prefer fetching the listing then following the numeric download_file links; skip register-of-interests, council-of-governors and publication-scheme pages.</t>
         </is>
       </c>
       <c r="J190" t="b">
@@ -13007,17 +13037,17 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>'Board of Directors';'Meeting Papers' / 'Meeting Pack';'Public Board';DD.MM.YYYY in title;/download_file/ path;large file size (4-14 MB)</t>
+          <t>Label 'Board of Directors ... Meeting Papers/Pack - DD.MM.YYYY';PDF hrefs /download_file/&lt;id&gt;/1439;monthly public board cadence, first Thursday;packs are large single PDFs (4-20MB)</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Part 2;private;confidential;Council of Governors;AGM;committee;minutes-only</t>
+          <t>/board-directors-register-interests;/Council-Governors;/publications-reports-policies/;/corporate-registers</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13027,7 +13057,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Static fetch lists dated board packs for Feb-Jul 2026 (e.g. 'Board of Directors Meeting Papers - 02.07.2026.pdf') plus year archives back to 2020.</t>
+          <t>Landing lists dated 2025-2026 board packs each linking a PDF; a sampled 2026 link returned a &gt;10MB PDF.</t>
         </is>
       </c>
     </row>
@@ -13198,7 +13228,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Static fetch returns empty (JS-rendered). This is a landing/hub page; browser crawler follows 'Agendas and Reports by Year' (/about-us/meet-board/board-meetings-public/previous-meetings-year) for dated agendas/reports and 'Calendar of Meetings' for the schedule. Dated packs live one level down. Needs Playwright.</t>
+          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering. Both static fetch and headless Playwright receive the hCaptcha 'Additional security check is required' interstitial rather than page content, so a normal Playwright crawler cannot reach the packs without captcha bypass/allowlisting. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page -- the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path.</t>
         </is>
       </c>
       <c r="J193" t="b">
@@ -13206,17 +13236,17 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>Agendas and Reports;agenda;papers;reports</t>
+          <t>.../board-meetings-public/previous-meetings-year (agendas &amp; reports by year);.../board-meetings-public/upcoming-meetings (calendar)</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>confidential;private;Part 2</t>
+          <t>bfwh.nhs.uk parallel/legacy pages;Imperva/hCaptcha challenge shell</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -13226,7 +13256,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Re-checked 2026-07-11 via Playwright: same Agendas-and-Reports-by-Year JS document library; must click the 2026/27 Meetings folder to reveal dated packs (02.07.26, 04.06.26, 07.05.26 seen); plain fetch of the folder URL returns empty, so Playwright genuinely required.</t>
+          <t>Landing URL confirmed live and correct, but content is gated by an Imperva/hCaptcha wall that defeats both static fetch and headless Playwright.</t>
         </is>
       </c>
     </row>
@@ -13322,35 +13352,35 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>UPDATE 2026-07-11: packs are listed inline on the main board-meetings page and a plain HTTP fetch returns them, so Playwright is NO LONGER required. Static fetch returns empty (JS-rendered). Browser crawler sees dated public board packs ('Trust Board (Public) Papers - May 2026', etc.) plus upcoming dates. PDFs may flag accessibility warnings but the pack links are present. Needs Playwright.</t>
+          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content. Static fetch and headless Playwright both hit the hCaptcha 'Additional security check is required' interstitial, so a standard Playwright crawler is blocked without captcha-solving or IP allowlisting. Once past the wall, the page lists scheduled board meetings (e.g. 12 Nov 2025, 14 Jan 2026, 11 Mar 2026 in the Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs from the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf'). Accessible versions via TrustBoardQuestions@elht.nhs.uk.</t>
         </is>
       </c>
       <c r="J195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Trust Board (Public) Papers;Trust Board (Public Session) Papers;Agenda and Papers;Open Session Papers</t>
+          <t>/application/files/**/Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf;meeting dates 12 Nov 2025 / 14 Jan 2026 / 11 Mar 2026</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Private Session;confidential;Part 2;Closed</t>
+          <t>yumpu.com mirrored copies;TrustBoardQuestions@ contact link;Imperva/hCaptcha challenge shell</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Re-checked 2026-07-11: dated packs listed inline on the main board-meetings page (Trust Board Papers (Public) - July 2026.pdf etc.); plain fetch returns the same list so Playwright no longer required.</t>
+          <t>Landing URL confirmed live and correct, but packs sit behind an Imperva/hCaptcha wall blocking both static fetch and headless Playwright.</t>
         </is>
       </c>
     </row>
@@ -14020,7 +14050,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>The old board-meetings path redirects to /about-scas/our-board/, which should be the tracked URL. That page holds a jQuery DataTables 'Board paper archive' whose rows load via a client-side AJAX call, so a static fetch sees an empty table body ('No matching documents') - Playwright is required, and you must wait ~3-5s for the table to populate before scraping. Each populated row's link points to a direct PDF under /wp-content/uploads/YYYY/MM/... with the meeting date in the row title (DD Mon YYYY). Prefer the main 'SCAS public Board papers - &lt;date&gt;' rows; bi-monthly, so ~6 packs/year. Coverage 2025-2026 on the live table (older on request from company.secretary@scas.nhs.uk).</t>
+          <t>The DB URL is correct -- the full board-paper archive lives inline on /about-scas/our-board/, not a separate papers page. Papers are inside JS-rendered accordion/tab sections ('Board papers - financial year 2026/27' and 'Board paper archive'), so a static fetch returns the shell with zero PDF links (the no_papers_visible cause). Rendering with a headless browser exposes ~25 dated public-board PDFs under /wp-content/uploads/. Prefer Playwright on this page; scrape a[href] ending .pdf under /wp-content/uploads/YYYY/MM/. The /document-category/board-papers/ taxonomy page renders empty -- skip it. Meetings bi-monthly; each pack a single large combined PDF, occasionally a separate 'Supporting' PDF.</t>
         </is>
       </c>
       <c r="J205" t="b">
@@ -14028,27 +14058,27 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>SCAS public Board papers;Public-Board-Papers;wp-content/uploads/YYYY/MM/ path;date in title;~7-17 MB file size</t>
+          <t>PDFs at /wp-content/uploads/YYYY/MM/;filename contains 'Board-Papers'/'Board-Meeting' plus a date (e.g. _03062026, _5Feb2026, 27Nov2025);occasional 'Supporting' companion file;meetings ~every 2 months</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>Supporting / SupportingInformation;Council of Governors / CoG;Joint Committee;Terms of Reference;Nominations/Remuneration/Audit Committee;Constitution</t>
+          <t>committee Terms of Reference PDFs (Audit/Remuneration/Nominations/QualitySafety/FinancePerformance/PeopleCulture/CharitableFunds ToR);SCAS-Constitution.pdf;registers-of-interests pages;/document-category/board-papers/ (renders no listing)</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Old /board-meetings/ 301-redirects to /about-scas/our-board/, whose 'Board paper archive' DataTable is empty on static fetch but populates via AJAX to 25 rows once JS runs (SCAS public Board papers 3 June 2026, 2 April 2026, 5 Feb 2026 confirmed).</t>
+          <t>Playwright rendering of /about-scas/our-board/ surfaced ~25 dated public board-pack PDFs incl. multiple 2025-2026 packs; static fetch shows none.</t>
         </is>
       </c>
     </row>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -797,7 +797,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Landing lists per-meeting pages through 23 July 2026; direct combined-pack PDFs for May 2026, Feb 2026 and Dec 2025 confirmed on the org domain.</t>
+          <t>Per-meeting sub-pages live and current: 'Meeting papers: 23 July 2026' newest, back through 9 July, 14 May, 12 March and 12 February 2026.</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Latest July 2026 Board in Common pack (agenda + papers + info pack) present as direct PDFs on the static page.</t>
+          <t>Static fetch reaches the listing: July 2026 'Board in Common' agenda, meeting papers and public information pack all present as direct PDFs, with a dropdown back to 2015. The scanner's near-empty body is an anti-bot response, not JS rendering.</t>
         </is>
       </c>
     </row>
@@ -3184,30 +3184,30 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.combined.nhs.uk/about-us/our-board/previous-board-meetings/</t>
+          <t>https://www.combined.nhs.uk/about/our-board/board-meetings/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>The old /about/our-board/board-meetings/ path moved to the /about-us/ tree. /about-us/our-board/board-meetings/ lists UPCOMING dates; /about-us/our-board/previous-board-meetings/ is the dated-pack ARCHIVE (papers from Jan 2014 onward), linking to per-meeting board-pack PDFs. Packs are single combined PDFs under wp-content/uploads/YYYY/MM/ named PUBLIC-TRUST-BOARD-PAPERS-DD.MM.YY.pdf or FINAL-...; some served via WP File Download (/wpfd_file/&lt;slug&gt;/). CRITICAL: the whole www.combined.nhs.uk origin resets the TCP connection (ERR_CONNECTION_RESET) for direct fetch, WebFetch AND headless Playwright from datacenter IPs -- a WAF block, not a moved page. Needs a residential/browser fetch; prefer deriving month PDFs from the wp-content/uploads/YYYY/MM/ pattern when the page can't render.</t>
+          <t>URL PATCHED 2026-07-30: the site dropped the /about-us/ prefix in favour of /about/, so the old /about-us/our-board/previous-board-meetings/ path now genuinely 404s (reproduced independently, not a WAF artefact - Google still surfaces the dead /about-us/ URLs, so ignore stale search hits). Strategy: the landing /about/our-board/board-meetings/ lists UPCOMING dates (papers appear the Friday before) plus the ~11 most recent past meetings; the full back-catalogue from 2014 is one long page at /about/our-board/board-meetings/board-meeting-archive/. Each past meeting is its own page at /board-meeting-archive/trust-board-meeting-&lt;month&gt;-&lt;year&gt;/ with a 'Meeting downloads' block - but DO NOT construct those slugs, they are inconsistent (March 2026 is trust-board-meeting-march_2026 with an underscore; May 2023 carries a -2 suffix). Scrape hrefs instead. IMPORTANT: on the two most recent meeting pages the Elementor PDF buttons render with NO href attribute at all, so a link-scraper finds zero PDFs for the newest meetings; the reliable route is the WordPress REST media API at /wp-json/wp/v2/media?search=PUBLIC-TRUST-BOARD&amp;per_page=100&amp;orderby=date&amp;order=desc&amp;_fields=source_url,date. Server-rendered WordPress, no JS needed, but the edge resets TLS connections on roughly 60-90% of attempts (ECONNRESET / curl exit 35) and WebFetch fails every time; use a browser User-Agent with a 10-15 attempt retry loop, or the r.jina.ai reader proxy as a fallback. Upload folder does not match meeting month (Jan and Mar 2026 briefings both sit under /uploads/2026/04/). Bi-monthly cadence: Jan, Mar, May, Jul, Sep, Nov, second Thursday.</t>
         </is>
       </c>
       <c r="J42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>PUBLIC TRUST BOARD PAPERS;FINAL PUBLIC TRUST BOARD PAPERS;DD.MM.YY date in filename</t>
+          <t>PUBLIC TRUST BOARD PAPERS;PUBLIC TRUST BOARD PACK;FINAL- prefix;Full meeting agenda and papers;DD.MM.YY date suffix</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Ask the Board archive;Annual General Meetings;FOI publication scheme;confidential/private board papers;video recording links</t>
+          <t>CEO written board report;Chair report;Trust Board Briefing;superseded -V1 where a -V2 exists;OPEN TRUST BOARD (pre-2020 naming)</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Live 2026 board packs (15 Jan 2026, 9 Jul 2026) confirmed via search-indexed PDF URLs on the org domain; origin WAF-blocks automated fetching.</t>
+          <t>Old /about-us/ path confirmed HTTP 404; new /about/our-board/board-meetings/ returns 200 (title 'Board meetings - North Staffordshire Combined Healthcare NHS Trust') linking July, May and March 2026 archive pages, with 2026 pack PDFs verified via the WordPress media API.</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Playwright enumeration confirmed 2026 month folders each containing dated 'Board of Directors meeting pack' PDFs (e.g. June 2026).</t>
+          <t>Human landing uhb.nhs.uk/about/trust-management/bod/papers/ re-confirmed as still pointing at the docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD Nextcloud share; the share itself remains JS-rendered so static scans see nothing.</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Landing confirmed on own domain with 2025 and 2026 boardbook PDFs (Sep 2025, Mar 2026).</t>
+          <t>Static fetch reaches the listing: 23 July 2026 boardbook linked (Public-BOD-23.7.26-Boardbook-v1.pdf) with Sep and Nov 2026 dates pending papers. The scanner's near-empty body is an anti-bot response, not JS rendering.</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026 meetings table links directly to combined board-pack PDFs; May 2026, July 2026, March 2025 all return HTTP 200 application/pdf.</t>
+          <t>2026 meetings table live with 'Agenda and Papers' links through 9 July 2026; Sep and Nov 2026 dates listed pending papers.</t>
         </is>
       </c>
     </row>
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="J99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Confirmed HTTP-200 dated 2026 PDFs (13 Jan 2026 group board pack, Nov 2025, May 2026), though the landing page itself was down in a site-wide outage at scan time.</t>
+          <t>Landing renders statically this week (last month's site-wide outage has cleared); 12 May 2026 group board agenda-and-papers PDF linked, with Sep and Nov 2026 dates scheduled.</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Landing lists meetings to July 2026; 2026_06 Combined_paper_pack.pdf downloaded as a valid 8.6MB PDF.</t>
+          <t>Legacy ASP landing live; 2 July 2026 meeting listed with an 'Agenda &amp; Papers' link at /about/trustboard/2026_07/, forward dates through March 2027.</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>GOSH trust board meetings page live; latest 18 June 2026 'Download meeting papers' pack linked. Step-1 error was transient connection reset.</t>
+          <t>Landing live; 'Download meeting papers July 2026' (10.3MB) and June 2026 (6.1MB) packs listed. Scan-time connection reset was transient anti-bot behaviour.</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Archive lists board packs from 3 April 2025 through 4 June 2026; one confirmed as a 7.3MB PDF pack.</t>
+          <t>Archive live and grouped by fiscal year; 4 June 2026 and 2 April 2026 'Agenda and papers' packs present.</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Landing URL confirmed live and correct, but board packs are hidden behind an Imperva/hCaptcha wall that blocks both static fetch and headless Playwright.</t>
+          <t>Re-probed 2026-07-30: fhft.nhs.uk still returns a 212-byte Imperva/Incapsula _Incapsula_Resource interstitial to every automated request, browser User-Agent included, so neither static fetch nor headless Playwright reaches the board-paper listing. The landing URL itself remains correct.</t>
         </is>
       </c>
     </row>
@@ -11040,25 +11040,25 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>The DB URL is correct and live (title 'Board Dates and Papers :: Northern Care Alliance'). Upcoming/recent packs appear as direct 'Meeting papers here' links under 'Watch the Board of Directors Meetings', using a /download_file/view/&lt;id&gt;/875 pattern (single combined PDF pack). Older packs live inside JS-collapsible year-range accordions that must be clicked to expand, plus a document-library table for pre-2021. WebFetch returned HTTP 502 (bot-block), while Playwright rendered cleanly -- prefer Playwright; expand year accordions for historical packs.</t>
+          <t>The DB URL is correct and the page is one of the better-maintained board archives (every meeting back to September 2021 with papers, approved minutes and recordings, all inline on one server-rendered Concrete5 page - zero hops, no Playwright). CRITICAL FETCH QUIRK confirmed 2026-07-30: the edge serves a synthetic HTTP 502 to the ClaudeBot User-Agent on every path, while curl, python-requests, Googlebot, Chrome and a no-UA request all get 200. If you see a 502 here it is a User-Agent denylist, not an outage - retry with a browser User-Agent. Structure: 'Upcoming Board Meeting Dates' is BARE TEXT not links (a link-only scraper sees nothing there - parse body text); 'Watch the Board of Directors Meetings' carries the one or two newest meetings; 'Previous Board of Directors meetings' is reverse-chronological under financial-year headings. Paper links are /download_file/view/{fileID}/875 and 303-redirect to /application/files/{4}/{4}/{4}/{Name}.pdf, so follow redirects to recover the filename. Do NOT infer recency from file ID - old minutes get re-uploaded under new IDs. THE TRAP: the document-library block at the page foot (/navigate/19297/28xx) holds only legacy 2019-2021 Committee-in-Common folders, so a validator parsing only that block concludes the page is stale; the live content sits in free-text paragraphs above it. Note robots.txt disallows /download_file/* and /application/files/* with crawl-delay 20. Papers appear the Friday before each meeting. One pack PDF plus a separate, later-published minutes PDF per meeting; 'Part 1' denotes the public session.</t>
         </is>
       </c>
       <c r="J161" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>/download_file/view/&lt;fileID&gt;/875 links labelled 'Meeting papers here';listed under 'Watch the Board of Directors Meetings' with date + livestream;year-range accordions e.g. 'Board of Directors - April 2025 - March 2026'</t>
+          <t>Board of Directors Papers;Meeting Papers;papers pack;Part 1 papers pack;Download the meeting papers</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>youtu.be/ livestream links;mailto: addresses;/navigate/19297/&lt;id&gt; CiC pre-2021 folders;?occurrenceID= calendar permalinks</t>
+          <t>approved minutes;Committee in Common (legacy 2019-2021 folders);watch the meeting video links</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Two 2026 board packs confirmed as direct PDF links (08 Jul 2026, 06 May 2026).</t>
+          <t>Page confirmed live via a non-ClaudeBot User-Agent; 8 Jul 2026 (18.6MB), 6 May 2026, 4 Mar 2026 and 14 Jan 2026 packs all verified HTTP 200 application/pdf. The 502 the scanner sees is a ClaudeBot-specific UA block.</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Landing lists 2026 meetings (04 Feb, 01 Apr, 17 Jun) each with a working combined PDF bundle plus an archive link.</t>
+          <t>Landing live listing 2026 meetings (04 Feb, 01 Apr, 17 Jun) each with a 'Meeting papers' link; Aug, Oct and Dec 2026 pending publication.</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Landing serves the current combined board pack and links a dated archive folder with confirmed 2025-2026 packs.</t>
+          <t>Landing live serving the current 'July 2026 Board Papers' pack (21MB) plus the 'Previous board papers' archive folder.</t>
         </is>
       </c>
     </row>
@@ -12251,12 +12251,12 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://www.lhch.nhs.uk/board-of-directors-meetings</t>
+          <t>https://www.uhliverpool.nhs.uk/about-us/meet-our-board/trust-board-meetings</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Static HTML -- no Playwright; WebFetch retrieves the full dated links list. Live archive landing: lists each 2025 meeting date each linking a single combined agenda+papers PDF, plus collapsible year archive sections back to 2015 (2024 and earlier under /about-lhch/our-board-of-directors/board-of-directors-meetings-YYYY). Board packs served from opaque /resources/download/lhch-&lt;hash&gt; URLs with no .pdf extension or date -- this is why the validator saw weak evidence. Prefer this page as entry point; skip /about-lhch/our-board-of-directors/ (membership only).</t>
+          <t>URL PATCHED 2026-07-30: LHCH joined the NHS University Hospitals of Liverpool Group in October 2025 and no longer holds its own board in public - the old lhch.nhs.uk/board-of-directors-meetings page is now a historic archive whose own dated packs stop at 23 September 2025 and which links out to the group board for 2026. The live board is the single UHLG Group Board covering LUHFT, LWH and LHCH (it meets in the LHCH conference room and carries LHCH's integrated performance report), so RBQ now shares this URL with REM and REP - dedupe logic must tolerate three ODS codes on one landing, and pack analysis should be attributed to all three. Strategy: the landing holds a 'Board papers' document-library table of YEAR FOLDERS - 2026 at /navigate/4487/21268, 2025 at /navigate/4487/15006, 2024 at /navigate/4487/9744, plus legacy 'LUHFT archive' (17796) and 'LWH archive' (17800). Inside a year folder, collect /download_file/{id}/423 anchors titled 'UHLG Board of Directors Public Pack - {date}'; those URLs carry no date and no .pdf extension and 303-redirect before serving, so take the date from the anchor text and follow redirects. Future meetings appear as event pages under /about-us/events/details?occurrenceID=... . Contrary to the older REM/REP notes the year folders are NOT JS-rendered - plain curl with a Chrome User-Agent returns fully server-rendered HTML containing every download_file anchor; the only obstacle is a User-Agent WAF that 403s WebFetch and default agents, so Playwright is optional. Bi-monthly: Jan, Mar, May, Jul, Sep, Nov.</t>
         </is>
       </c>
       <c r="J179" t="b">
@@ -12264,17 +12264,17 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Board pack PDFs from /resources/download/lhch-&lt;hex-hash&gt; (no .pdf, no date);One combined PDF per meeting date; large files (&gt;10MB);Meeting dates rendered as static HTML text</t>
+          <t>UHLG Board of Directors Public Pack;Public Meeting Pack;Public Pack;Meeting Pack plus date</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>uhliverpool.nhs.uk (group parent, not RBQ's own archive);/about-lhch/our-board-of-directors/ (membership only);/governor-meetings (Council of Governors)</t>
+          <t>Jargon Buster Guide;Questions to the UHLG Board of Directors;Public Consent Pack;Assurance and Risk Committee;superseded V1 where a V2 exists</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="O179" t="inlineStr">
         <is>
-          <t>Landing lists five 2025 dated board packs with working links; most recent confirmed 23 September 2025 (&gt;10MB download).</t>
+          <t>Group board landing confirmed HTTP 200 (title 'Group Board meetings :: NHS University Hospitals of Liverpool Group'); 16 Jul 2026, 14 May 2026, 12 Mar 2026 and 15 Jan 2026 UHLG public packs verified as live PDFs, the July pack agenda naming LHCH explicitly.</t>
         </is>
       </c>
     </row>
@@ -12349,7 +12349,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Landing shows the live 2 April 2026 pack and paginates (Page 1 of 12) to older dated packs, all on the org domain.</t>
+          <t>WordPress archive live; latest pack is 'Trust Board Meeting - 2nd April 2026' (26MB, uploaded July 2026) with pagination to older packs. The ~3-month publication lag is the trust's own cadence, not a URL fault.</t>
         </is>
       </c>
     </row>
@@ -13047,7 +13047,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Landing lists dated 2025-2026 board packs each linking a PDF; a sampled 2026 link returned a &gt;10MB PDF.</t>
+          <t>Landing live with six dated 2026 packs through 'Board of Directors Meeting Papers - 02.07.2026.pdf'.</t>
         </is>
       </c>
     </row>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Landing URL confirmed live and correct, but content is gated by an Imperva/hCaptcha wall that defeats both static fetch and headless Playwright.</t>
+          <t>Re-probed 2026-07-30: blackpoolteachinghospitals.nhs.uk still returns a 212-byte Imperva/Incapsula _Incapsula_Resource interstitial to every automated request, browser User-Agent included, so neither static fetch nor headless Playwright reaches the board-paper listing. The landing URL itself remains correct.</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13370,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Landing URL confirmed live and correct, but packs sit behind an Imperva/hCaptcha wall blocking both static fetch and headless Playwright.</t>
+          <t>Re-probed 2026-07-30: elht.nhs.uk still returns a 212-byte Imperva/Incapsula _Incapsula_Resource interstitial to every automated request, browser User-Agent included, so neither static fetch nor headless Playwright reaches the board-paper listing. The landing URL itself remains correct.</t>
         </is>
       </c>
     </row>
@@ -14050,7 +14050,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>The DB URL is correct -- the full board-paper archive lives inline on /about-scas/our-board/, not a separate papers page. Papers are inside JS-rendered accordion/tab sections ('Board papers - financial year 2026/27' and 'Board paper archive'), so a static fetch returns the shell with zero PDF links (the no_papers_visible cause). Rendering with a headless browser exposes ~25 dated public-board PDFs under /wp-content/uploads/. Prefer Playwright on this page; scrape a[href] ending .pdf under /wp-content/uploads/YYYY/MM/. The /document-category/board-papers/ taxonomy page renders empty -- skip it. Meetings bi-monthly; each pack a single large combined PDF, occasionally a separate 'Supporting' PDF.</t>
+          <t>The DB URL is correct - the full board-paper archive lives inline on /about-scas/our-board/ (and on the byte-identical alias /about-scas/our-board/board-meetings/), not on a separate papers page; /about-scas/our-board/board-papers/ is a 404. The paper tables are Document Library Pro widgets running serverSide:true, so rows are fetched by AJAX and have NEVER existed in the HTML source - a static fetch legitimately sees empty tables plus a 'papers will be published shortly before each meeting' note. That note is long-standing boilerplate, NOT a sign the trust has stopped publishing (verified 2026-07-30 against Wayback snapshots from June 2025, February 2026 and June 2026, none of which carried PDF links either). You do NOT need a browser: scrape the table ids matching id="dlp_&lt;hash&gt;_&lt;n&gt;" from the page HTML, then POST to /wp-admin/admin-ajax.php with action=dlp_load_posts&amp;table_id=&lt;id&gt;&amp;draw=1&amp;start=0&amp;length=100 - no nonce, cookie or referer required - and regex href="([^"]+)" out of the returned DataTables JSON 'link' field. Current map: _1 = current financial year (empty between meetings, by design), _2 = the 25-document archive spanning January 2023 to 3 June 2026, _3 = constitution and committee terms of reference. Do NOT hardcode the table id hashes - they change whenever an editor edits the block. The WordPress REST media API is closed (401). No WAF. Bi-monthly public board; packs move from _1 into _2 after each meeting.</t>
         </is>
       </c>
       <c r="J205" t="b">
@@ -14058,17 +14058,17 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>PDFs at /wp-content/uploads/YYYY/MM/;filename contains 'Board-Papers'/'Board-Meeting' plus a date (e.g. _03062026, _5Feb2026, 27Nov2025);occasional 'Supporting' companion file;meetings ~every 2 months</t>
+          <t>SCAS Public Board Papers plus date;Trust BoD in Public meeting papers;public Board papers</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>committee Terms of Reference PDFs (Audit/Remuneration/Nominations/QualitySafety/FinancePerformance/PeopleCulture/CharitableFunds ToR);SCAS-Constitution.pdf;registers-of-interests pages;/document-category/board-papers/ (renders no listing)</t>
+          <t>Supporting papers annex;constitution and committee terms of reference (table _3);superseded duplicate uploads of the same meeting</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Playwright rendering of /about-scas/our-board/ surfaced ~25 dated public board-pack PDFs incl. multiple 2025-2026 packs; static fetch shows none.</t>
+          <t>Archive confirmed intact (25 documents, January 2023 to 3 June 2026) via the plugin's admin-ajax endpoint; 3 Jun 2026 (17.5MB), 2 Apr 2026, 5 Feb 2026 and 27 Nov 2025 packs all HTTP 200. The empty static tables are AJAX rendering, not withdrawal of papers.</t>
         </is>
       </c>
     </row>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The current landing IS the live archive; the shallow check only failed due to an intermittent WAF (connection-reset/403 against datacenter IPs) - a browser User-Agent plus retry gets clean static HTML, no JS needed. Board packs are Joomla-style download links /documents/{id}-{slug}/file that 302 to the actual PDF; the page lists the last ~12 months with dates spanning May/June/July 2026 (bi-monthly public board). Crawl the landing, collect /documents/*/file hrefs, prefer the one slugged plainly 'board-paper-{DD-month-YYYY}' as the main pack and treat extra-descriptor siblings as supplementary. A child page /board-meetings-and-papers/board-papers also exists but the landing already surfaces the dated links.</t>
+          <t>The current landing IS the live archive; the shallow check only failed due to an intermittent WAF (connection-reset/403 against datacenter IPs) - a browser User-Agent plus retry gets clean static HTML, no JS needed. Board packs are Joomla-style download links /documents/{id}-{slug}/file that 302 to the actual PDF; the page lists the last ~12 months with dates spanning May/June/July 2026 (bi-monthly public board). Crawl the landing, collect /documents/*/file hrefs, prefer the one slugged plainly 'board-paper-{DD-month-YYYY}' as the main pack and treat extra-descriptor siblings as supplementary. A child page /board-meetings-and-papers/board-papers also exists but the landing already surfaces the dated links. ACCESS ROUTE (re-checked 2026-08-01): browser-UA curl from Dave's machine reaches the page (HTTP 200, 47KB of static HTML) while server-side WebFetch was refused 403 and the scanner's plain/Playwright fetches were connection-reset -- so retry with a browser User-Agent rather than treating a reset or a 403 as a dead URL.</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -624,7 +624,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Current URL returns HTTP 200, title 'Board Meetings and Papers | Sussex Community NHS Trust', links directly to dated 2026 board packs (e.g. board-paper-28-may-2026); shallow-check failure was an intermittent WAF connection reset.</t>
+          <t>Re-verified 2026-08-01: plain curl with a browser User-Agent returns HTTP 200 and the landing lists the current pack 'Board paper 30th July 2026' (/documents/512-board-paper-30th-july-2026) plus a /board-papers sub-page. Server-side WebFetch was refused 403 on this run and the scanner saw a connection reset, so the block is route-specific, not a dead page.</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Per-meeting sub-pages live and current: 'Meeting papers: 23 July 2026' newest, back through 9 July, 14 May, 12 March and 12 February 2026.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: 'Meetings in public' lists 'Meeting papers: 23 July 2026' and '9 July 2026' newest-first plus forward dates to March 2027. The papers_partial classification is a false negative -- packs sit one hop down on the per-meeting sub-pages, so the landing itself carries no dated PDF links.</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Two 2026 agenda-paper PDFs (21 April, 17 February) linked directly plus an archive link.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: 'Meetings in public' lists 2026 packs (21 April, 17 February) and forward dates 18 Aug, 15 Sep (AGM), 20 Oct, 15 Dec 2026. The scanner's connection reset is a WAF artefact on the local path only.</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Static fetch reaches the listing: July 2026 'Board in Common' agenda, meeting papers and public information pack all present as direct PDFs, with a dropdown back to 2015. The scanner's near-empty body is an anti-bot response, not JS rendering.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: the July 2026 'Board in Common' set is present as three direct PDFs (content/doclib/14558-14560.pdf: agenda, meeting papers, public information pack) with the year dropdown back ~5 years. Static fetch reaches the current pack; Playwright is only needed to enumerate the historic archive.</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>URL PATCHED 2026-07-30: the site dropped the /about-us/ prefix in favour of /about/, so the old /about-us/our-board/previous-board-meetings/ path now genuinely 404s (reproduced independently, not a WAF artefact - Google still surfaces the dead /about-us/ URLs, so ignore stale search hits). Strategy: the landing /about/our-board/board-meetings/ lists UPCOMING dates (papers appear the Friday before) plus the ~11 most recent past meetings; the full back-catalogue from 2014 is one long page at /about/our-board/board-meetings/board-meeting-archive/. Each past meeting is its own page at /board-meeting-archive/trust-board-meeting-&lt;month&gt;-&lt;year&gt;/ with a 'Meeting downloads' block - but DO NOT construct those slugs, they are inconsistent (March 2026 is trust-board-meeting-march_2026 with an underscore; May 2023 carries a -2 suffix). Scrape hrefs instead. IMPORTANT: on the two most recent meeting pages the Elementor PDF buttons render with NO href attribute at all, so a link-scraper finds zero PDFs for the newest meetings; the reliable route is the WordPress REST media API at /wp-json/wp/v2/media?search=PUBLIC-TRUST-BOARD&amp;per_page=100&amp;orderby=date&amp;order=desc&amp;_fields=source_url,date. Server-rendered WordPress, no JS needed, but the edge resets TLS connections on roughly 60-90% of attempts (ECONNRESET / curl exit 35) and WebFetch fails every time; use a browser User-Agent with a 10-15 attempt retry loop, or the r.jina.ai reader proxy as a fallback. Upload folder does not match meeting month (Jan and Mar 2026 briefings both sit under /uploads/2026/04/). Bi-monthly cadence: Jan, Mar, May, Jul, Sep, Nov, second Thursday.</t>
+          <t>URL PATCHED 2026-07-30: the site dropped the /about-us/ prefix in favour of /about/, so the old /about-us/our-board/previous-board-meetings/ path now genuinely 404s (reproduced independently, not a WAF artefact - Google still surfaces the dead /about-us/ URLs, so ignore stale search hits). Strategy: the landing /about/our-board/board-meetings/ lists UPCOMING dates (papers appear the Friday before) plus the ~11 most recent past meetings; the full back-catalogue from 2014 is one long page at /about/our-board/board-meetings/board-meeting-archive/. Each past meeting is its own page at /board-meeting-archive/trust-board-meeting-&lt;month&gt;-&lt;year&gt;/ with a 'Meeting downloads' block - but DO NOT construct those slugs, they are inconsistent (March 2026 is trust-board-meeting-march_2026 with an underscore; May 2023 carries a -2 suffix). Scrape hrefs instead. IMPORTANT: on the two most recent meeting pages the Elementor PDF buttons render with NO href attribute at all, so a link-scraper finds zero PDFs for the newest meetings; the reliable route is the WordPress REST media API at /wp-json/wp/v2/media?search=PUBLIC-TRUST-BOARD&amp;per_page=100&amp;orderby=date&amp;order=desc&amp;_fields=source_url,date. Server-rendered WordPress, no JS needed, but the edge resets TLS connections on roughly 60-90% of attempts (ECONNRESET / curl exit 35) and WebFetch fails every time; use a browser User-Agent with a 10-15 attempt retry loop, or the r.jina.ai reader proxy as a fallback. Upload folder does not match meeting month (Jan and Mar 2026 briefings both sit under /uploads/2026/04/). Bi-monthly cadence: Jan, Mar, May, Jul, Sep, Nov, second Thursday. FETCH WARNING (2026-08-01): every route tried this run (requests, local Playwright, browser-UA curl, server-side WebFetch) was connection-reset on /about/our-board/ paths even though the site root answered 200 -- the domain sits behind DDoSX bot mitigation. The page itself is live (Google index shows the landing and a July 2026 meeting archive page). Retry later or from another egress; do not repoint the URL on a reset alone.</t>
         </is>
       </c>
       <c r="J42" t="b">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Old /about-us/ path confirmed HTTP 404; new /about/our-board/board-meetings/ returns 200 (title 'Board meetings - North Staffordshire Combined Healthcare NHS Trust') linking July, May and March 2026 archive pages, with 2026 pack PDFs verified via the WordPress media API.</t>
+          <t>2026-08-01: no fetch route reached the board path this run -- local requests, local Playwright, browser-UA curl and server-side WebFetch all got a connection reset, while the site root answered 200 intermittently (www.combined.nhs.uk is fronted by ddosx.com). Google's index still carries the landing plus a /board-meetings/board-meeting-archive/trust-board-meeting-july-2026/ page and a January 2026 pack PDF, so the page is live and the URL correct; treat the resets as DDoSX bot mitigation, not rot.</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Static fetch reaches the listing: 23 July 2026 boardbook linked (Public-BOD-23.7.26-Boardbook-v1.pdf) with Sep and Nov 2026 dates pending papers. The scanner's near-empty body is an anti-bot response, not JS rendering.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: 23 July 2026 boardbook linked (/wp-content/uploads/2026/07/Public-BOD-23.7.26-Boardbook-v1.pdf) with forward dates 24 Sep, 25 Nov 2026, 28 Jan and 24 Mar 2027. Server-rendered -- no Playwright needed for the landing.</t>
         </is>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>2026 meetings table live with 'Agenda and Papers' links through 9 July 2026; Sep and Nov 2026 dates listed pending papers.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: the 2026 table carries 'Agenda and Papers' links for 15 Jan, 12 Mar, 14 May and 9 Jul 2026, with 10 Sep and 12 Nov 2026 pending. no_papers_visible is a false negative -- the links are CMS handlers without a .pdf suffix and the historic years sit in client-side accordions.</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Confirmed a 2026 full board pack plus two 2025 packs via index-&gt;year-&gt;event drill-down on cuh.nhs.uk / media.cuh.nhs.uk.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: landing is the year index (2017-2026) with the 2026 sub-page linked; page footer stamped 01-08-2026. Local requests and Playwright still get ERR_CONNECTION_RESET -- WebFetch remains the working route.</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>The registered URL /about-us/board-papers/ is wrong and 500s; the real landing is /p/about-us/trust-board-meetings (older archive at /p/historic-meeting-papers-1). At scan time the entire uhbw.nhs.uk site returned an ASP.NET 'Runtime Error' (transient site-wide outage, not a moved page, since /assets/1/ still served PDFs with HTTP 200). UHBW now meets jointly with North Bristol NHS Trust, so packs are titled 'Public Group Board Meeting' or 'meeting in common (UHBW &amp; NBT)'. Board meets in public every other month; papers published ~1 week before. PDFs sit flat in /assets/1/ with free-text filenames (e.g. public_group_board_meeting_13012026_papers.pdf). Needs render: the landing is ASP.NET/JS, so a crawler should retry the landing when the site recovers and scrape /assets/1/ links, or discover PDFs via site-search. Prefer the single combined '...papers' bundle per meeting; filter out Council of Governors packs, separate agendas, and minutes-only files.</t>
+          <t>The registered URL /about-us/board-papers/ is wrong and 500s; the real landing is /p/about-us/trust-board-meetings (older archive at /p/historic-meeting-papers-1). At scan time the entire uhbw.nhs.uk site returned an ASP.NET 'Runtime Error' (transient site-wide outage, not a moved page, since /assets/1/ still served PDFs with HTTP 200). UHBW now meets jointly with North Bristol NHS Trust, so packs are titled 'Public Group Board Meeting' or 'meeting in common (UHBW &amp; NBT)'. Board meets in public every other month; papers published ~1 week before. PDFs sit flat in /assets/1/ with free-text filenames (e.g. public_group_board_meeting_13012026_papers.pdf). Needs render: the landing is ASP.NET/JS, so a crawler should retry the landing when the site recovers and scrape /assets/1/ links, or discover PDFs via site-search. Prefer the single combined '...papers' bundle per meeting; filter out Council of Governors packs, separate agendas, and minutes-only files. Update 2026-08-01: the site-wide ASP.NET 'Runtime Error' seen on 2026-07-30 has cleared and the landing serves normally again.</t>
         </is>
       </c>
       <c r="J99" t="b">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Landing renders statically this week (last month's site-wide outage has cleared); 12 May 2026 group board agenda-and-papers PDF linked, with Sep and Nov 2026 dates scheduled.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: the site-wide ASP.NET runtime error seen on 2026-07-30 has cleared. /p/about-us/trust-board-meetings loads, shows papers plus a recording for 12 May 2026 and forward dates 14 Jul, 8 Sep, 10 Nov 2026, and states papers appear about a week before each meeting under press embargo until the meeting.</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Legacy ASP landing live; 2 July 2026 meeting listed with an 'Agenda &amp; Papers' link at /about/trustboard/2026_07/, forward dates through March 2027.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: forthcoming meetings 2 Jul, 3 Sep, 5 Nov 2026 and 7 Jan 2027 listed, archive dropdown runs from Jan 2020 to June 2026. no_papers_visible is a false negative -- packs live on the per-month /about/trustboard/YYYY_MM/ pages, not the index.</t>
         </is>
       </c>
     </row>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Landing live; 'Download meeting papers July 2026' (10.3MB) and June 2026 (6.1MB) packs listed. Scan-time connection reset was transient anti-bot behaviour.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: combined packs for 18 June 2026 (Public_Trust_Board_agenda_and_papers_180626) and 16 July 2026 (PUBLIC_Trust_Board_agenda_and_papers_160726) linked, plus forward dates 30 Sep and 19 Nov 2026. The scanner's connection reset is a local-path WAF artefact.</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Archive live and grouped by fiscal year; 4 June 2026 and 2 April 2026 'Agenda and papers' packs present.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: fiscal-year sections from 2026/27 back to 2019/20, with 'Agenda and papers' links for 4 June 2026 and 2 April 2026. no_papers_visible is a false negative caused by the extension-less /download_file/view/&lt;uuid&gt;/668 handler.</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>The URL is valid, but the near-empty body is NOT client-side JS -- the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to non-human traffic. Plain static fetch returns the challenge shell (empty), and headless Playwright is ALSO blocked (snapshot shows only the Imperva hCaptcha iframe). A standard Playwright crawler cannot reach the packs; it needs a captcha-solving/residential session or an allowlisted IP. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk).</t>
+          <t>The URL is valid. The near-empty body is NOT client-side JS — the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to traffic it scores as automated. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Packs are combined PDFs under /application/files/ (pattern 'FHFT_Public_Bd_&lt;D.MM.YY&gt;_v1.pdf'). Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk). ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback.</t>
         </is>
       </c>
       <c r="J149" t="b">
@@ -10366,17 +10366,17 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Re-probed 2026-07-30: fhft.nhs.uk still returns a 212-byte Imperva/Incapsula _Incapsula_Resource interstitial to every automated request, browser User-Agent included, so neither static fetch nor headless Playwright reaches the board-paper listing. The landing URL itself remains correct.</t>
+          <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: the scanner holds 5 forward dates (Aug-Dec 2026) and downloaded + analysed the 3 Jul 2026 pack straight from fhft.nhs.uk/application/files/, so the site IS reachable server-side. Landing URL correct.</t>
         </is>
       </c>
     </row>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Page confirmed live via a non-ClaudeBot User-Agent; 8 Jul 2026 (18.6MB), 6 May 2026, 4 Mar 2026 and 14 Jan 2026 packs all verified HTTP 200 application/pdf. The 502 the scanner sees is a ClaudeBot-specific UA block.</t>
+          <t>Re-verified 2026-08-01: browser-UA curl returns the full 292KB page with meetings 14 Jan, 4 Mar, 6 May, 8 Jul, 2 Sep and 4 Nov 2026 plus the 2025/26 archive. Server-side WebFetch was still answered with a synthetic HTTP 502 -- the edge's ClaudeBot block is unchanged, so use curl/requests rather than WebFetch here.</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Landing live listing 2026 meetings (04 Feb, 01 Apr, 17 Jun) each with a 'Meeting papers' link; Aug, Oct and Dec 2026 pending publication.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: combined public bundles linked for 4 Feb, 1 Apr, 17 Jun and 5 Aug 2026 under /media/board/Papers/2026/. no_papers_visible is a false negative -- the hrefs are space-encoded .pdf paths the classifier missed.</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Landing live serving the current 'July 2026 Board Papers' pack (21MB) plus the 'Previous board papers' archive folder.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: landing shows the current 'July 2026 Board Papers' combined pack (21.09 MB) plus the 'Previous board papers' folder link.</t>
         </is>
       </c>
     </row>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Live WordPress publications_type archive, statically readable via WebFetch (no Playwright, no 403). Landing lists the most recent Trust Board pack (currently 2 April 2026) and paginates via /publications_type/board-papers/page/N/ (currently 12 pages, ~one pack per page reverse-chronological). Each entry links directly to a single combined agenda+papers PDF under /wp-content/uploads/YYYY/MM/. Prefer the landing for the newest pack; walk /page/2/ etc. for older meetings.</t>
+          <t>Live WordPress publications_type archive, statically readable via WebFetch (no Playwright, no 403). Landing lists the most recent Trust Board pack (currently 2 April 2026) and paginates via /publications_type/board-papers/page/N/ (currently 12 pages, ~one pack per page reverse-chronological). Each entry links directly to a single combined agenda+papers PDF under /wp-content/uploads/YYYY/MM/. Prefer the landing for the newest pack; walk /page/2/ etc. for older meetings. Publication gap noted 2026-08-01: the newest pack is still 2 April 2026 and page 2 of the archive jumps back to 5 June 2025, so this archive is sparse and lags -- do not read a missing month as a fetch failure.</t>
         </is>
       </c>
       <c r="J180" t="b">
@@ -12349,17 +12349,17 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>papers_partial</t>
         </is>
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>WordPress archive live; latest pack is 'Trust Board Meeting - 2nd April 2026' (26MB, uploaded July 2026) with pagination to older packs. The ~3-month publication lag is the trust's own cadence, not a URL fault.</t>
+          <t>Re-verified 2026-08-01 via WebFetch and curl: the archive is live but thin -- page 1 holds only 'Trust Board Meeting - 2nd April 2026' (26MB) and page 2 jumps straight back to 5 June 2025, so no pack has been published for four months and the intervening meetings are absent. URL is correct; the gap is on the trust's side.</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Strategy: landing lists year archives (3 year links this run, e.g. 'Board papers 2025'). Follow each year link to dated PDF listings; main packs typically 5-30MB. Static fetch works. Pattern B.</t>
+          <t>Strategy: rewritten 2026-08-01 after re-inspecting the raw HTML -- the earlier 'year archives' description was wrong. The landing /about-us/how-were-run/trust-board/board-meetings ('Trust Board meetings and papers') carries the packs inline: several dozen direct links of the form /download_file/view/&lt;uuid&gt;/1221 listed against their meeting dates, no year sub-pages and no per-meeting pages to follow. Because that handler has no .pdf suffix, extension-based link filters see zero PDFs -- this is exactly why the validator scores the page papers_partial. Static fetch works, but only with a browser User-Agent: browser-UA curl returns HTTP 200 and the full 92KB page while server-side WebFetch was refused 403 on 2026-08-01, so try requests/curl with a normal UA first and treat a 403 as a route problem rather than a dead URL. Collection id 1221 identifies the board-papers document set; prefer the largest combined agenda-and-papers file per date.</t>
         </is>
       </c>
       <c r="J183" t="b">
@@ -12574,7 +12574,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=0, year_archives=3, meeting_subpages=0.</t>
+          <t>Re-verified 2026-08-01: browser-UA curl returns HTTP 200 and the landing carries dozens of inline /download_file/view/&lt;uuid&gt;/1221 pack links (server-side WebFetch got 403). papers_partial is a false negative from the extension-less download handler.</t>
         </is>
       </c>
     </row>
@@ -13047,7 +13047,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Landing live with six dated 2026 packs through 'Board of Directors Meeting Papers - 02.07.2026.pdf'.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: dated packs listed for 05.02.26, 05.03.26, 02.04.26, 07.05.26, 04.06.26 and 02.07.26. no_papers_visible is a false negative from the numeric /download_file/&lt;id&gt;/1439 handler carrying no .pdf suffix.</t>
         </is>
       </c>
     </row>
@@ -13228,7 +13228,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering. Both static fetch and headless Playwright receive the hCaptcha 'Additional security check is required' interstitial rather than page content, so a normal Playwright crawler cannot reach the packs without captcha bypass/allowlisting. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page -- the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path.</t>
+          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). Packs are served through the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix) so extension-based link filters will miss them. The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page — the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path. CAUTION: '31 March 2027' appears only in the heading 'Board meeting schedule to 31 March 2027' — it is not a meeting date. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback.</t>
         </is>
       </c>
       <c r="J193" t="b">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>.../board-meetings-public/previous-meetings-year (agendas &amp; reports by year);.../board-meetings-public/upcoming-meetings (calendar)</t>
+          <t>.../board-meetings-public/previous-meetings-year (agendas &amp; reports by year);.../board-meetings-public/upcoming-meetings (calendar);/download_file/&lt;id&gt;/&lt;id&gt; CMS handler links (no .pdf extension)</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -13246,17 +13246,17 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Re-probed 2026-07-30: blackpoolteachinghospitals.nhs.uk still returns a 212-byte Imperva/Incapsula _Incapsula_Resource interstitial to every automated request, browser User-Agent included, so neither static fetch nor headless Playwright reaches the board-paper listing. The landing URL itself remains correct.</t>
+          <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: WebFetch logged OK on 2026-07-13 (6 forward dates), the scanner holds 9 forward dates (Aug 2026-Mar 2027), and it downloaded + analysed the 2 Jul 2026 pack via /download_file/12115/2316. Landing URL correct.</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content. Static fetch and headless Playwright both hit the hCaptcha 'Additional security check is required' interstitial, so a standard Playwright crawler is blocked without captcha-solving or IP allowlisting. Once past the wall, the page lists scheduled board meetings (e.g. 12 Nov 2025, 14 Jan 2026, 11 Mar 2026 in the Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs from the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf'). Accessible versions via TrustBoardQuestions@elht.nhs.uk.</t>
+          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Once past the wall the page lists scheduled board meetings (Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs; two delivery paths are in use — the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf') and the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix), so extension-based link filters will miss the latter. Accessible versions via TrustBoardQuestions@elht.nhs.uk. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback.</t>
         </is>
       </c>
       <c r="J195" t="b">
@@ -13360,7 +13360,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>/application/files/**/Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf;meeting dates 12 Nov 2025 / 14 Jan 2026 / 11 Mar 2026</t>
+          <t>/application/files/**/Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf;meeting dates 12 Nov 2025 / 14 Jan 2026 / 11 Mar 2026;/download_file/&lt;id&gt;/&lt;id&gt; CMS handler links (no .pdf extension)</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -13370,17 +13370,17 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Re-probed 2026-07-30: elht.nhs.uk still returns a 212-byte Imperva/Incapsula _Incapsula_Resource interstitial to every automated request, browser User-Agent included, so neither static fetch nor headless Playwright reaches the board-paper listing. The landing URL itself remains correct.</t>
+          <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: WebFetch logged OK on 2026-07-13 (earlier 404 no longer occurs), the scanner holds 4 forward dates (Sep 2026-Mar 2027), and it downloaded + analysed the 8 Jul 2026 pack via /download_file/30649/191. Landing URL correct. Note the path was corrected to /about-us/our-trust-board/... — the older /about-us/board-meetings-... path 404s.</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Archive confirmed intact (25 documents, January 2023 to 3 June 2026) via the plugin's admin-ajax endpoint; 3 Jun 2026 (17.5MB), 2 Apr 2026, 5 Feb 2026 and 27 Nov 2025 packs all HTTP 200. The empty static tables are AJAX rendering, not withdrawal of papers.</t>
+          <t>Re-verified 2026-08-01 via WebFetch: the board page lists the 2026/27 meeting schedule (2 Apr, 3 Jun, 3 Sep, 28 Oct AGM, 5 Nov 2026, 4 Mar 2027) but the paper tables render empty, exactly as expected -- they are serverSide Document Library Pro widgets whose rows arrive by AJAX and never exist in the HTML source. Landing URL correct.</t>
         </is>
       </c>
     </row>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O208"/>
+  <dimension ref="A1:R208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -435,6 +435,9 @@
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="60" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,6 +514,21 @@
       <c r="O1" s="1" t="inlineStr">
         <is>
           <t>validation_notes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>retrieval_route</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>group_board</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>group_board_url</t>
         </is>
       </c>
     </row>
@@ -562,6 +580,9 @@
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -637,6 +658,9 @@
           <t>Re-verified 2026-08-01: plain curl with a browser User-Agent returns HTTP 200 and the landing lists the current pack 'Board paper 30th July 2026' (/documents/512-board-paper-30th-july-2026) plus a /board-papers sub-page. Server-side WebFetch was refused 403 on this run and the scanner saw a connection reset, so the block is route-specific, not a dead page.</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -686,6 +710,9 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -735,6 +762,9 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -810,6 +840,9 @@
           <t>Re-verified 2026-08-01 via WebFetch: 'Meetings in public' lists 'Meeting papers: 23 July 2026' and '9 July 2026' newest-first plus forward dates to March 2027. The papers_partial classification is a false negative -- packs sit one hop down on the per-meeting sub-pages, so the landing itself carries no dated PDF links.</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -885,6 +918,9 @@
           <t>June 2026 meeting page lists ~35 board paper PDFs (agenda, CEO report, finance, quality) all live on ashfordstpeters.info.</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -960,6 +996,9 @@
           <t>2026 and 2025 year-archive pages each list multiple dated public board meetings with agenda and paper PDFs as static download_file links.</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1035,6 +1074,9 @@
           <t>Live packs present for June 2026 (open-meeting-pack 04.06.26) and April/February 2026 plus full back-catalogue to 2024.</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1110,6 +1152,9 @@
           <t>New /board-meetings-and-papers page lists monthly combined Board papers PDFs incl April 2026 and January 2026 plus full 2024-25 history; old /about-us/trust-board/ path is dead (404).</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1159,6 +1204,9 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1234,6 +1282,9 @@
           <t>Re-verified 2026-08-01 via WebFetch: 'Meetings in public' lists 2026 packs (21 April, 17 February) and forward dates 18 Aug, 15 Sep (AGM), 20 Oct, 15 Dec 2026. The scanner's connection reset is a WAF artefact on the local path only.</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1309,6 +1360,9 @@
           <t>Validator (static) found dated_pdfs=63, year_archives=0, meeting_subpages=4.</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1380,6 +1434,9 @@
           <t>board-meetings page lists 2025 and 2026 dated meeting sub-pages; confirmed the 28 May 2026 sub-page links a combined Public Board Meeting Pack PDF.</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1455,6 +1512,9 @@
           <t>board-meetings archive lists 14 May 2026, 31 March 2026 and 5 February 2026 meetings; confirmed direct 2026 papers PDFs under /wp-content/uploads/2026/.</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1504,6 +1564,9 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1553,6 +1616,9 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1628,6 +1694,9 @@
           <t>Old /board-of-directors-and-meetings overview page has no paper links; live dated packs are in a JS document library at /board-papers/ (year folder then per-meeting date sub-folder), confirmed Public Board pack 28 May 2026 via browser.</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1703,6 +1772,9 @@
           <t>page lists direct combined board-meeting-papers PDFs through June 2026 (e.g. 0-board-meeting-papers-v3-june-2026.pdf, april-2026, february-2026).</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1752,6 +1824,9 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1801,6 +1876,9 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1850,6 +1928,9 @@
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1899,6 +1980,9 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1974,6 +2058,9 @@
           <t>Search-confirmed live combined packs 27 January 2026 and 26 May 2026 under leicspart.nhs.uk/wp-content/uploads/2026/; site blocks automated fetch (anti-bot).</t>
         </is>
       </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2023,6 +2110,9 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2072,6 +2162,9 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2147,6 +2240,9 @@
           <t>Inline dated PDFs present for the 11 June 2026 Boards in Common meeting (agenda + committee reports); older packs via the 'previous Trust Board meetings' publication-scheme link.</t>
         </is>
       </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2191,11 +2287,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>The registered URL /board-and-board-papers/ is only an info page (meeting dates + governance contact) and correctly shows no PDFs. The actual papers live one level down at /board-papers (linked in that page's sidebar). That index lists year folders as query-string links: /board-papers?media_folder=1422&amp;root_folder=2025/26 and /board-papers?media_folder=1466&amp;root_folder=2026/27. A crawler must follow the media_folder query params to reach per-meeting PDFs (folder contents load dynamically, so render or fetch the folder URLs). Coverage current to 2026/27. Prefer the full board pack/'supporting documents' bundle per meeting; filter out minutes-only and agenda-only files and pre-2025 folders. Point the crawler at root_folder=2026/27 for the latest papers.</t>
+          <t>The registered URL /board-and-board-papers/ is only an info page (meeting dates + governance contact) and correctly shows no PDFs. The actual papers live one level down at /board-papers (linked in that page's sidebar). That index lists year folders as query-string links: /board-papers?media_folder=1422&amp;root_folder=2025/26 and /board-papers?media_folder=1466&amp;root_folder=2026/27. A crawler must follow the media_folder query params to reach per-meeting PDFs (folder contents load dynamically, so render or fetch the folder URLs). Coverage current to 2026/27. Prefer the full board pack/'supporting documents' bundle per meeting; filter out minutes-only and agenda-only files and pre-2025 folders. Point the crawler at root_folder=2026/27 for the latest papers. RETRIEVAL 5 Aug 2026: papers live at /board-papers in a MEDIA BROWSER, not as direct links. Navigate /board-papers?media_folder=&lt;id&gt;&amp;root_folder=&lt;year&gt; to a financial-year folder, then one sub-folder PER MEETING, each containing the pack. 2026/27 = media_folder=1466. Plain requests reads it fine - Playwright not needed.</t>
         </is>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2209,7 +2305,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2222,6 +2318,9 @@
           <t>Papers are present in dynamically-loaded year folders (2025/26 and 2026/27) reached via media_folder query params off /board-papers; individual PDFs require rendering the folder view to enumerate.</t>
         </is>
       </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2297,6 +2396,9 @@
           <t>2026 packs listed for 27 Jan, 24 Mar, 19 May 2026; 2025 sample 'Agenda and papers' = /download_file/view/6958/222 (14 Jan 2025).</t>
         </is>
       </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2372,6 +2474,9 @@
           <t>Validator (static) found dated_pdfs=57, year_archives=0, meeting_subpages=0.</t>
         </is>
       </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2447,6 +2552,9 @@
           <t>Dated month links present under both 2025 and 2026 headings, e.g. 'January 2026 (Performance Report)' and 'August 2025', each a download_file/view PDF.</t>
         </is>
       </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2522,6 +2630,9 @@
           <t>Landing page lists 2025 and 2026 board meetings each with a downloadable ZIP papers archive (e.g. trust-board-papers-may-2026.zip).</t>
         </is>
       </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2597,6 +2708,9 @@
           <t>Re-verified 2026-08-01 via WebFetch: the July 2026 'Board in Common' set is present as three direct PDFs (content/doclib/14558-14560.pdf: agenda, meeting papers, public information pack) with the year dropdown back ~5 years. Static fetch reaches the current pack; Playwright is only needed to enumerate the historic archive.</t>
         </is>
       </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2672,6 +2786,9 @@
           <t>2026 packs: 'Trust Board Papers – May 2026', 'March 2026', 'January 2026'; 2025 includes 'Trust Board Papers – November 2025' and 'September 2025'.</t>
         </is>
       </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2747,6 +2864,9 @@
           <t>Archive page lists a dated 2025 combined board pack (07.10.2025) plus year sections; 2026/27 joint board dates listed with packs to follow.</t>
         </is>
       </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2822,6 +2942,9 @@
           <t>Trust-board-papers page lists multiple dated 2025 and 2026 board-pack PDFs (Jan 2025 through Apr 2026) directly downloadable.</t>
         </is>
       </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2897,6 +3020,9 @@
           <t>Current URL /our-organisation/trust-board-meetings/ returns HTTP 200 and is the canonical 'Trust Board Meetings' page; 2026 combined public board packs (2 April 2026, 4 June 2026) are indexed under the site's own /download/clientfiles/files/ path. Shallow-check failure was a WAF connection reset.</t>
         </is>
       </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2972,6 +3098,9 @@
           <t>2025-2026 year sub-page lists seven dated combined board packs (07.05.2025 through 04.03.2026); 2026-2027 sub-page already created.</t>
         </is>
       </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3021,6 +3150,9 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3070,6 +3202,9 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3145,6 +3280,9 @@
           <t>Validator (static) found dated_pdfs=26, year_archives=0, meeting_subpages=31.</t>
         </is>
       </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3220,6 +3358,9 @@
           <t>2026-08-01: no fetch route reached the board path this run -- local requests, local Playwright, browser-UA curl and server-side WebFetch all got a connection reset, while the site root answered 200 intermittently (www.combined.nhs.uk is fronted by ddosx.com). Google's index still carries the landing plus a /board-meetings/board-meeting-archive/trust-board-meeting-july-2026/ page and a January 2026 pack PDF, so the page is live and the URL correct; treat the resets as DDoSX bot mitigation, not rot.</t>
         </is>
       </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3295,6 +3436,9 @@
           <t>Static page lists dated 2025/2026 board PDFs; confirmed HTTP-200 full public board pack for 20 May 2026 (~22MB).</t>
         </is>
       </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3370,6 +3514,9 @@
           <t>Confirmed combined public Board Meeting Pack PDFs for Jan, Mar and May 2026 (plus full 2025 set) on bwc.nhs.uk /download/ paths.</t>
         </is>
       </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3445,6 +3592,9 @@
           <t>Landing page directly lists combined Trust Board Papers PDFs for multiple 2025 and 2026 meetings via download_file links.</t>
         </is>
       </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3494,6 +3644,9 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3569,6 +3722,9 @@
           <t>Human landing uhb.nhs.uk/about/trust-management/bod/papers/ re-confirmed as still pointing at the docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD Nextcloud share; the share itself remains JS-rendered so static scans see nothing.</t>
         </is>
       </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3644,6 +3800,9 @@
           <t>Validator (static) found dated_pdfs=0, year_archives=5, meeting_subpages=1.</t>
         </is>
       </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3719,6 +3878,9 @@
           <t>2026 year page resolves to per-meeting pages with live 2026 board-pack PDFs (May 2026 combined agenda confirmed, HTTP 200 application/pdf).</t>
         </is>
       </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3768,6 +3930,9 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3843,6 +4008,9 @@
           <t>Validator (static) found dated_pdfs=348, year_archives=2, meeting_subpages=1.</t>
         </is>
       </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3918,6 +4086,9 @@
           <t>Validator (static) found dated_pdfs=27, year_archives=0, meeting_subpages=18.</t>
         </is>
       </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3993,6 +4164,9 @@
           <t>Confirmed multiple dated combined board packs including a 42MB 'BCHC Public Board Papers Pack 4 June 2026' and packs through Feb 2025.</t>
         </is>
       </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4068,6 +4242,9 @@
           <t>Validator (static) found dated_pdfs=59, year_archives=0, meeting_subpages=6.</t>
         </is>
       </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4143,6 +4320,9 @@
           <t>Kingston &amp; Richmond board meetings page live; latest 7 May 2026 Part 1 pack + board paper archive link.</t>
         </is>
       </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4185,13 +4365,46 @@
           <t>https://www.guysandstthomas.nhs.uk/about-us/our-board/agenda-and-papers</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>HARDEST KNOWN CASE - two separate problems, both solved. (1) The whole host sits behind a WAF that returns HTTP 403 (a ~784KB error page) to curl, requests, WebFetch, real-Chrome-headful AND the full anti-automation recipe (stealth init script, disable-blink-features, site-root-first for cookies, ctx.request.get with Referer); after a few attempts it escalates to resetting the TLS connection outright, i.e. an IP-level block. (2) Documents are served from /media/&lt;id&gt;/&lt;url-encoded title&gt; with NO FILE EXTENSION, so any crawler keying on '.pdf' or '/download' finds zero links even on a page it can read. WHAT WORKS: fetch through Archive.org Save Page Now - GET https://web.archive.org/save/&lt;url&gt;. Archive.org crawls from its own infrastructure so the IP block does not apply. This works for BOTH the landing page (returns 31 document links incl. the full back-archive) and for the document URLs themselves (the response body is the PDF bytes - check for %PDF and strip any prefix). Verified 5 Aug 2026 on the 22 July 2026 board pack (8MB) and agenda (163KB). Match documents with the pattern guysandstthomas.nhs.uk/media/&lt;digits&gt;/ - NOT a .pdf extension.</t>
+        </is>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>/media/{id}/Board+of+Directors+meeting+papers+-+{Weekday}+{D}+{Month}+{YYYY};/media/{id}/Board+of+Directors+meeting+agenda+-+{Weekday}+{D}+{Month}+{YYYY}</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>minutes;register-of-interests</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Board meets quarterly. 22 July 2026 pack (97pp) and agenda retrieved via Archive.org Save Page Now on 5 Aug 2026; landing page also lists packs back to January 2024. Next meeting 21 October 2026.</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>archive_org_save_page_now</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4267,6 +4480,9 @@
           <t>2026: 'Trust Board Meeting, Tuesday 28 April 2026'; 2025: 'Trust Board 30 September 2025' and 'Trust Board 24 June 2025'.</t>
         </is>
       </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4316,6 +4532,9 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4391,6 +4610,9 @@
           <t>Page titled 'Group Board Papers and Agenda' lists dated group-board PDFs May 2025 through July 2026 as direct hyperlinks; static fetch resolves every href.</t>
         </is>
       </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4466,6 +4688,9 @@
           <t>Landing page directly links combined public Board of Directors agenda+papers PDFs for every 2025 and 2026 meeting with dates in the URL.</t>
         </is>
       </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4541,6 +4766,9 @@
           <t>Confirmed dated public group board packs from 1 May 2025 through 8 May 2026 as direct PDF downloads.</t>
         </is>
       </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4616,6 +4844,9 @@
           <t>2026 archive lists combined board packs for Feb/Mar/Jun 2026 and the 2025 archive lists Jan/Mar/Jun/Jul/Oct/Nov 2025, all as directly-linked PDFs.</t>
         </is>
       </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4691,6 +4922,9 @@
           <t>Via Playwright confirmed dated public board packs incl. 'Public Board papers - 19 Nov 2025' and 'Public Board Pack 26.03.2025'; 2026 meeting dates (Mar/Jul/Sep/Nov 2026) also scheduled.</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4766,6 +5000,9 @@
           <t>HRCH merged into Kingston &amp; Richmond (RAX) 1 Nov 2024; same combined board/URL as RAX (dedupe). Latest 7 May 2026.</t>
         </is>
       </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4837,6 +5074,9 @@
           <t>Live archive at /publications/board-papers-and-committee-tor. Confirmed PDFs 28 May 2026, 30 Apr 2026, 26 Mar 2026 (Trust Board) + Board-in-Common 29 Apr 2026 + 22 Oct 2025.</t>
         </is>
       </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4912,6 +5152,9 @@
           <t>Re-verified 2026-08-01 via WebFetch: 23 July 2026 boardbook linked (/wp-content/uploads/2026/07/Public-BOD-23.7.26-Boardbook-v1.pdf) with forward dates 24 Sep, 25 Nov 2026, 28 Jan and 24 Mar 2027. Server-rendered -- no Playwright needed for the landing.</t>
         </is>
       </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4987,6 +5230,9 @@
           <t>Confirmed dated agendas for 25 February 2026 and 25 March 2026 plus 2024/25 archive on the new yorkhospitals.nhs.uk domain.</t>
         </is>
       </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5036,6 +5282,9 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5111,6 +5360,9 @@
           <t>Latest pack '06 May 2026 Public Board of Directors Meeting papers' plus full back-catalogue of combined PDFs visible on the live page.</t>
         </is>
       </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5186,6 +5438,9 @@
           <t>Via the WPFD AJAX endpoint each 2025-26 month sub-folder returns one combined board pack and the June 2026 download URL was verified live (HTTP 200, application/pdf, 4.7MB).</t>
         </is>
       </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5261,6 +5516,9 @@
           <t>taxonomy/term/37 lists dated 2025-2026 board meeting sub-pages; search confirmed a Feb 2026 combined public pack PDF under /sites/default/files/2026-02/ on the org's own domain.</t>
         </is>
       </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5336,6 +5594,9 @@
           <t>Validator (static) found dated_pdfs=29, year_archives=0, meeting_subpages=0.</t>
         </is>
       </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5385,6 +5646,9 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5460,6 +5724,9 @@
           <t>Live 2026 board-papers page lists six 2026 meeting dates as accordion tabs; individual enclosure PDFs on clientfiles paths but require tab expansion to enumerate.</t>
         </is>
       </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5535,6 +5802,9 @@
           <t>Live NLG Boards-in-Common hub lists 2026 year card with Feb/Mar/Apr/May 2026 combined packs; replaced stale 2021 archive URL.</t>
         </is>
       </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5584,6 +5854,9 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5659,6 +5932,9 @@
           <t>Board meetings index lists a 28 May 2026 public-board ZIP pack and a 26 March 2026 board-meeting document page on the org's own domain.</t>
         </is>
       </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5734,6 +6010,9 @@
           <t>2026 folder lists 'Public Board Papers - 27 May 2026', '25 March 2026', '28 January 2026'; 2025 folder includes 'Public Board Papers - 28 May 2025'.</t>
         </is>
       </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5809,6 +6088,17 @@
           <t>NLG board-papers year page lists six 2025 Boards-in-Common combined PDFs (Feb-Dec 2025) plus a 'Board papers 2026' archive, explicitly covering Hull University Teaching Hospitals under the group structure.</t>
         </is>
       </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Humber Health Partnership board - packs hosted on the NLaG domain</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>https://www.nlg.nhs.uk/resources/?resources_type=board-papers</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5884,6 +6174,9 @@
           <t>Re-verified 2026-08-01 via WebFetch: the 2026 table carries 'Agenda and Papers' links for 15 Jan, 12 Mar, 14 May and 9 Jul 2026, with 10 Sep and 12 Nov 2026 pending. no_papers_visible is a false negative -- the links are CMS handlers without a .pdf suffix and the historic years sit in client-side accordions.</t>
         </is>
       </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5959,6 +6252,9 @@
           <t>Document section lists 2026 board pack sub-pages (May/March/January 2026) each linking the meeting's combined agenda pack, plus matching minutes entries.</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6008,6 +6304,9 @@
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6083,6 +6382,9 @@
           <t>Recent 2026 public board packs (30 June, 28 April, 31 March) linked as direct PDFs.</t>
         </is>
       </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6132,6 +6434,9 @@
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6207,6 +6512,9 @@
           <t>Validator (static) found dated_pdfs=89, year_archives=0, meeting_subpages=1.</t>
         </is>
       </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6282,6 +6590,9 @@
           <t>Confirmed dated agenda/minutes PDFs for the 28 May 2026 public Board of Directors meeting plus March 2026, January 2026 and November 2025 on the meeting-minutes-and-agendas page on the live sheffieldpartnership.nhs.uk domain.</t>
         </is>
       </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6331,6 +6642,17 @@
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Norfolk and Waveney University Hospitals Group</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>https://nw-uhg.org.uk/p/about-us/meetings-and-agendas</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6406,6 +6728,9 @@
           <t>Confirmed year-folder structure on landing with current folders '2025 to 2026 Board meetings papers' and a '2026 to 2027' folder containing 'May 2026 ESNEFT board meeting papers'.</t>
         </is>
       </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6455,6 +6780,9 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6530,6 +6858,9 @@
           <t>Archive is a client-rendered media browser exposing 2025 and 2026 board-paper folders but no PDF hrefs in static HTML.</t>
         </is>
       </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6603,6 +6934,17 @@
       <c r="O91" t="inlineStr">
         <is>
           <t>Confirmed dated combined public board packs for 26 September 2025 and 25 July 2025 on the board-and-governors-meetings page, with a noted transition to Norfolk and Waveney Group Board meetings from April 2026.</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Norfolk and Waveney University Hospitals Group</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>https://nw-uhg.org.uk/p/about-us/meetings-and-agendas</t>
         </is>
       </c>
     </row>
@@ -6654,6 +6996,9 @@
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6729,6 +7074,9 @@
           <t>Re-verified 2026-08-01 via WebFetch: landing is the year index (2017-2026) with the 2026 sub-page linked; page footer stamped 01-08-2026. Local requests and Playwright still get ERR_CONNECTION_RESET -- WebFetch remains the working route.</t>
         </is>
       </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6778,6 +7126,17 @@
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Norfolk and Waveney University Hospitals Group</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>https://nw-uhg.org.uk/p/about-us/meetings-and-agendas</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6827,6 +7186,9 @@
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6902,6 +7264,9 @@
           <t>Direct PDFs visible e.g. 'Public Board Meeting Book - 03.06.2026.pdf' (June 2026) and 'Public Board Meeting Papers 26112025.pdf' (Nov 2025).</t>
         </is>
       </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6977,6 +7342,9 @@
           <t>Landing page directly lists dated meetings with agenda and item PDFs for 28 Jan, 18 Mar, 1 Apr and 20 May 2026 plus Sep and Nov 2025.</t>
         </is>
       </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7052,6 +7420,9 @@
           <t>Confirmed combined 'Board of Director Part 1 Meeting Pack 13 May 2026' PDF and supporting agenda/reading-room files on the our-performance page, with 2026 meeting dates listed through November 2026.</t>
         </is>
       </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7125,6 +7496,17 @@
       <c r="O99" t="inlineStr">
         <is>
           <t>Re-verified 2026-08-01 via WebFetch: the site-wide ASP.NET runtime error seen on 2026-07-30 has cleared. /p/about-us/trust-board-meetings loads, shows papers plus a recording for 12 May 2026 and forward dates 14 Jul, 8 Sep, 10 Nov 2026, and states papers appear about a week before each meeting under press embargo until the meeting.</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Bristol group board - NBT and UHBW meet in common; NBT hosts the year pages</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>https://www.nbt.nhs.uk/about-us/meet-our-board/trust-board-meetings-20262027</t>
         </is>
       </c>
     </row>
@@ -7176,6 +7558,9 @@
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7251,6 +7636,9 @@
           <t>Trust Board Meetings sub-page lists dated 2025 and 2026 Part 1 board paper pack PDFs (e.g. Feb, Apr, Jun, Aug, Oct, Dec 2025 and Feb, Apr 2026).</t>
         </is>
       </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7326,6 +7714,9 @@
           <t>Re-verified 2026-08-01 via WebFetch: forthcoming meetings 2 Jul, 3 Sep, 5 Nov 2026 and 7 Jan 2027 listed, archive dropdown runs from Jan 2020 to June 2026. no_papers_visible is a false negative -- packs live on the per-month /about/trustboard/YYYY_MM/ pages, not the index.</t>
         </is>
       </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7401,6 +7792,9 @@
           <t>Validator (static) found dated_pdfs=14, year_archives=0, meeting_subpages=0.</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7476,6 +7870,9 @@
           <t>Current-year page (BoardMeetings2526.aspx) lists 'Agenda Pack Trust Board in Public March 2026' and full monthly back-catalogue of agenda packs.</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7525,6 +7922,9 @@
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7569,11 +7969,11 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Landing page is live and current but the site sits behind a WAF that returns HTTP 403 to WebFetch; use Playwright/headless browser, which loads it cleanly. The page lists the current calendar year's meetings inline with a 'Board papers and minutes' section giving, per meeting date, a meeting-pack PDF link plus a separate 'Minutes' PDF link, all served from the /media/{hash}/ path on the org domain. Older years live at .../board-meetings-papers-minutes/archive/. Match the meeting-pack PDF (filenames contain 'pack' or 'meeting-book' or 'meeting-pack'), not the minutes.</t>
+          <t>Landing page is live and current but the site sits behind a WAF that returns HTTP 403 to WebFetch; use Playwright/headless browser, which loads it cleanly. The page lists the current calendar year's meetings inline with a 'Board papers and minutes' section giving, per meeting date, a meeting-pack PDF link plus a separate 'Minutes' PDF link, all served from the /media/{hash}/ path on the org domain. Older years live at .../board-meetings-papers-minutes/archive/. Match the meeting-pack PDF (filenames contain 'pack' or 'meeting-book' or 'meeting-pack'), not the minutes. UPDATE 5 Aug 2026: Playwright is no longer required. Archive.org Save Page Now (GET https://web.archive.org/save/&lt;landing&gt;) returns the live page with document links (direct fetch 403s with a 473-byte body; SPN returned 200 / 88KB / 8 doc links). SPN is much cheaper than a browser launch - try it first, keep Playwright as the backstop.</t>
         </is>
       </c>
       <c r="J106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -7587,7 +7987,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7600,6 +8000,13 @@
           <t>Three 2026 meeting packs (27 May, 25 Mar, 28 Jan) plus minutes listed inline on the live page, last updated June 2026.</t>
         </is>
       </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>archive_org_save_page_now</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7649,6 +8056,9 @@
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7698,6 +8108,9 @@
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7747,6 +8160,9 @@
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7822,6 +8238,9 @@
           <t>board-papers page exposes Board papers 2025 and 2026 year archives, and the 2026 archive lists dated per-meeting sub-pages (8 Jan, 5 Mar, 13 May 2026).</t>
         </is>
       </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7871,6 +8290,9 @@
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7946,6 +8368,9 @@
           <t>Validator (static) found dated_pdfs=25, year_archives=0, meeting_subpages=1.</t>
         </is>
       </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7995,6 +8420,17 @@
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Bristol group board - NBT and UHBW meet in common; NBT hosts the year pages</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>https://www.nbt.nhs.uk/about-us/meet-our-board/trust-board-meetings-20262027</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8070,6 +8506,9 @@
           <t>Landing confirms year folders e.g. '2025 - 2026' and '2024 - 2025'; individual dated 2025/2026 PDFs sit one level inside each year folder (navigate IDs dynamic, read from live page).</t>
         </is>
       </c>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8145,6 +8584,9 @@
           <t>Validator (static) found dated_pdfs=0, year_archives=3, meeting_subpages=0.</t>
         </is>
       </c>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8194,6 +8636,9 @@
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8269,6 +8714,9 @@
           <t>Corrected from wrong domain; new page shows 2025-2026 Trust Board Part A main + supplementary packs.</t>
         </is>
       </c>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8318,6 +8766,9 @@
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8367,6 +8818,9 @@
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8416,6 +8870,17 @@
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>NW London Acute Provider Collaborative Board in Common</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>https://www.nwl-acute-provider-group.nhs.uk/publications</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8491,6 +8956,9 @@
           <t>WAF returns 403/500 to bots; Google confirms URL is the live 'Trust board meetings' page.</t>
         </is>
       </c>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8566,6 +9034,17 @@
           <t>Board-in-Common full-pack PDFs for 20 Jan 2026 and 28 Apr 2026 (covering Hillingdon) are published on the NWL Acute Provider Collaborative site.</t>
         </is>
       </c>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>NW London Acute Provider Collaborative Board in Common</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>https://www.nwl-acute-provider-group.nhs.uk/publications</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8641,6 +9120,9 @@
           <t>Inside the folder structure confirmed pack 'Trust Board (Public) Papers 15.01.26 (v2) For Website Reduced Size.pdf' (uploaded 16 Jan 2026); March/May 2026 folders present.</t>
         </is>
       </c>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8716,6 +9198,9 @@
           <t>Direct dated links e.g. 'Download the board papers for 21 May 2026' (doc 16288) and 'Download the board papers for 26 November 2025' (doc 16128).</t>
         </is>
       </c>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8791,6 +9276,17 @@
           <t>Validator (static) found dated_pdfs=0, year_archives=5, meeting_subpages=2.</t>
         </is>
       </c>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>NW London Acute Provider Collaborative Board in Common</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>https://www.nwl-acute-provider-group.nhs.uk/publications</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8866,6 +9362,9 @@
           <t>Direct PDFs e.g. May 2026 (/download/may-2026-paperspdf.pdf) and November 2025 (/download/november-2025.pdf).</t>
         </is>
       </c>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8941,6 +9440,9 @@
           <t>Validator (static) found dated_pdfs=12, year_archives=17, meeting_subpages=6.</t>
         </is>
       </c>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8990,6 +9492,17 @@
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>NW London Acute Provider Collaborative Board in Common</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>https://www.nwl-acute-provider-group.nhs.uk/publications</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9065,6 +9578,9 @@
           <t>Validator (static) found dated_pdfs=34, year_archives=0, meeting_subpages=1.</t>
         </is>
       </c>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9140,6 +9656,9 @@
           <t>Re-verified 2026-08-01 via WebFetch: combined packs for 18 June 2026 (Public_Trust_Board_agenda_and_papers_180626) and 16 July 2026 (PUBLIC_Trust_Board_agenda_and_papers_160726) linked, plus forward dates 30 Sep and 19 Nov 2026. The scanner's connection reset is a local-path WAF artefact.</t>
         </is>
       </c>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9189,6 +9708,9 @@
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9238,6 +9760,9 @@
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9313,6 +9838,9 @@
           <t>Validator (static) found dated_pdfs=55, year_archives=0, meeting_subpages=0.</t>
         </is>
       </c>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9388,6 +9916,9 @@
           <t>MERGER: Tavistock &amp; Portman dissolved into North London NHS FT (ODS G6V2S) on 1 Apr 2026; old site retired (301 to successor). URL repointed to successor board papers. Duplicates row G6V2S - flag for reconciliation.</t>
         </is>
       </c>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9437,6 +9968,9 @@
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9512,6 +10046,9 @@
           <t>Corrected sub-page lists Combined board paper PDFs through 21 May 2026.</t>
         </is>
       </c>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9587,6 +10124,9 @@
           <t>Re-verified 2026-08-01 via WebFetch: fiscal-year sections from 2026/27 back to 2019/20, with 'Agenda and papers' links for 4 June 2026 and 2 April 2026. no_papers_visible is a false negative caused by the extension-less /download_file/view/&lt;uuid&gt;/668 handler.</t>
         </is>
       </c>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9662,6 +10202,9 @@
           <t>Static page lists dated combined Agenda+Papers board-pack PDFs for 2025 and 2026; sampled May 2026 link returned a multi-MB PDF.</t>
         </is>
       </c>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9711,6 +10254,9 @@
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9760,6 +10306,9 @@
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9835,6 +10384,9 @@
           <t>Confirmed dated packs e.g. 'Public board papers - January 2026' (/download_file/3812/875) and 'Public board papers - November 2025' (/download_file/3764/875).</t>
         </is>
       </c>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -9910,6 +10462,9 @@
           <t>Resources filter lists dated UHT group board agendas/papers and a confirmed 5 March 2026 papers PDF resolves on the southtees.nhs.uk domain.</t>
         </is>
       </c>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -9985,6 +10540,17 @@
           <t>Same UHT group board as South Tees; dated 2026 group packs confirmed on the shared southtees.nhs.uk domain.</t>
         </is>
       </c>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>University Hospitals Tees group board - packs hosted on the SOUTH Tees domain</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>https://www.southtees.nhs.uk/resources/?topic=board-of-directors</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10060,6 +10626,9 @@
           <t>Validator (static) found dated_pdfs=53, year_archives=0, meeting_subpages=0.</t>
         </is>
       </c>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10135,6 +10704,9 @@
           <t>/about/team/board/ lists 'CNTW Board of Directors Public Papers Jan 2026' and 'April 2026' (posted 17/06/2026) as download_file links; old publications pages return genuine 404.</t>
         </is>
       </c>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10184,6 +10756,9 @@
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10259,6 +10834,9 @@
           <t>Confirmed dated entries e.g. 'Tuesday 10 February 2026' and 'Tuesday 09 December 2025', each with a public agenda link plus a 'Confidential agenda' to skip.</t>
         </is>
       </c>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10304,6 +10882,9 @@
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10379,6 +10960,9 @@
           <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: the scanner holds 5 forward dates (Aug-Dec 2026) and downloaded + analysed the 3 Jul 2026 pack straight from fhft.nhs.uk/application/files/, so the site IS reachable server-side. Landing URL correct.</t>
         </is>
       </c>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10428,6 +11012,9 @@
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10503,6 +11090,9 @@
           <t>Validator (static) found dated_pdfs=3, year_archives=3, meeting_subpages=0.</t>
         </is>
       </c>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10552,6 +11142,9 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10601,6 +11194,9 @@
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10650,6 +11246,9 @@
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10699,6 +11298,9 @@
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10748,6 +11350,9 @@
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10797,6 +11402,9 @@
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -10872,6 +11480,9 @@
           <t>Year sub-pages list per-meeting document folders for 2025 and 2026; the March 2026 folder contains the numbered agenda and papers PDFs (00-22).</t>
         </is>
       </c>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -10947,6 +11558,9 @@
           <t>13 in-window meetings via brute-force /board-meetings/{month-year}/ probe. May 2026 and March 2026 packs (15MB + 11MB) both have detectable BAF sections.</t>
         </is>
       </c>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -10996,6 +11610,9 @@
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11071,6 +11688,9 @@
           <t>Re-verified 2026-08-01: browser-UA curl returns the full 292KB page with meetings 14 Jan, 4 Mar, 6 May, 8 Jul, 2 Sep and 4 Nov 2026 plus the 2025/26 archive. Server-side WebFetch was still answered with a synthetic HTTP 502 -- the edge's ClaudeBot block is unchanged, so use curl/requests rather than WebFetch here.</t>
         </is>
       </c>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11146,6 +11766,9 @@
           <t>Child meetings page lists combined Board of Directors PDF bundles for every 2025 and 2026 meeting under year headings.</t>
         </is>
       </c>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11221,6 +11844,17 @@
           <t>Minutes/agendas child page has combined public Trust Board paper PDFs for every 2025 and 2026 meeting (Jan-Nov 2025, Jan and Mar 2026).</t>
         </is>
       </c>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>South East Sector Health Care Partnership joint board (from 1 April 2026)</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>https://www.southeastsector-hcp.nhs.uk/</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11296,6 +11930,9 @@
           <t>Re-verified 2026-08-01 via WebFetch: combined public bundles linked for 4 Feb, 1 Apr, 17 Jun and 5 Aug 2026 under /media/board/Papers/2026/. no_papers_visible is a false negative -- the hrefs are space-encoded .pdf paths the classifier missed.</t>
         </is>
       </c>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11345,6 +11982,9 @@
       <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11418,6 +12058,17 @@
       <c r="O166" t="inlineStr">
         <is>
           <t>2025 single-trust public packs on the Stockport page and a live June 2026 Joint Public Board Meeting Pack on the partnership site confirmed.</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>South East Sector Health Care Partnership joint board (from 1 April 2026)</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>https://www.southeastsector-hcp.nhs.uk/</t>
         </is>
       </c>
     </row>
@@ -11469,6 +12120,9 @@
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11544,6 +12198,9 @@
           <t>Validator (static) found dated_pdfs=28, year_archives=0, meeting_subpages=0.</t>
         </is>
       </c>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -11619,6 +12276,9 @@
           <t>Year archives are share-my-box JS galleries. Playwright + year-tab click required; one Feb 2026 pack recovered (BAF score 236).</t>
         </is>
       </c>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11690,6 +12350,9 @@
           <t>Landing page links to single combined Meeting Book PDFs for all 2025 meetings and the Feb and May 2026 meetings; the Feb 2026 document slug resolved directly to a multi-page PDF.</t>
         </is>
       </c>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -11765,6 +12428,9 @@
           <t>Latest pack '0-Meeting-in-Public 02.07.2026 compressed' plus prior May/March 2026 packs visible on the live page.</t>
         </is>
       </c>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -11814,6 +12480,9 @@
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -11889,6 +12558,9 @@
           <t>Re-verified 2026-08-01 via WebFetch: landing shows the current 'July 2026 Board Papers' combined pack (21.09 MB) plus the 'Previous board papers' folder link.</t>
         </is>
       </c>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -11964,6 +12636,9 @@
           <t>Board-meetings landing lists dated combined public board packs for May 2026, March 2026 and January 2026 as direct PDFs.</t>
         </is>
       </c>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -12039,6 +12714,9 @@
           <t>Accordion reveals live 2026 meeting books for 21 May, 26 March and 22 January 2026 (plus full history to 2021).</t>
         </is>
       </c>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -12114,6 +12792,9 @@
           <t>Validator (static) found dated_pdfs=13, year_archives=0, meeting_subpages=97.</t>
         </is>
       </c>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -12163,6 +12844,9 @@
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -12212,6 +12896,9 @@
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -12287,6 +12974,17 @@
           <t>Group board landing confirmed HTTP 200 (title 'Group Board meetings :: NHS University Hospitals of Liverpool Group'); 16 Jul 2026, 14 May 2026, 12 Mar 2026 and 15 Jan 2026 UHLG public packs verified as live PDFs, the July pack agenda naming LHCH explicitly.</t>
         </is>
       </c>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>University Hospitals of Liverpool Group joint board (LUHFT + LWH + LHCH)</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>https://www.uhliverpool.nhs.uk/about-us/meet-our-board/trust-board-meetings</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12362,6 +13060,9 @@
           <t>Re-verified 2026-08-01 via WebFetch and curl: the archive is live but thin -- page 1 holds only 'Trust Board Meeting - 2nd April 2026' (26MB) and page 2 jumps straight back to 5 June 2025, so no pack has been published for four months and the intervening meetings are absent. URL is correct; the gap is on the trust's side.</t>
         </is>
       </c>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -12437,6 +13138,9 @@
           <t>On the 2025-26 sub-page, confirmed e.g. 'Board of Directors Bundle Part I (Public) - 29 January 2026' and '27 November 2025'.</t>
         </is>
       </c>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12512,6 +13216,9 @@
           <t>Via Playwright on the 2026 tab, confirmed 'UHLG Board of Directors Public Pack - 15 January 2026' (/download_file/20288/423) and '14 May 2026' (/download_file/21451/423).</t>
         </is>
       </c>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12587,6 +13294,9 @@
           <t>Re-verified 2026-08-01: browser-UA curl returns HTTP 200 and the landing carries dozens of inline /download_file/view/&lt;uuid&gt;/1221 pack links (server-side WebFetch got 403). papers_partial is a false negative from the extension-less download handler.</t>
         </is>
       </c>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12660,6 +13370,17 @@
       <c r="O184" t="inlineStr">
         <is>
           <t>Group Board meetings page (Playwright-confirmed) shows a Board papers table with 2024/2025/2026 year folders and a Liverpool Women's archive folder, plus 2025-2026 meeting recordings.</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>University Hospitals of Liverpool Group joint board (LUHFT + LWH + LHCH)</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>https://www.uhliverpool.nhs.uk/about-us/meet-our-board/trust-board-meetings</t>
         </is>
       </c>
     </row>
@@ -12711,6 +13432,9 @@
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr"/>
       <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12786,6 +13510,9 @@
           <t>Two 2026 meetings (Mar 5, Jan 13) and full 2025 set each link to a working agenda+papers PDF on the trust's own eastcheshire.nhs.uk domain.</t>
         </is>
       </c>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -12861,6 +13588,9 @@
           <t>Old URL was an error page; corrected page shows 54 dated 'Agenda and Papers' PDFs (2023-2026).</t>
         </is>
       </c>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -12936,6 +13666,9 @@
           <t>Validator (static) found dated_pdfs=17, year_archives=1, meeting_subpages=42.</t>
         </is>
       </c>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -12985,6 +13718,9 @@
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -13060,6 +13796,9 @@
           <t>Re-verified 2026-08-01 via WebFetch: dated packs listed for 05.02.26, 05.03.26, 02.04.26, 07.05.26, 04.06.26 and 02.07.26. no_papers_visible is a false negative from the numeric /download_file/&lt;id&gt;/1439 handler carrying no .pdf suffix.</t>
         </is>
       </c>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13109,6 +13848,9 @@
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
       <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13184,6 +13926,9 @@
           <t>27 May 2026 board summary links to a live full agenda-pack PDF (PUBLIC_BoD_Agenda_Pack_Final_27_05_2026.pdf).</t>
         </is>
       </c>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -13259,6 +14004,9 @@
           <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: WebFetch logged OK on 2026-07-13 (6 forward dates), the scanner holds 9 forward dates (Aug 2026-Mar 2027), and it downloaded + analysed the 2 Jul 2026 pack via /download_file/12115/2316. Landing URL correct.</t>
         </is>
       </c>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -13308,6 +14056,9 @@
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13383,6 +14134,9 @@
           <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: WebFetch logged OK on 2026-07-13 (earlier 404 no longer occurs), the scanner holds 4 forward dates (Sep 2026-Mar 2027), and it downloaded + analysed the 8 Jul 2026 pack via /download_file/30649/191. Landing URL correct. Note the path was corrected to /about-us/our-trust-board/... — the older /about-us/board-meetings-... path 404s.</t>
         </is>
       </c>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13432,6 +14186,9 @@
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13507,6 +14264,9 @@
           <t>Confirmed dated meeting links e.g. 'Public Board of Directors Meeting - Wednesday 28 January 2026' and 'Wednesday 1 October 2025', each resolving to its own publications sub-page of PDFs.</t>
         </is>
       </c>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -13582,6 +14342,9 @@
           <t>Archive page lists dated board-paper sub-pages through to March/May 2026.</t>
         </is>
       </c>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -13657,6 +14420,9 @@
           <t>New board-meetings page lists dated meetings with direct PDF packs up to 29 April 2026.</t>
         </is>
       </c>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -13732,6 +14498,9 @@
           <t>Per-meeting sub-pages (e.g. 26 March 2026) host the full set of dated agenda-item PDFs under /media/.</t>
         </is>
       </c>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -13781,6 +14550,9 @@
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -13856,6 +14628,9 @@
           <t>Dated 2025 and 2026 agenda and minutes sub-pages are listed and reachable, but agenda pages show paper titles only and direct readers to email for the actual board-pack PDFs.</t>
         </is>
       </c>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -13931,6 +14706,9 @@
           <t>Dated 2025-2026 board reports are published as individual HTML report pages (no PDFs) reachable via the minutes-archive index.</t>
         </is>
       </c>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -14006,6 +14784,9 @@
           <t>Live archive links directly to dated combined board pack PDFs in /wp-content/uploads/ for Feb 2025 through Apr 2026.</t>
         </is>
       </c>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -14081,6 +14862,9 @@
           <t>Re-verified 2026-08-01 via WebFetch: the board page lists the 2026/27 meeting schedule (2 Apr, 3 Jun, 3 Sep, 28 Oct AGM, 5 Nov 2026, 4 Mar 2027) but the paper tables render empty, exactly as expected -- they are serverSide Document Library Pro widgets whose rows arrive by AJAX and never exist in the HTML source. Landing URL correct.</t>
         </is>
       </c>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14156,6 +14940,9 @@
           <t>Flat landing page lists 2025-26 dated Board-in-Public agenda packs and a 7 May 2026 pack PDF downloaded successfully (exceeded 10MB fetch limit, confirming a real large PDF).</t>
         </is>
       </c>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -14205,6 +14992,9 @@
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -14242,6 +15032,9 @@
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr"/>
       <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01: plain curl with a browser User-Agent returns HTTP 200 and the landing lists the current pack 'Board paper 30th July 2026' (/documents/512-board-paper-30th-july-2026) plus a /board-papers sub-page. Server-side WebFetch was refused 403 on this run and the scanner saw a connection reset, so the block is route-specific, not a dead page.</t>
+          <t>Re-checked 2026-08-08: URL unchanged and confirmed live - the search index still returns this exact path as the trust's 'Board Meetings and Papers' page, with a /board-papers child listing dated packs. All fetch routes tried today failed at the network layer (requests and local headless Playwright both ERR_CONNECTION_RESET, server-side WebFetch also reset, and the browser-User-Agent retry that worked on 2026-08-01 was reset too), so the WAF is currently more aggressive than last week. Treated as a fetch block, not a stale URL; no change made.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -827,7 +827,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: 'Meetings in public' lists 'Meeting papers: 23 July 2026' and '9 July 2026' newest-first plus forward dates to March 2027. The papers_partial classification is a false negative -- packs sit one hop down on the per-meeting sub-pages, so the landing itself carries no dated PDF links.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: flat 'Meeting papers: &lt;date&gt;' list current through 23 July 2026 (also 9 Jul, 14 May, 12 Mar, 12 Feb 2026) with the archive reaching back to April 2014. The papers_partial classification is a false negative - each date is a sub-page, so few PDFs are linked directly on the landing.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: the July 2026 'Board in Common' set is present as three direct PDFs (content/doclib/14558-14560.pdf: agenda, meeting papers, public information pack) with the year dropdown back ~5 years. Static fetch reaches the current pack; Playwright is only needed to enumerate the historic archive.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: the August 2026 'Board in Common' triplet is served statically on the landing (content/doclib/14565-14567.pdf: public agenda, meeting papers, information pack). Only the historic-year dropdown needs JS, so the needs_playwright classification is a false positive for current packs.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-08-01: no fetch route reached the board path this run -- local requests, local Playwright, browser-UA curl and server-side WebFetch all got a connection reset, while the site root answered 200 intermittently (www.combined.nhs.uk is fronted by ddosx.com). Google's index still carries the landing plus a /board-meetings/board-meeting-archive/trust-board-meeting-july-2026/ page and a January 2026 pack PDF, so the page is live and the URL correct; treat the resets as DDoSX bot mitigation, not rot.</t>
+          <t>Re-checked 2026-08-08: URL unchanged and confirmed live - search index returns /about/our-board/board-meetings/ as the current page plus a board-meeting-archive child holding the July 2026 meeting, and a Jan 2026 pack at /wp-content/uploads/2026/01/. Every fetch route reset at the network layer today (requests, local Playwright, WebFetch), so this is a fetch block, not a stale URL; no change made.</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Human landing uhb.nhs.uk/about/trust-management/bod/papers/ re-confirmed as still pointing at the docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD Nextcloud share; the share itself remains JS-rendered so static scans see nothing.</t>
+          <t>Re-verified 2026-08-08: the Nextcloud public share returns HTTP 200 but its static HTML carries no file listing or dates, exactly as recorded - the file tree is JS-rendered, which is what produces the no_papers_visible classification. URL correct; Playwright still required to enumerate the year/month folders.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -5139,7 +5139,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: 23 July 2026 boardbook linked (/wp-content/uploads/2026/07/Public-BOD-23.7.26-Boardbook-v1.pdf) with forward dates 24 Sep, 25 Nov 2026, 28 Jan and 24 Mar 2027. Server-rendered -- no Playwright needed for the landing.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: landing is server-rendered with the 23 July 2026 boardbook live at /wp-content/uploads/2026/07/Public-BOD-23.7.26-Boardbook-v1.pdf and forward dates 24 Sep, 25 Nov 2026, 28 Jan and 24 Mar 2027, plus per-year 'previous meetings' links back to 2017. needs_playwright is a false positive.</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -6161,7 +6161,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: the 2026 table carries 'Agenda and Papers' links for 15 Jan, 12 Mar, 14 May and 9 Jul 2026, with 10 Sep and 12 Nov 2026 pending. no_papers_visible is a false negative -- the links are CMS handlers without a .pdf suffix and the historic years sit in client-side accordions.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: landing lists the 2026 Board of Directors dates with 'Agenda &amp; Papers' live for 15 Jan, 12 Mar, 14 May and 9 Jul 2026 (10 Sep and 12 Nov pending), plus year accordions back to 2015. The no_papers_visible classification is a false negative from the collapsed accordions.</t>
         </is>
       </c>
       <c r="P80" t="inlineStr"/>
@@ -7462,12 +7462,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.uhbw.nhs.uk/p/about-us/trust-board-meetings</t>
+          <t>https://www.bristolft.nhs.uk/about-us/our-board/board-meetings</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>The registered URL /about-us/board-papers/ is wrong and 500s; the real landing is /p/about-us/trust-board-meetings (older archive at /p/historic-meeting-papers-1). At scan time the entire uhbw.nhs.uk site returned an ASP.NET 'Runtime Error' (transient site-wide outage, not a moved page, since /assets/1/ still served PDFs with HTTP 200). UHBW now meets jointly with North Bristol NHS Trust, so packs are titled 'Public Group Board Meeting' or 'meeting in common (UHBW &amp; NBT)'. Board meets in public every other month; papers published ~1 week before. PDFs sit flat in /assets/1/ with free-text filenames (e.g. public_group_board_meeting_13012026_papers.pdf). Needs render: the landing is ASP.NET/JS, so a crawler should retry the landing when the site recovers and scrape /assets/1/ links, or discover PDFs via site-search. Prefer the single combined '...papers' bundle per meeting; filter out Council of Governors packs, separate agendas, and minutes-only files. Update 2026-08-01: the site-wide ASP.NET 'Runtime Error' seen on 2026-07-30 has cleared and the landing serves normally again.</t>
+          <t>URL PATCHED 2026-08-08: UHBW and North Bristol NHS Trust legally combined on 1 July 2026 to form Bristol NHS Foundation Trust, and the old landing /p/about-us/trust-board-meetings on uhbw.nhs.uk now serves only a redirect notice ("We're moving content to our new website") pointing at www.bristolft.nhs.uk/about-us/our-board/board-meetings. That new page is the live board archive: static server-rendered, no Playwright, listing each dated public board meeting with a 'Board papers published' link to a single combined PDF under /sites/default/files/&lt;yyyy-mm&gt;/ plus a YouTube recording link. Board meets roughly every other month (14 Jul 2026 papers live; forward dates 8 Sep, 10 Nov 2026, 12 Jan, 9 Mar 2027) and papers publish about a week before, under press embargo until the meeting. Months with no public meeting may still post a standalone Integrated Quality Performance Report - that is not a board pack. The legacy UHBW archive (uhbw.nhs.uk /p/historic-meeting-papers-1 and the flat /assets/1/ PDF store, filenames like public_group_board_meeting_13012026_papers.pdf) still resolves and remains the only source for pre-July-2026 UHBW/group packs, so keep it for backfill. Note the sibling entry RVJ (North Bristol) still points at nbt.nhs.uk, which was still serving papers at this scan - both entries will need repointing to the single Bristol FT board once NBT's pages retire; flagged for manual review.</t>
         </is>
       </c>
       <c r="J99" t="b">
@@ -7475,17 +7475,17 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>public_group_board_meeting;board_meeting_in_common_uhbw;agenda_and_papers;_papers.pdf;/assets/1/</t>
+          <t>'Board papers published' link on each dated meeting;/sites/default/files/&lt;yyyy-mm&gt;/*Board*Meeting*.pdf;legacy UHBW backfill: /assets/1/public_group_board_meeting_&lt;ddmmyyyy&gt;_papers.pdf</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>council_of_governors;minutes;error.aspx;attending-board-meetings</t>
+          <t>Integrated Quality Performance Report (standalone, non-meeting months);council_of_governors;minutes;meeting recording / YouTube links;attending-board-meetings</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: the site-wide ASP.NET runtime error seen on 2026-07-30 has cleared. /p/about-us/trust-board-meetings loads, shows papers plus a recording for 12 May 2026 and forward dates 14 Jul, 8 Sep, 10 Nov 2026, and states papers appear about a week before each meeting under press embargo until the meeting.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: the old uhbw.nhs.uk landing now returns only a migration notice, so the URL was repointed to www.bristolft.nhs.uk/about-us/our-board/board-meetings, which confirms the 1 July 2026 NBT+UHBW merger into Bristol NHS Foundation Trust and lists the 14 Jul 2026 pack plus forward dates to 9 Mar 2027.</t>
         </is>
       </c>
       <c r="P99" t="inlineStr"/>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: forthcoming meetings 2 Jul, 3 Sep, 5 Nov 2026 and 7 Jan 2027 listed, archive dropdown runs from Jan 2020 to June 2026. no_papers_visible is a false negative -- packs live on the per-month /about/trustboard/YYYY_MM/ pages, not the index.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: legacy ASP landing is current - forward dates 2 Jul, 3 Sep, 5 Nov 2026 and 7 Jan, 4 Mar 2027, with the July 2026 agenda-and-papers link live and the month dropdown reaching back to January 2020.</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: fiscal-year sections from 2026/27 back to 2019/20, with 'Agenda and papers' links for 4 June 2026 and 2 April 2026. no_papers_visible is a false negative caused by the extension-less /download_file/view/&lt;uuid&gt;/668 handler.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: fiscal-year archive current, with '6 August 2026 - Agenda', '4 June 2026 - Agenda and papers' and '2 April 2026 - Agenda and papers' at the top and coverage back to May 2019 via the /download_file/view/&lt;uuid&gt;/668 handler.</t>
         </is>
       </c>
       <c r="P137" t="inlineStr"/>
@@ -10957,7 +10957,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: the scanner holds 5 forward dates (Aug-Dec 2026) and downloaded + analysed the 3 Jul 2026 pack straight from fhft.nhs.uk/application/files/, so the site IS reachable server-side. Landing URL correct.</t>
+          <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: the scanner holds 5 forward dates (Aug-Dec 2026) and downloaded + analysed the 3 Jul 2026 pack straight from fhft.nhs.uk/application/files/, so the site IS reachable server-side. Landing URL correct. || Re-probed 2026-08-08: server-side WebFetch also returned the empty Imperva/Incapsula shell today, so the challenge is currently being served to that route as well. This does NOT retire the recorded server-side route - the board-paper-machine's confirmed pulls from fhft.nhs.uk/application/files/ stand as the last positive evidence. Landing URL correct; keep trying WebFetch first.</t>
         </is>
       </c>
       <c r="P149" t="inlineStr"/>
@@ -11675,7 +11675,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01: browser-UA curl returns the full 292KB page with meetings 14 Jan, 4 Mar, 6 May, 8 Jul, 2 Sep and 4 Nov 2026 plus the 2025/26 archive. Server-side WebFetch was still answered with a synthetic HTTP 502 -- the edge's ClaudeBot block is unchanged, so use curl/requests rather than WebFetch here.</t>
+          <t>Re-verified 2026-08-08: plain fetch with a browser User-Agent returns HTTP 200 (292KB) with meetings listed through August 2026, while server-side WebFetch again got the synthetic HTTP 502 the edge serves to ClaudeBot - the recorded User-Agent quirk reproduces exactly. URL correct; use curl/requests with a browser UA, not WebFetch.</t>
         </is>
       </c>
       <c r="P161" t="inlineStr"/>
@@ -11917,7 +11917,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: combined public bundles linked for 4 Feb, 1 Apr, 17 Jun and 5 Aug 2026 under /media/board/Papers/2026/. no_papers_visible is a false negative -- the hrefs are space-encoded .pdf paths the classifier missed.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: 2026 public meetings listed with 'Meeting papers' PDFs live for 04 Feb, 01 Apr, 17 Jun and 05 Aug 2026 (07 Oct and 02 Dec pending), plus a separate prior-year archive section.</t>
         </is>
       </c>
       <c r="P164" t="inlineStr"/>
@@ -12545,7 +12545,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: landing shows the current 'July 2026 Board Papers' combined pack (21.09 MB) plus the 'Previous board papers' folder link.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: landing carries the current combined pack ('July 2026 Board Papers', 21.09 MB) plus the 'Previous board papers' folder for earlier meetings. papers_partial simply reflects that only the latest pack sits on the landing.</t>
         </is>
       </c>
       <c r="P173" t="inlineStr"/>
@@ -13047,7 +13047,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch and curl: the archive is live but thin -- page 1 holds only 'Trust Board Meeting - 2nd April 2026' (26MB) and page 2 jumps straight back to 5 June 2025, so no pack has been published for four months and the intervening meetings are absent. URL is correct; the gap is on the trust's side.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: the publications_type archive is live and pagination works (page 2 of 12 renders). The most recent pack on the landing is still Trust Board Meeting 2 April 2026 (26MB) - unchanged from last week, so no pack appears to have been published for the May-July 2026 meetings. URL is correct; the gap is a publishing question for the trust, not a data error.</t>
         </is>
       </c>
       <c r="P180" t="inlineStr"/>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: dated packs listed for 05.02.26, 05.03.26, 02.04.26, 07.05.26, 04.06.26 and 02.07.26. no_papers_visible is a false negative from the numeric /download_file/&lt;id&gt;/1439 handler carrying no .pdf suffix.</t>
+          <t>Re-verified 2026-08-08 via WebFetch: newest-first pack list current through 'Board of Directors Meeting Papers - 02.07.2026', with six 2026 packs (05.02, 05.03, 02.04, 07.05, 04.06, 02.07) and year grouping back to 2020.</t>
         </is>
       </c>
       <c r="P190" t="inlineStr"/>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>27 May 2026 board summary links to a live full agenda-pack PDF (PUBLIC_BoD_Agenda_Pack_Final_27_05_2026.pdf).</t>
+          <t>Re-checked 2026-08-08: URL unchanged. WebFetch returned HTTP 403 and local requests/Playwright were connection-reset, consistent with the recorded Cloudflare block; the search index still shows the board summaries index and per-meeting summary pages live under cwp.nhs.uk. Fetch block, not a stale URL.</t>
         </is>
       </c>
       <c r="P192" t="inlineStr"/>
@@ -14001,7 +14001,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: WebFetch logged OK on 2026-07-13 (6 forward dates), the scanner holds 9 forward dates (Aug 2026-Mar 2027), and it downloaded + analysed the 2 Jul 2026 pack via /download_file/12115/2316. Landing URL correct.</t>
+          <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: WebFetch logged OK on 2026-07-13 (6 forward dates), the scanner holds 9 forward dates (Aug 2026-Mar 2027), and it downloaded + analysed the 2 Jul 2026 pack via /download_file/12115/2316. Landing URL correct. || Re-probed 2026-08-08: server-side WebFetch also returned the empty Imperva/Incapsula shell today. The recorded working route stands - the board-paper-machine's 2 Jul 2026 pack pull via /download_file/12115/2316 remains the last positive evidence. Landing URL correct; keep trying WebFetch first.</t>
         </is>
       </c>
       <c r="P193" t="inlineStr"/>
@@ -14131,7 +14131,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: WebFetch logged OK on 2026-07-13 (earlier 404 no longer occurs), the scanner holds 4 forward dates (Sep 2026-Mar 2027), and it downloaded + analysed the 8 Jul 2026 pack via /download_file/30649/191. Landing URL correct. Note the path was corrected to /about-us/our-trust-board/... — the older /about-us/board-meetings-... path 404s.</t>
+          <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: WebFetch logged OK on 2026-07-13 (earlier 404 no longer occurs), the scanner holds 4 forward dates (Sep 2026-Mar 2027), and it downloaded + analysed the 8 Jul 2026 pack via /download_file/30649/191. Landing URL correct. Note the path was corrected to /about-us/our-trust-board/... — the older /about-us/board-meetings-... path 404s. || Re-probed 2026-08-08: server-side WebFetch also returned the empty Imperva/Incapsula shell today. The recorded working route stands - the board-paper-machine's 8 Jul 2026 pack pull via /download_file/30649/191 remains the last positive evidence. Landing URL correct; keep trying WebFetch first.</t>
         </is>
       </c>
       <c r="P195" t="inlineStr"/>
@@ -14849,7 +14849,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: the board page lists the 2026/27 meeting schedule (2 Apr, 3 Jun, 3 Sep, 28 Oct AGM, 5 Nov 2026, 4 Mar 2027) but the paper tables render empty, exactly as expected -- they are serverSide Document Library Pro widgets whose rows arrive by AJAX and never exist in the HTML source. Landing URL correct.</t>
+          <t>Re-verified 2026-08-08 via direct fetch: /about-scas/our-board/ returns HTTP 200 with the 2026 board meeting schedule (Apr, Jun, Sep, Oct, Nov 2026) in the HTML. The paper tables remain serverSide AJAX widgets whose rows never appear in source, which is what drives the no_papers_visible classification. URL correct.</t>
         </is>
       </c>
       <c r="P205" t="inlineStr"/>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Re-checked 2026-08-08: URL unchanged and confirmed live - the search index still returns this exact path as the trust's 'Board Meetings and Papers' page, with a /board-papers child listing dated packs. All fetch routes tried today failed at the network layer (requests and local headless Playwright both ERR_CONNECTION_RESET, server-side WebFetch also reset, and the browser-User-Agent retry that worked on 2026-08-01 was reset too), so the WAF is currently more aggressive than last week. Treated as a fetch block, not a stale URL; no change made.</t>
+          <t>2026-08-15: the local deep scan got a connection reset and server-side WebFetch also reset, so the intermittent WAF was active on both paths this run. No evidence the URL moved - the shallow check still returned HTTP 200.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -827,17 +827,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>papers_partial</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: flat 'Meeting papers: &lt;date&gt;' list current through 23 July 2026 (also 9 Jul, 14 May, 12 Mar, 12 Feb 2026) with the archive reaching back to April 2014. The papers_partial classification is a false negative - each date is a sub-page, so few PDFs are linked directly on the landing.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: Meetings in public page live; most recent papers 23 July 2026, forthcoming meetings 16 Sep and 12 Nov 2026. Papers sit behind a dropdown selector, which is why the validator sees only a partial signal.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>June 2026 meeting page lists ~35 board paper PDFs (agenda, CEO report, finance, quality) all live on ashfordstpeters.info.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: /board-meetings is live, indexing Trust Board meetings back to 2013 including 22 July 2026, 3 June 2026 and 25 March 2026 as per-meeting sub-pages. The local deep-scan 403 was a WAF false positive.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Live packs present for June 2026 (open-meeting-pack 04.06.26) and April/February 2026 plus full back-catalogue to 2024.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: Board of Directors page live with meeting packs to 28 July 2026 under /s3/assets/files/board_of_directors_docs/bod-meeting-packs/. The local scan SSL-verify failure was a false positive.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1973,13 +1973,39 @@
           <t>https://www.lpft.nhs.uk/get-involved/meeting-dates-and-minutes/board-directors-meetings</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Strategy: the landing (/get-involved/meeting-dates-and-minutes/board-directors-meetings) is a schedule-plus-folders page, not a flat PDF list. It carries the forward meeting timetable (Feb 2026 through Feb 2027) and states that agenda and papers are posted roughly seven days before each meeting. The packs themselves sit one hop down in a 'Previous meetings' folder and per-year folders (2025, 2026) that must be opened to reach the dated agenda/report PDFs; past meetings are also recorded on YouTube. Static fetch works via server-side WebFetch - the local deep scan's SSL-verify failure on lpft.nhs.uk is a local-path artefact, not a dead page. Crawl the landing for the schedule, then follow the year/previous-meetings folder links for packs.</t>
+        </is>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Agenda;Board of Directors;Trust Board;papers</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Minutes only;Council of Governors;Annual General Meeting</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Verified 2026-08-15 via WebFetch: Board of Directors Meetings page live, listing the 2026-27 meeting schedule (Feb 2026 through Feb 2027) plus folders holding past packs. The local SSL-verify failure was a false positive.</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -2677,7 +2703,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Despite the prior needs_playwright flag, the current board pack renders server-side and is reachable by a plain static fetch: the landing shows the latest 'Board in Common' set (agenda, meeting papers, public information pack) as direct PDF links. What static fetch misses is only the historical archive: older meetings (2015 onward) are selected via a JavaScript dropdown/postback that swaps the visible links, so Playwright is only needed to enumerate prior years -- load the page, select a year, wait for the link list to re-render, then harvest the /content/doclib/&lt;id&gt;.pdf links. The most recent packs need no JS.</t>
+          <t>Despite the prior needs_playwright flag, the current board pack renders server-side and is reachable by a plain static fetch: the landing shows the latest 'Board in Common' set (agenda, meeting papers, public information pack) as direct PDF links. What static fetch misses is only the historical archive: older meetings (2015 onward) are selected via a JavaScript dropdown/postback that swaps the visible links, so Playwright is only needed to enumerate prior years -- load the page, select a year, wait for the link list to re-render, then harvest the /content/doclib/&lt;id&gt;.pdf links. The most recent packs need no JS. Route check 2026-08-15: server-side WebFetch returned an empty body this run, so the static path that worked previously is intermittent rather than reliably open - retry it first, then fall back to a browser render. The landing URL itself is unchanged (shallow check HTTP 200).</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -3007,7 +3033,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3017,7 +3043,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Current URL /our-organisation/trust-board-meetings/ returns HTTP 200 and is the canonical 'Trust Board Meetings' page; 2026 combined public board packs (2 April 2026, 4 June 2026) are indexed under the site's own /download/clientfiles/files/ path. Shallow-check failure was a WAF connection reset.</t>
+          <t>2026-08-15: local deep scan and server-side WebFetch both hit connection resets, so the uhcw.nhs.uk WAF was active on both paths this run. The shallow check still returned HTTP 200, so the URL is unchanged.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -4229,7 +4255,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4239,7 +4265,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=59, year_archives=0, meeting_subpages=6.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: Our Board of Directors page live with year-grouped packs, latest July 2026 via /download_file/view/16137/240. The local connection-reset was a WAF false positive.</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
@@ -4367,7 +4393,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>HARDEST KNOWN CASE - two separate problems, both solved. (1) The whole host sits behind a WAF that returns HTTP 403 (a ~784KB error page) to curl, requests, WebFetch, real-Chrome-headful AND the full anti-automation recipe (stealth init script, disable-blink-features, site-root-first for cookies, ctx.request.get with Referer); after a few attempts it escalates to resetting the TLS connection outright, i.e. an IP-level block. (2) Documents are served from /media/&lt;id&gt;/&lt;url-encoded title&gt; with NO FILE EXTENSION, so any crawler keying on '.pdf' or '/download' finds zero links even on a page it can read. WHAT WORKS: fetch through Archive.org Save Page Now - GET https://web.archive.org/save/&lt;url&gt;. Archive.org crawls from its own infrastructure so the IP block does not apply. This works for BOTH the landing page (returns 31 document links incl. the full back-archive) and for the document URLs themselves (the response body is the PDF bytes - check for %PDF and strip any prefix). Verified 5 Aug 2026 on the 22 July 2026 board pack (8MB) and agenda (163KB). Match documents with the pattern guysandstthomas.nhs.uk/media/&lt;digits&gt;/ - NOT a .pdf extension.</t>
+          <t>HARDEST KNOWN CASE - two separate problems, both solved. (1) The whole host sits behind a WAF that returns HTTP 403 (a ~784KB error page) to curl, requests, WebFetch, real-Chrome-headful AND the full anti-automation recipe (stealth init script, disable-blink-features, site-root-first for cookies, ctx.request.get with Referer); after a few attempts it escalates to resetting the TLS connection outright, i.e. an IP-level block. (2) Documents are served from /media/&lt;id&gt;/&lt;url-encoded title&gt; with NO FILE EXTENSION, so any crawler keying on '.pdf' or '/download' finds zero links even on a page it can read. WHAT WORKS: fetch through Archive.org Save Page Now - GET https://web.archive.org/save/&lt;url&gt;. Archive.org crawls from its own infrastructure so the IP block does not apply. This works for BOTH the landing page (returns 31 document links incl. the full back-archive) and for the document URLs themselves (the response body is the PDF bytes - check for %PDF and strip any prefix). Verified 5 Aug 2026 on the 22 July 2026 board pack (8MB) and agenda (163KB). Match documents with the pattern guysandstthomas.nhs.uk/media/&lt;digits&gt;/ - NOT a .pdf extension. Route check 2026-08-15: server-side WebFetch reached the Agenda and papers page cleanly this run and enumerated the year-grouped meetings to 22 July 2026 - so WebFetch is worth trying FIRST before the archive.org Save Page Now route recorded above, which remains the reliable fallback. Local requests/Playwright still get the 403.</t>
         </is>
       </c>
       <c r="J56" t="b">
@@ -4385,7 +4411,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4395,7 +4421,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Board meets quarterly. 22 July 2026 pack (97pp) and agenda retrieved via Archive.org Save Page Now on 5 Aug 2026; landing page also lists packs back to January 2024. Next meeting 21 October 2026.</t>
+          <t>Re-verified 2026-08-15: WebFetch reached the Agenda and papers page this run (year-grouped meetings 2023-2026, latest 22 July 2026) - the WAF that previously 403'd every fetcher was not blocking server-side WebFetch today. The local 403 persists.</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -5139,7 +5165,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5149,7 +5175,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: landing is server-rendered with the 23 July 2026 boardbook live at /wp-content/uploads/2026/07/Public-BOD-23.7.26-Boardbook-v1.pdf and forward dates 24 Sep, 25 Nov 2026, 28 Jan and 24 Mar 2027, plus per-year 'previous meetings' links back to 2017. needs_playwright is a false positive.</t>
+          <t>2026-08-15: WebFetch returned an empty body this run while the shallow check returned HTTP 200. The landing is unchanged - retry static fetch or use a browser render.</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -5347,7 +5373,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5357,7 +5383,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Latest pack '06 May 2026 Public Board of Directors Meeting papers' plus full back-catalogue of combined PDFs visible on the live page.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: year-tabbed board archive live, latest Public Board pack 1 July 2026 under /wp-content/uploads/2026/07/. The local 403 was a WAF false positive.</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
@@ -6161,7 +6187,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6171,7 +6197,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: landing lists the 2026 Board of Directors dates with 'Agenda &amp; Papers' live for 15 Jan, 12 Mar, 14 May and 9 Jul 2026 (10 Sep and 12 Nov pending), plus year accordions back to 2015. The no_papers_visible classification is a false negative from the collapsed accordions.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: 2026 Board of Directors table live with Combined Public Board PDFs to 9 July 2026 under /fileadmin/.../BoardPapers/2026/. The no_papers_visible result was a false negative from the collapsed year accordions.</t>
         </is>
       </c>
       <c r="P80" t="inlineStr"/>
@@ -6369,7 +6395,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6379,7 +6405,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Recent 2026 public board packs (30 June, 28 April, 31 March) linked as direct PDFs.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: meeting-papers page live, latest Public agenda and papers 28 July 2026 under /wp-content/uploads/2026/07/. The local 403 was a WAF false positive.</t>
         </is>
       </c>
       <c r="P83" t="inlineStr"/>
@@ -7061,7 +7087,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7071,7 +7097,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: landing is the year index (2017-2026) with the 2026 sub-page linked; page footer stamped 01-08-2026. Local requests and Playwright still get ERR_CONNECTION_RESET -- WebFetch remains the working route.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: year-index page live listing 2017-2026 sub-pages. The local connection-reset was a WAF false positive; WebFetch reaches it cleanly.</t>
         </is>
       </c>
       <c r="P93" t="inlineStr"/>
@@ -7485,7 +7511,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7495,7 +7521,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: the old uhbw.nhs.uk landing now returns only a migration notice, so the URL was repointed to www.bristolft.nhs.uk/about-us/our-board/board-meetings, which confirms the 1 July 2026 NBT+UHBW merger into Bristol NHS Foundation Trust and lists the 14 Jul 2026 pack plus forward dates to 9 Mar 2027.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: Bristol NHS FT board-meetings page live, July 2026 pack published plus an Aug-26 IQPR under /sites/default/files/2026-0X/. Predecessor NBT/UHBW archives are still linked.</t>
         </is>
       </c>
       <c r="P99" t="inlineStr"/>
@@ -7701,7 +7727,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7711,7 +7737,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: legacy ASP landing is current - forward dates 2 Jul, 3 Sep, 5 Nov 2026 and 7 Jan, 4 Mar 2027, with the July 2026 agenda-and-papers link live and the month dropdown reaching back to January 2020.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: legacy ASP board page live listing meetings to 3 September 2026; the month sub-pages (e.g. /about/trustboard/2026_07/index.asp) carry the packs, so the landing itself holding no PDFs explains the no_papers_visible result.</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -7857,7 +7883,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7867,7 +7893,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Current-year page (BoardMeetings2526.aspx) lists 'Agenda Pack Trust Board in Public March 2026' and full monthly back-catalogue of agenda packs.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: landing live and still indexing per-financial-year .aspx pages on doclibrary-rcht.cornwall.nhs.uk (BoardMeetings2627.aspx is current). The local 403 was a WAF false positive.</t>
         </is>
       </c>
       <c r="P104" t="inlineStr"/>
@@ -7915,13 +7941,39 @@
           <t>https://www.somersetft.nhs.uk/about-us/trust-board-meetings/</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing under year headings ('2026 Board Papers', '2025 Board Papers', '2024 board papers') - no year tabs, no per-meeting sub-pages. Each entry links straight to a combined 'Boardbook' PDF in the WordPress media library at /about-us/wp-content/uploads/sites/148/YYYY/MM/. Latest confirmed 14 July 2026. Note two quirks: large meetings are occasionally split into PART 1 / PART 2 files (take both), and the odd entry links a .docx agenda rather than a PDF. Extraordinary meetings appear inline alongside ordinary ones. Static fetch works via server-side WebFetch; the local scan's read-timeout is a local-path artefact. Prefer filenames containing 'Boardbook'.</t>
+        </is>
+      </c>
+      <c r="J105" t="b">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Boardbook;Public Board Meeting;FINAL Boardbook for website</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Extraordinary;Agenda only;.docx</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Verified 2026-08-15 via WebFetch: Trust board meetings page live with year-grouped Boardbook PDFs, latest 14 July 2026 under /about-us/wp-content/uploads/sites/148/2026/07/. The local read-timeout was a false positive.</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
       <c r="R105" t="inlineStr"/>
@@ -7987,7 +8039,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7997,7 +8049,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Three 2026 meeting packs (27 May, 25 Mar, 28 Jan) plus minutes listed inline on the live page, last updated June 2026.</t>
+          <t>2026-08-15: WebFetch returned HTTP 403 as recorded; the shallow check returned HTTP 200. Playwright and the archive.org Save Page Now route remain the working paths - do not read this as unreachable.</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -8943,7 +8995,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8953,7 +9005,7 @@
       </c>
       <c r="O121" t="inlineStr">
         <is>
-          <t>WAF returns 403/500 to bots; Google confirms URL is the live 'Trust board meetings' page.</t>
+          <t>2026-08-15: WebFetch returned HTTP 403, matching the recorded anti-bot behaviour; the shallow check returned HTTP 200 so the URL stands. Browser/Playwright remains the working route.</t>
         </is>
       </c>
       <c r="P121" t="inlineStr"/>
@@ -10111,7 +10163,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10121,7 +10173,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: fiscal-year archive current, with '6 August 2026 - Agenda', '4 June 2026 - Agenda and papers' and '2 April 2026 - Agenda and papers' at the top and coverage back to May 2019 via the /download_file/view/&lt;uuid&gt;/668 handler.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: Board papers page live with fiscal-year groups, latest 6 August 2026 agenda via /download_file/view/&lt;uuid&gt;/668. The no_papers_visible result was a false negative.</t>
         </is>
       </c>
       <c r="P137" t="inlineStr"/>
@@ -10929,7 +10981,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>The URL is valid. The near-empty body is NOT client-side JS — the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to traffic it scores as automated. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Packs are combined PDFs under /application/files/ (pattern 'FHFT_Public_Bd_&lt;D.MM.YY&gt;_v1.pdf'). Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk). ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback.</t>
+          <t>The URL is valid. The near-empty body is NOT client-side JS — the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to traffic it scores as automated. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Packs are combined PDFs under /application/files/ (pattern 'FHFT_Public_Bd_&lt;D.MM.YY&gt;_v1.pdf'). Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk). ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously pulled this domain's pages and packs fine. Keep trying WebFetch first and only escalate to a captcha-solving / residential session if it fails again. Landing URL unchanged (shallow check HTTP 200).</t>
         </is>
       </c>
       <c r="J149" t="b">
@@ -11675,7 +11727,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11685,7 +11737,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08: plain fetch with a browser User-Agent returns HTTP 200 (292KB) with meetings listed through August 2026, while server-side WebFetch again got the synthetic HTTP 502 the edge serves to ClaudeBot - the recorded User-Agent quirk reproduces exactly. URL correct; use curl/requests with a browser UA, not WebFetch.</t>
+          <t>2026-08-15: WebFetch returned the synthetic HTTP 502 the edge serves to the ClaudeBot User-Agent, exactly as recorded on 2026-07-30; curl and python-requests remain the working route and the shallow check returned HTTP 200.</t>
         </is>
       </c>
       <c r="P161" t="inlineStr"/>
@@ -11917,7 +11969,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11927,7 +11979,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: 2026 public meetings listed with 'Meeting papers' PDFs live for 04 Feb, 01 Apr, 17 Jun and 05 Aug 2026 (07 Oct and 02 Dec pending), plus a separate prior-year archive section.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: Board Papers page live with 2026 public bundles to 5 August 2026 under /media/board/Papers/2026/. The no_papers_visible result was a false negative.</t>
         </is>
       </c>
       <c r="P164" t="inlineStr"/>
@@ -12415,7 +12467,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12425,7 +12477,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>Latest pack '0-Meeting-in-Public 02.07.2026 compressed' plus prior May/March 2026 packs visible on the live page.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: Agendas and Meetings page live, latest Meeting in Public pack 2 July 2026 under /wp-content/uploads/2026/06/. The local 403 was a WAF false positive.</t>
         </is>
       </c>
       <c r="P171" t="inlineStr"/>
@@ -12545,17 +12597,17 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>papers_partial</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: landing carries the current combined pack ('July 2026 Board Papers', 21.09 MB) plus the 'Previous board papers' folder for earlier meetings. papers_partial simply reflects that only the latest pack sits on the landing.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: Board papers page live with the July 2026 pack (21MB) via /download_file/&lt;uuid&gt;/368 plus the Previous board papers folder at /navigate/758/9379. Only one pack sits on the landing, hence the partial signal.</t>
         </is>
       </c>
       <c r="P173" t="inlineStr"/>
@@ -12701,7 +12753,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12711,7 +12763,7 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Accordion reveals live 2026 meeting books for 21 May, 26 March and 22 January 2026 (plus full history to 2021).</t>
+          <t>2026-08-15: WebFetch returned HTTP 403 as expected behind Cloudflare; the shallow check returned HTTP 200. Playwright against the collapsed board-papers accordion remains the working route.</t>
         </is>
       </c>
       <c r="P175" t="inlineStr"/>
@@ -13029,7 +13081,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Live WordPress publications_type archive, statically readable via WebFetch (no Playwright, no 403). Landing lists the most recent Trust Board pack (currently 2 April 2026) and paginates via /publications_type/board-papers/page/N/ (currently 12 pages, ~one pack per page reverse-chronological). Each entry links directly to a single combined agenda+papers PDF under /wp-content/uploads/YYYY/MM/. Prefer the landing for the newest pack; walk /page/2/ etc. for older meetings. Publication gap noted 2026-08-01: the newest pack is still 2 April 2026 and page 2 of the archive jumps back to 5 June 2025, so this archive is sparse and lags -- do not read a missing month as a fetch failure.</t>
+          <t>Live WordPress publications_type archive, statically readable via WebFetch (no Playwright, no 403). Landing lists the most recent Trust Board pack (currently 2 April 2026) and paginates via /publications_type/board-papers/page/N/ (currently 12 pages, ~one pack per page reverse-chronological). Each entry links directly to a single combined agenda+papers PDF under /wp-content/uploads/YYYY/MM/. Prefer the landing for the newest pack; walk /page/2/ etc. for older meetings. Publication gap noted 2026-08-01: the newest pack is still 2 April 2026 and page 2 of the archive jumps back to 5 June 2025, so this archive is sparse and lags -- do not read a missing month as a fetch failure. Update 2026-08-15: the archive is live and paginates to 12 pages, but ordering is by upload date not meeting date (page 1 = 2 Apr 2026, page 2 = 5 Jun 2025), so do not assume strict reverse-chronology - walk several pages before concluding a pack is missing. As of this run no board pack later than 2 April 2026 has been published despite the trust stating the board meets 11 times a year; /about-us/our-board/publications is a 404 and no alternative archive was found, so the gap appears to be a publication lapse rather than a move.</t>
         </is>
       </c>
       <c r="J180" t="b">
@@ -13047,7 +13099,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13057,7 +13109,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: the publications_type archive is live and pagination works (page 2 of 12 renders). The most recent pack on the landing is still Trust Board Meeting 2 April 2026 (26MB) - unchanged from last week, so no pack appears to have been published for the May-July 2026 meetings. URL is correct; the gap is a publishing question for the trust, not a data error.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: the archive is live and paginated (page 2 of 12 reached), but the newest pack published is still Trust Board 2 April 2026 - no May/June/July/August 2026 pack has appeared despite the trust stating the board meets 11 times a year. URL is correct; the gap looks like a publication lapse, not a moved page.</t>
         </is>
       </c>
       <c r="P180" t="inlineStr"/>
@@ -13203,7 +13255,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13213,7 +13265,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>Via Playwright on the 2026 tab, confirmed 'UHLG Board of Directors Public Pack - 15 January 2026' (/download_file/20288/423) and '14 May 2026' (/download_file/21451/423).</t>
+          <t>2026-08-15: WebFetch returned HTTP 403 as expected; the shallow check returned HTTP 200. Playwright against the AJAX year tabs remains the working route.</t>
         </is>
       </c>
       <c r="P182" t="inlineStr"/>
@@ -13575,7 +13627,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13585,7 +13637,7 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>Old URL was an error page; corrected page shows 54 dated 'Agenda and Papers' PDFs (2023-2026).</t>
+          <t>Re-verified 2026-08-15 via WebFetch: meeting-packs page live with dated PAPERS-Board-of-Directors PDFs under /media/, latest 21 July 2026. The local SSL-verify failure was a false positive.</t>
         </is>
       </c>
       <c r="P187" t="inlineStr"/>
@@ -13783,7 +13835,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13793,7 +13845,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: newest-first pack list current through 'Board of Directors Meeting Papers - 02.07.2026', with six 2026 packs (05.02, 05.03, 02.04, 07.05, 04.06, 02.07) and year grouping back to 2020.</t>
+          <t>Re-verified 2026-08-15 via WebFetch: Board papers page live, dated packs via /download_file/&lt;id&gt;/1439 through 4 June 2026. The no_papers_visible result was a false negative.</t>
         </is>
       </c>
       <c r="P190" t="inlineStr"/>
@@ -13913,7 +13965,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13923,7 +13975,7 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Re-checked 2026-08-08: URL unchanged. WebFetch returned HTTP 403 and local requests/Playwright were connection-reset, consistent with the recorded Cloudflare block; the search index still shows the board summaries index and per-meeting summary pages live under cwp.nhs.uk. Fetch block, not a stale URL.</t>
+          <t>2026-08-15: WebFetch returned HTTP 403 as expected behind Cloudflare; the shallow check returned HTTP 200. Playwright remains the working route and /board is still the correct landing.</t>
         </is>
       </c>
       <c r="P192" t="inlineStr"/>
@@ -13973,7 +14025,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). Packs are served through the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix) so extension-based link filters will miss them. The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page — the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path. CAUTION: '31 March 2027' appears only in the heading 'Board meeting schedule to 31 March 2027' — it is not a meeting date. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback.</t>
+          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). Packs are served through the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix) so extension-based link filters will miss them. The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page — the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path. CAUTION: '31 March 2027' appears only in the heading 'Board meeting schedule to 31 March 2027' — it is not a meeting date. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200).</t>
         </is>
       </c>
       <c r="J193" t="b">
@@ -14103,7 +14155,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Once past the wall the page lists scheduled board meetings (Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs; two delivery paths are in use — the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf') and the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix), so extension-based link filters will miss the latter. Accessible versions via TrustBoardQuestions@elht.nhs.uk. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback.</t>
+          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Once past the wall the page lists scheduled board meetings (Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs; two delivery paths are in use — the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf') and the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix), so extension-based link filters will miss the latter. Accessible versions via TrustBoardQuestions@elht.nhs.uk. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200).</t>
         </is>
       </c>
       <c r="J195" t="b">

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -827,17 +827,17 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: Meetings in public page live; most recent papers 23 July 2026, forthcoming meetings 16 Sep and 12 Nov 2026. Papers sit behind a dropdown selector, which is why the validator sees only a partial signal.</t>
+          <t>Re-verified 2026-08-22 and upgraded from papers_partial: flat list of per-meeting sub-pages back to 2014, newest 'Meeting papers: 23 July 2026'.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -2703,11 +2703,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Despite the prior needs_playwright flag, the current board pack renders server-side and is reachable by a plain static fetch: the landing shows the latest 'Board in Common' set (agenda, meeting papers, public information pack) as direct PDF links. What static fetch misses is only the historical archive: older meetings (2015 onward) are selected via a JavaScript dropdown/postback that swaps the visible links, so Playwright is only needed to enumerate prior years -- load the page, select a year, wait for the link list to re-render, then harvest the /content/doclib/&lt;id&gt;.pdf links. The most recent packs need no JS. Route check 2026-08-15: server-side WebFetch returned an empty body this run, so the static path that worked previously is intermittent rather than reliably open - retry it first, then fall back to a browser render. The landing URL itself is unchanged (shallow check HTTP 200).</t>
+          <t>Despite the prior needs_playwright flag, the current board pack renders server-side and is reachable by a plain static fetch: the landing shows the latest 'Board in Common' set (agenda, meeting papers, public information pack) as direct PDF links. What static fetch misses is only the historical archive: older meetings (2015 onward) are selected via a JavaScript dropdown/postback that swaps the visible links, so Playwright is only needed to enumerate prior years -- load the page, select a year, wait for the link list to re-render, then harvest the /content/doclib/&lt;id&gt;.pdf links. The most recent packs need no JS. Route check 2026-08-15: server-side WebFetch returned an empty body this run, so the static path that worked previously is intermittent rather than reliably open - retry it first, then fall back to a browser render. The landing URL itself is unchanged (shallow check HTTP 200). ACCESS CHANGE 2026-08-22: shropscommunityhealth.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) gets the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the static route described above was confirmed working as recently as 2026-08-08, so try server-side WebFetch and a plain static fetch FIRST and only treat the archive as unreachable if those also fail.</t>
         </is>
       </c>
       <c r="J33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via WebFetch: the August 2026 'Board in Common' triplet is served statically on the landing (content/doclib/14565-14567.pdf: public agenda, meeting papers, information pack). Only the historic-year dropdown needs JS, so the needs_playwright classification is a false positive for current packs.</t>
+          <t>Not re-readable from this machine on 2026-08-22 (Imperva/Incapsula shell on requests and on local Playwright). Status carried forward from the 2026-08-08 confirmation that the current 'Board in Common' pack renders server-side; no evidence the archive has moved or stopped.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3225,9 +3225,21 @@
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Landing validator 2026-08-22: papers_found - 1 dated PDFs, 2 year archives, 0 meeting sub-pages visible on the landing (HTTP 200).</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -3449,7 +3461,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3459,7 +3471,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Static page lists dated 2025/2026 board PDFs; confirmed HTTP-200 full public board pack for 20 May 2026 (~22MB).</t>
+          <t>Landing validator 2026-08-22: papers_found - 5 dated PDFs, 1 year archives, 0 meeting sub-pages visible on the landing (HTTP 200).</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -3667,9 +3679,21 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Landing validator 2026-08-22: papers_found - 0 dated PDFs, 25 year archives, 188 meeting sub-pages visible on the landing (HTTP 200).</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -3735,7 +3759,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3745,7 +3769,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08: the Nextcloud public share returns HTTP 200 but its static HTML carries no file listing or dates, exactly as recorded - the file tree is JS-rendered, which is what produces the no_papers_visible classification. URL correct; Playwright still required to enumerate the year/month folders.</t>
+          <t>Playwright re-check 2026-08-22: Nextcloud share renders normally; root lists 18 year folders (2008-2026) and the 2026 folder holds March, June and July month packs (July 31.4MB). The static 'no papers' reading is the known JS false negative.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -4623,7 +4647,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4633,7 +4657,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Page titled 'Group Board Papers and Agenda' lists dated group-board PDFs May 2025 through July 2026 as direct hyperlinks; static fetch resolves every href.</t>
+          <t>Re-verified 2026-08-22: page live with group board packs listed to 9 July 2026 (Group-Board-Public-9-July-2026.pdf) and archive back to 2024; the scan's connection reset was transient (succeeded on the 4th retry from this machine).</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -4935,7 +4959,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4945,7 +4969,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Via Playwright confirmed dated public board packs incl. 'Public Board papers - 19 Nov 2025' and 'Public Board Pack 26.03.2025'; 2026 meeting dates (Mar/Jul/Sep/Nov 2026) also scheduled.</t>
+          <t>Landing validator 2026-08-22: papers_found - 24 dated PDFs, 0 year archives, 0 meeting sub-pages visible on the landing (HTTP 200).</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -5147,11 +5171,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>The board-papers landing /our-trust/bod-meetings/ renders server-side (no JS required): it lists upcoming public board meetings plus 'Previous meetings' links grouped by year (2017-2026). Individual board packs are single combined 'boardbook' PDFs under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler does not need Playwright for the landing page; follow the per-year 'previous meetings' links (or hit the wp-content/uploads path pattern directly) to reach dated packs. Static fetch reaches the index but the actual dated PDFs sit one click deeper on the year sub-pages.</t>
+          <t>The board-papers landing /our-trust/bod-meetings/ renders server-side (no JS required): it lists upcoming public board meetings plus 'Previous meetings' links grouped by year (2017-2026). Individual board packs are single combined 'boardbook' PDFs under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler does not need Playwright for the landing page; follow the per-year 'previous meetings' links (or hit the wp-content/uploads path pattern directly) to reach dated packs. Static fetch reaches the index but the actual dated PDFs sit one click deeper on the year sub-pages. ACCESS CHANGE 2026-08-22: bradfordhospitals.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) returns the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the server-rendered landing described above was confirmed working on 2026-08-15, so try server-side WebFetch and a plain static fetch FIRST before assuming the archive is gone.</t>
         </is>
       </c>
       <c r="J66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5165,7 +5189,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5175,7 +5199,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-08-15: WebFetch returned an empty body this run while the shallow check returned HTTP 200. The landing is unchanged - retry static fetch or use a browser render.</t>
+          <t>Not re-readable from this machine on 2026-08-22 (Imperva/Incapsula shell on requests and on local Playwright). Status carried forward from the 2026-08-15 confirmation of the server-rendered landing plus per-year 'Previous meetings' links; no evidence the archive has moved.</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -6187,7 +6211,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6197,7 +6221,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: 2026 Board of Directors table live with Combined Public Board PDFs to 9 July 2026 under /fileadmin/.../BoardPapers/2026/. The no_papers_visible result was a false negative from the collapsed year accordions.</t>
+          <t>Re-verified 2026-08-22: 2026 meetings to 9 July each carry an 'Agenda and Papers' link; 10 Sept and 12 Nov 2026 listed without packs yet; 2025 archive accordion intact.</t>
         </is>
       </c>
       <c r="P80" t="inlineStr"/>
@@ -7433,7 +7457,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7443,7 +7467,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Confirmed combined 'Board of Director Part 1 Meeting Pack 13 May 2026' PDF and supporting agenda/reading-room files on the our-performance page, with 2026 meeting dates listed through November 2026.</t>
+          <t>Landing validator 2026-08-22: papers_found - 21 dated PDFs, 1 year archives, 0 meeting sub-pages visible on the landing (HTTP 200).</t>
         </is>
       </c>
       <c r="P98" t="inlineStr"/>
@@ -7511,7 +7535,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7521,7 +7545,7 @@
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: Bristol NHS FT board-meetings page live, July 2026 pack published plus an Aug-26 IQPR under /sites/default/files/2026-0X/. Predecessor NBT/UHBW archives are still linked.</t>
+          <t>Re-verified 2026-08-22: 14 July 2026 board pack published on the bristolft.nhs.uk landing; Sept 2026 to Mar 2027 dates listed pending papers.</t>
         </is>
       </c>
       <c r="P99" t="inlineStr"/>
@@ -7581,9 +7605,21 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Landing validator 2026-08-22: papers_found - 14 dated PDFs, 0 year archives, 0 meeting sub-pages visible on the landing (HTTP 200).</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
@@ -7727,7 +7763,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7737,7 +7773,7 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: legacy ASP board page live listing meetings to 3 September 2026; the month sub-pages (e.g. /about/trustboard/2026_07/index.asp) carry the packs, so the landing itself holding no PDFs explains the no_papers_visible result.</t>
+          <t>Re-verified 2026-08-22: month dropdown runs Jan 2020 to June 2026 and the forthcoming 2 July 2026 meeting carries an 'Agenda &amp; Papers' link; legacy ASP pages render statically.</t>
         </is>
       </c>
       <c r="P102" t="inlineStr"/>
@@ -8209,9 +8245,21 @@
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Landing validator 2026-08-22: papers_found - 46 dated PDFs, 0 year archives, 0 meeting sub-pages visible on the landing (HTTP 200).</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
       <c r="R109" t="inlineStr"/>
@@ -8277,7 +8325,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8287,7 +8335,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>board-papers page exposes Board papers 2025 and 2026 year archives, and the 2026 archive lists dated per-meeting sub-pages (8 Jan, 5 Mar, 13 May 2026).</t>
+          <t>Landing validator 2026-08-22: papers_found - 0 dated PDFs, 5 year archives, 0 meeting sub-pages visible on the landing (HTTP 200).</t>
         </is>
       </c>
       <c r="P110" t="inlineStr"/>
@@ -9757,9 +9805,21 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Landing validator 2026-08-22: papers_found - 0 dated PDFs, 3 year archives, 2 meeting sub-pages visible on the landing (HTTP 200).</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
       <c r="R131" t="inlineStr"/>
@@ -9809,9 +9869,21 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Landing validator 2026-08-22: papers_found - 18 dated PDFs, 0 year archives, 3 meeting sub-pages visible on the landing (HTTP 200).</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
       <c r="R132" t="inlineStr"/>
@@ -10017,9 +10089,21 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Landing validator 2026-08-22: papers_found - 13 dated PDFs, 0 year archives, 5 meeting sub-pages visible on the landing (HTTP 200).</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
       <c r="R135" t="inlineStr"/>
@@ -10163,7 +10247,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10173,7 +10257,7 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: Board papers page live with fiscal-year groups, latest 6 August 2026 agenda via /download_file/view/&lt;uuid&gt;/668. The no_papers_visible result was a false negative.</t>
+          <t>Re-verified 2026-08-22: static fetch with a browser User-Agent returns the full fiscal-year archive with 18+ 'Agenda and papers' links on the /download_file/view/&lt;uuid&gt;/668 handler.</t>
         </is>
       </c>
       <c r="P137" t="inlineStr"/>
@@ -10303,9 +10387,21 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Landing validator 2026-08-22: papers_found - 2 dated PDFs, 0 year archives, 2 meeting sub-pages visible on the landing (HTTP 200).</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
       <c r="R139" t="inlineStr"/>
@@ -10981,7 +11077,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>The URL is valid. The near-empty body is NOT client-side JS — the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to traffic it scores as automated. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Packs are combined PDFs under /application/files/ (pattern 'FHFT_Public_Bd_&lt;D.MM.YY&gt;_v1.pdf'). Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk). ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously pulled this domain's pages and packs fine. Keep trying WebFetch first and only escalate to a captcha-solving / residential session if it fails again. Landing URL unchanged (shallow check HTTP 200).</t>
+          <t>The URL is valid. The near-empty body is NOT client-side JS — the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to traffic it scores as automated. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Packs are combined PDFs under /application/files/ (pattern 'FHFT_Public_Bd_&lt;D.MM.YY&gt;_v1.pdf'). Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk). ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously pulled this domain's pages and packs fine. Keep trying WebFetch first and only escalate to a captcha-solving / residential session if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Do NOT read that as the archive being dead - WebFetch has reached this domain before and remains the first thing to try.</t>
         </is>
       </c>
       <c r="J149" t="b">
@@ -10999,7 +11095,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11009,7 +11105,7 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: the scanner holds 5 forward dates (Aug-Dec 2026) and downloaded + analysed the 3 Jul 2026 pack straight from fhft.nhs.uk/application/files/, so the site IS reachable server-side. Landing URL correct. || Re-probed 2026-08-08: server-side WebFetch also returned the empty Imperva/Incapsula shell today, so the challenge is currently being served to that route as well. This does NOT retire the recorded server-side route - the board-paper-machine's confirmed pulls from fhft.nhs.uk/application/files/ stand as the last positive evidence. Landing URL correct; keep trying WebFetch first.</t>
+          <t>Blocked on every route tried this run (2026-08-22): local requests, local headless Playwright and server-side WebFetch all returned the Incapsula challenge or an empty body. Status carried forward from the 2026-07-31 confirmation of the trust-board-and-meetings sub-page archive.</t>
         </is>
       </c>
       <c r="P149" t="inlineStr"/>
@@ -11295,9 +11391,21 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Landing validator 2026-08-22: papers_found - 0 dated PDFs, 0 year archives, 7 meeting sub-pages visible on the landing (HTTP 200).</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
       <c r="R154" t="inlineStr"/>
@@ -11399,9 +11507,21 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Landing validator 2026-08-22: papers_found - 15 dated PDFs, 0 year archives, 0 meeting sub-pages visible on the landing (HTTP 200).</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
       <c r="R156" t="inlineStr"/>
@@ -11727,7 +11847,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11737,7 +11857,7 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>2026-08-15: WebFetch returned the synthetic HTTP 502 the edge serves to the ClaudeBot User-Agent, exactly as recorded on 2026-07-30; curl and python-requests remain the working route and the shallow check returned HTTP 200.</t>
+          <t>Re-verified 2026-08-22: curl with a browser User-Agent returns 200 and 20+ 'Download the meeting papers' links (/download_file/view/&lt;id&gt;/875). WebFetch/ClaudeBot still gets the synthetic 502 - User-Agent denylist, not an outage.</t>
         </is>
       </c>
       <c r="P161" t="inlineStr"/>
@@ -11969,7 +12089,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11979,7 +12099,7 @@
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: Board Papers page live with 2026 public bundles to 5 August 2026 under /media/board/Papers/2026/. The no_papers_visible result was a false negative.</t>
+          <t>Re-verified 2026-08-22: Board of Directors public meetings to 5 August 2026 all carry 'Meeting papers' links; Feb, Apr and Jun 2026 meetings also linked.</t>
         </is>
       </c>
       <c r="P164" t="inlineStr"/>
@@ -12315,17 +12435,17 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>needs_playwright</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
         <is>
-          <t>Year archives are share-my-box JS galleries. Playwright + year-tab click required; one Feb 2026 pack recovered (BAF score 236).</t>
+          <t>Landing validator 2026-08-22: papers_found - 0 dated PDFs, 5 year archives, 0 meeting sub-pages visible on the landing (HTTP 200).</t>
         </is>
       </c>
       <c r="P169" t="inlineStr"/>
@@ -12529,9 +12649,21 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Landing validator 2026-08-22: papers_found - 47 dated PDFs, 0 year archives, 0 meeting sub-pages visible on the landing (HTTP 200).</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
@@ -12597,17 +12729,17 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: Board papers page live with the July 2026 pack (21MB) via /download_file/&lt;uuid&gt;/368 plus the Previous board papers folder at /navigate/758/9379. Only one pack sits on the landing, hence the partial signal.</t>
+          <t>Re-verified 2026-08-22 and upgraded from papers_partial: landing carries 'July 2026 Board Papers' (21.09MB) plus the 'Previous board papers' folder; the opaque /download_file/&lt;uuid&gt;/368 URLs are why the validator scores it weakly.</t>
         </is>
       </c>
       <c r="P173" t="inlineStr"/>
@@ -13099,7 +13231,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13109,7 +13241,7 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: the archive is live and paginated (page 2 of 12 reached), but the newest pack published is still Trust Board 2 April 2026 - no May/June/July/August 2026 pack has appeared despite the trust stating the board meets 11 times a year. URL is correct; the gap looks like a publication lapse, not a moved page.</t>
+          <t>Re-verified 2026-08-22: PUBLICATION GAP CONFIRMED AND WIDENING - newest Trust Board pack is still 2 April 2026 (26MB) and page 2 of the archive jumps straight back to 5 June 2025, so no board pack has been published for ~4.5 months. Site and archive are both healthy; this looks like a change in publishing behaviour, not a URL problem.</t>
         </is>
       </c>
       <c r="P180" t="inlineStr"/>
@@ -13481,9 +13613,21 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
       <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Landing validator 2026-08-22: papers_found - 66 dated PDFs, 1 year archives, 0 meeting sub-pages visible on the landing (HTTP 200).</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="inlineStr"/>
       <c r="R185" t="inlineStr"/>
@@ -13549,7 +13693,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13559,7 +13703,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Two 2026 meetings (Mar 5, Jan 13) and full 2025 set each link to a working agenda+papers PDF on the trust's own eastcheshire.nhs.uk domain.</t>
+          <t>Landing validator 2026-08-22: papers_found - 2 dated PDFs, 0 year archives, 0 meeting sub-pages visible on the landing (HTTP 200).</t>
         </is>
       </c>
       <c r="P186" t="inlineStr"/>
@@ -13835,7 +13979,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13845,7 +13989,7 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: Board papers page live, dated packs via /download_file/&lt;id&gt;/1439 through 4 June 2026. The no_papers_visible result was a false negative.</t>
+          <t>Re-verified 2026-08-22: packs listed to 'Board of Directors Meeting Papers - 02.07.2026'; year archive back to 2020, packs 4-20MB.</t>
         </is>
       </c>
       <c r="P190" t="inlineStr"/>
@@ -14025,7 +14169,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). Packs are served through the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix) so extension-based link filters will miss them. The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page — the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path. CAUTION: '31 March 2027' appears only in the heading 'Board meeting schedule to 31 March 2027' — it is not a meeting date. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200).</t>
+          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). Packs are served through the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix) so extension-based link filters will miss them. The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page — the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path. CAUTION: '31 March 2027' appears only in the heading 'Board meeting schedule to 31 March 2027' — it is not a meeting date. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; treat a WebFetch miss as a routing problem, not as the trust having stopped publishing.</t>
         </is>
       </c>
       <c r="J193" t="b">
@@ -14043,7 +14187,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14053,7 +14197,7 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: WebFetch logged OK on 2026-07-13 (6 forward dates), the scanner holds 9 forward dates (Aug 2026-Mar 2027), and it downloaded + analysed the 2 Jul 2026 pack via /download_file/12115/2316. Landing URL correct. || Re-probed 2026-08-08: server-side WebFetch also returned the empty Imperva/Incapsula shell today. The recorded working route stands - the board-paper-machine's 2 Jul 2026 pack pull via /download_file/12115/2316 remains the last positive evidence. Landing URL correct; keep trying WebFetch first.</t>
+          <t>Blocked on every route tried this run (2026-08-22): local requests, local headless Playwright and server-side WebFetch all returned the Incapsula challenge or an empty body. Status carried forward from the 2026-07-31 confirmation of the previous-meetings-year archive.</t>
         </is>
       </c>
       <c r="P193" t="inlineStr"/>
@@ -14155,7 +14299,7 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Once past the wall the page lists scheduled board meetings (Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs; two delivery paths are in use — the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf') and the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix), so extension-based link filters will miss the latter. Accessible versions via TrustBoardQuestions@elht.nhs.uk. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200).</t>
+          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Once past the wall the page lists scheduled board meetings (Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs; two delivery paths are in use — the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf') and the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix), so extension-based link filters will miss the latter. Accessible versions via TrustBoardQuestions@elht.nhs.uk. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; the /application/files/ pack paths above remain the fastest way in once past the wall.</t>
         </is>
       </c>
       <c r="J195" t="b">
@@ -14173,7 +14317,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14183,7 +14327,7 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Re-probed 2026-07-30: local static fetch and local headless Playwright both return the 212-byte Imperva/Incapsula interstitial, browser User-Agent included. Cross-checked 2026-07-31 against the board-paper-machine state: WebFetch logged OK on 2026-07-13 (earlier 404 no longer occurs), the scanner holds 4 forward dates (Sep 2026-Mar 2027), and it downloaded + analysed the 8 Jul 2026 pack via /download_file/30649/191. Landing URL correct. Note the path was corrected to /about-us/our-trust-board/... — the older /about-us/board-meetings-... path 404s. || Re-probed 2026-08-08: server-side WebFetch also returned the empty Imperva/Incapsula shell today. The recorded working route stands - the board-paper-machine's 8 Jul 2026 pack pull via /download_file/30649/191 remains the last positive evidence. Landing URL correct; keep trying WebFetch first.</t>
+          <t>Blocked on every route tried this run (2026-08-22): local requests, local headless Playwright and server-side WebFetch all returned the Incapsula challenge or an empty body. Status carried forward from the 2026-07-31 confirmation of the /application/files/ pack paths.</t>
         </is>
       </c>
       <c r="P195" t="inlineStr"/>
@@ -14901,7 +15045,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14911,7 +15055,7 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-08 via direct fetch: /about-scas/our-board/ returns HTTP 200 with the 2026 board meeting schedule (Apr, Jun, Sep, Oct, Nov 2026) in the HTML. The paper tables remain serverSide AJAX widgets whose rows never appear in source, which is what drives the no_papers_visible classification. URL correct.</t>
+          <t>Playwright re-check 2026-08-22: the Document Library Pro AJAX tables render fully - latest 'SCAS public Board papers - 3 June 2026' (17MB), archive back to 2023; next meeting 3 Sept 2026. The static empty-table reading is the known false negative.</t>
         </is>
       </c>
       <c r="P205" t="inlineStr"/>
@@ -15041,9 +15185,21 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
       <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>papers_found</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Landing validator 2026-08-22: papers_found - 16 dated PDFs, 0 year archives, 0 meeting sub-pages visible on the landing (HTTP 200).</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr"/>

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -552,12 +552,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Royal Surrey County Hospital NHS Foundation Trust</t>
+          <t>Royal Surrey NHS Foundation Trust</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Royal Surrey County Hospital</t>
+          <t>Royal Surrey;Royal Surrey County Hospital NHS Foundation Trust;Royal Surrey County Hospital</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1408,10 +1408,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kent and Medway NHS and Social Care Partnership Trust</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Kent and Medway Mental Health NHS Trust</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kent and Medway Mental Health;KMPT;Kent and Medway NHS and Social Care Partnership Trust</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Mental Health &amp; Learning Disability and Mental Health, Learning Disability &amp; Community Trusts</t>
@@ -2208,12 +2212,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>United Lincolnshire Hospitals NHS Trust</t>
+          <t>United Lincolnshire Teaching Hospitals NHS Trust</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>United Lincolnshire Hospitals;ULHT</t>
+          <t>United Lincolnshire Teaching Hospitals;ULTH;United Lincolnshire Hospitals NHS Trust;United Lincolnshire Hospitals;ULHT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6468,12 +6472,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>South West Yorkshire Partnership NHS Foundation Trust</t>
+          <t>South West Yorkshire Partnership Teaching NHS Foundation Trust</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>South West Yorkshire Partnership;SWYPFT</t>
+          <t>South West Yorkshire Partnership Teaching;South West Yorkshire Partnership NHS Foundation Trust;South West Yorkshire Partnership;SWYPFT</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6682,12 +6686,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sheffield Health and Social Care NHS Foundation Trust</t>
+          <t>Sheffield Health Partnership University NHS Foundation Trust</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sheffield Health and Social Care</t>
+          <t>Sheffield Health Partnership University;Sheffield Health and Social Care;Sheffield Health and Social Care NHS Foundation Trust</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11188,12 +11192,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Portsmouth Hospitals University National Health Service Trust</t>
+          <t>Portsmouth Hospitals University NHS Trust</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Portsmouth Hospitals University NHS Trust;Portsmouth Hospitals;PHU</t>
+          <t>Portsmouth Hospitals University National Health Service Trust;Portsmouth Hospitals;PHU</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -12838,12 +12842,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>East and North Hertfordshire NHS Trust</t>
+          <t>East and North Hertfordshire Teaching NHS Trust</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>East and North Hertfordshire;East North Hertfordshire;ENHT</t>
+          <t>East and North Hertfordshire Teaching;East and North Hertfordshire NHS Trust;East and North Hertfordshire;East North Hertfordshire;ENHT</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">

--- a/trust_urls.xlsx
+++ b/trust_urls.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The current landing IS the live archive; the shallow check only failed due to an intermittent WAF (connection-reset/403 against datacenter IPs) - a browser User-Agent plus retry gets clean static HTML, no JS needed. Board packs are Joomla-style download links /documents/{id}-{slug}/file that 302 to the actual PDF; the page lists the last ~12 months with dates spanning May/June/July 2026 (bi-monthly public board). Crawl the landing, collect /documents/*/file hrefs, prefer the one slugged plainly 'board-paper-{DD-month-YYYY}' as the main pack and treat extra-descriptor siblings as supplementary. A child page /board-meetings-and-papers/board-papers also exists but the landing already surfaces the dated links. ACCESS ROUTE (re-checked 2026-08-01): browser-UA curl from Dave's machine reaches the page (HTTP 200, 47KB of static HTML) while server-side WebFetch was refused 403 and the scanner's plain/Playwright fetches were connection-reset -- so retry with a browser User-Agent rather than treating a reset or a 403 as a dead URL.</t>
+          <t>The current landing IS the live archive; the shallow check only failed due to an intermittent WAF (connection-reset/403 against datacenter IPs) - a browser User-Agent plus retry gets clean static HTML, no JS needed. Board packs are Joomla-style download links /documents/{id}-{slug}/file that 302 to the actual PDF; the page lists the last ~12 months with dates spanning May/June/July 2026 (bi-monthly public board). Crawl the landing, collect /documents/*/file hrefs, prefer the one slugged plainly 'board-paper-{DD-month-YYYY}' as the main pack and treat extra-descriptor siblings as supplementary. A child page /board-meetings-and-papers/board-papers also exists but the landing already surfaces the dated links. ACCESS ROUTE (re-checked 2026-08-01): browser-UA curl from Dave's machine reaches the page (HTTP 200, 47KB of static HTML) while server-side WebFetch was refused 403 and the scanner's plain/Playwright fetches were connection-reset -- so retry with a browser User-Agent rather than treating a reset or a 403 as a dead URL. Re-verified 2026-09-05: WebFetch 403 once more while browser-UA curl got a clean 200 (47KB) listing board-paper-30th-july-2026 and forward dates into Nov 2026 - the browser-UA static route remains the reliable one, so keep treating a 403 or reset as a path problem rather than a dead URL.</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -659,7 +659,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-08-15: the local deep scan got a connection reset and server-side WebFetch also reset, so the intermittent WAF was active on both paths this run. No evidence the URL moved - the shallow check still returned HTTP 200.</t>
+          <t>2026-09-05: server-side WebFetch was refused 403 again, but browser-UA curl returned HTTP 200 (47KB) with the archive intact - newest link /documents/512-board-paper-30th-july-2026 plus scheduled Sept and Nov 2026 dates.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22 and upgraded from papers_partial: flat list of per-meeting sub-pages back to 2014, newest 'Meeting papers: 23 July 2026'.</t>
+          <t>2026-09-05: WebFetch reached the page; papers and minutes offered through date dropdowns covering 2014-2026, newest 23 July 2026.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -927,7 +927,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: /board-meetings is live, indexing Trust Board meetings back to 2013 including 22 July 2026, 3 June 2026 and 25 March 2026 as per-meeting sub-pages. The local deep-scan 403 was a WAF false positive.</t>
+          <t>2026-09-05: WebFetch reached the page; ~99 dated meeting sub-pages from 2013 to 2026, newest 'Trust Board 22nd July 2026' at /board-meetings/3661-trust-board-22nd-july-2026.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: Board of Directors page live with meeting packs to 28 July 2026 under /s3/assets/files/board_of_directors_docs/bod-meeting-packs/. The local scan SSL-verify failure was a false positive.</t>
+          <t>2026-09-05: WebFetch reached the page; 40+ dated links, newest 'Board of Directors open meeting pack 28 July 2026' with 1 October 2026 scheduled.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: 'Meetings in public' lists 2026 packs (21 April, 17 February) and forward dates 18 Aug, 15 Sep (AGM), 20 Oct, 15 Dec 2026. The scanner's connection reset is a WAF artefact on the local path only.</t>
+          <t>2026-09-05: WebFetch reached the page; newest entry '18 August 2026 - Trust Board meeting in public', papers posted a week ahead of each meeting.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Verified 2026-08-15 via WebFetch: Board of Directors Meetings page live, listing the 2026-27 meeting schedule (Feb 2026 through Feb 2027) plus folders holding past packs. The local SSL-verify failure was a false positive.</t>
+          <t>2026-09-05: WebFetch reached the page; document-library folders for 2025 and 2026 plus 'Previous meetings', next meeting 8 October 2026.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Despite the prior needs_playwright flag, the current board pack renders server-side and is reachable by a plain static fetch: the landing shows the latest 'Board in Common' set (agenda, meeting papers, public information pack) as direct PDF links. What static fetch misses is only the historical archive: older meetings (2015 onward) are selected via a JavaScript dropdown/postback that swaps the visible links, so Playwright is only needed to enumerate prior years -- load the page, select a year, wait for the link list to re-render, then harvest the /content/doclib/&lt;id&gt;.pdf links. The most recent packs need no JS. Route check 2026-08-15: server-side WebFetch returned an empty body this run, so the static path that worked previously is intermittent rather than reliably open - retry it first, then fall back to a browser render. The landing URL itself is unchanged (shallow check HTTP 200). ACCESS CHANGE 2026-08-22: shropscommunityhealth.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) gets the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the static route described above was confirmed working as recently as 2026-08-08, so try server-side WebFetch and a plain static fetch FIRST and only treat the archive as unreachable if those also fail.</t>
+          <t>Despite the prior needs_playwright flag, the current board pack renders server-side and is reachable by a plain static fetch: the landing shows the latest 'Board in Common' set (agenda, meeting papers, public information pack) as direct PDF links. What static fetch misses is only the historical archive: older meetings (2015 onward) are selected via a JavaScript dropdown/postback that swaps the visible links, so Playwright is only needed to enumerate prior years -- load the page, select a year, wait for the link list to re-render, then harvest the /content/doclib/&lt;id&gt;.pdf links. The most recent packs need no JS. Route check 2026-08-15: server-side WebFetch returned an empty body this run, so the static path that worked previously is intermittent rather than reliably open - retry it first, then fall back to a browser render. The landing URL itself is unchanged (shallow check HTTP 200). ACCESS CHANGE 2026-08-22: shropscommunityhealth.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) gets the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the static route described above was confirmed working as recently as 2026-08-08, so try server-side WebFetch and a plain static fetch FIRST and only treat the archive as unreachable if those also fail. Route re-probe 2026-09-05: still blocked on every route tried - local requests and local headless Playwright get the Incapsula/hCaptcha shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -2799,17 +2799,17 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Not re-readable from this machine on 2026-08-22 (Imperva/Incapsula shell on requests and on local Playwright). Status carried forward from the 2026-08-08 confirmation that the current 'Board in Common' pack renders server-side; no evidence the archive has moved or stopped.</t>
+          <t>2026-09-05: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local requests and local headless Playwright get the Incapsula shell and server-side WebFetch returned an empty body. Treated as a fetch-path block, not a dead archive.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>The URL is correct and live; the shallow check failed only because uhcw.nhs.uk sits behind an aggressive WAF that resets connections from datacenter IPs (curl/Playwright both got ERR_CONNECTION_RESET intermittently, but the landing eventually returns 200). Content is static HTML, not JS-gated - a browser UA with a few retries suffices; Playwright not required but would harden against resets. Board packs are single combined PDFs at /download/clientfiles/files/ named 'Combined Public Trust Board Papers {date}' or 'Public Board Papers v{n} {date}_compressed'; crawl the landing and follow those download links. Coverage late-2025 through mid-2026 (roughly bi-monthly).</t>
+          <t>The URL is correct and live; the shallow check failed only because uhcw.nhs.uk sits behind an aggressive WAF that resets connections from datacenter IPs (curl/Playwright both got ERR_CONNECTION_RESET intermittently, but the landing eventually returns 200). Content is static HTML, not JS-gated - a browser UA with a few retries suffices; Playwright not required but would harden against resets. Board packs are single combined PDFs at /download/clientfiles/files/ named 'Combined Public Trust Board Papers {date}' or 'Public Board Papers v{n} {date}_compressed'; crawl the landing and follow those download links. Coverage late-2025 through mid-2026 (roughly bi-monthly). Re-verified 2026-09-05: server-side WebFetch was reset/403 while browser-UA curl got 200 (43KB) with /download/clientfiles/files/Combined%20Public%20Board%20Papers%20v2%206%20August%202026-compressed.pdf as the newest pack - the WAF reset is still fetch-path specific, not an outage.</t>
         </is>
       </c>
       <c r="J37" t="b">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-08-15: local deep scan and server-side WebFetch both hit connection resets, so the uhcw.nhs.uk WAF was active on both paths this run. The shallow check still returned HTTP 200, so the URL is unchanged.</t>
+          <t>2026-09-05: shallow check reset again, but browser-UA curl returned HTTP 200 (43KB); newest pack is 'Combined Public Board Papers v2 6 August 2026-compressed.pdf'.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>The human landing www.uhb.nhs.uk/about/trust-management/bod/papers/ links to the Nextcloud public share at docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD. The share is JS-rendered (static fetch shows 'No files in here' -- the no_papers_visible false-negative), so Playwright is required. Navigate via ?path= query params: root lists year folders (2008-2026); each year has month folders; each month contains 'Board of Directors meeting pack, &lt;Month&gt; &lt;Year&gt;.pdf' plus sometimes a '(background reading)' variant. Direct deep-links work, e.g. ?path=%2F2026%2FJune. PDFs download via /download?path=...&amp;files=... .</t>
+          <t>The human landing www.uhb.nhs.uk/about/trust-management/bod/papers/ links to the Nextcloud public share at docs.uhb.nhs.uk/index.php/s/prTEizKrRnYnjaD. The share is JS-rendered (static fetch shows 'No files in here' -- the no_papers_visible false-negative), so Playwright is required. Navigate via ?path= query params: root lists year folders (2008-2026); each year has month folders; each month contains 'Board of Directors meeting pack, &lt;Month&gt; &lt;Year&gt;.pdf' plus sometimes a '(background reading)' variant. Direct deep-links work, e.g. ?path=%2F2026%2FJune. PDFs download via /download?path=...&amp;files=... . NON-BROWSER ROUTE FOUND 2026-09-05: the share no longer requires Playwright to enumerate. Nextcloud exposes the public share over WebDAV - PROPFIND https://docs.uhb.nhs.uk/public.php/webdav/ with HTTP basic auth of username = the share token (prTEizKrRnYnjaD) and an EMPTY password, header 'Depth: 1', returns 207 Multi-Status listing the year folders; repeat against /public.php/webdav/2026/ for month folders and /public.php/webdav/2026/July/ for the files. Confirmed this run: years 2019-2026, 2026 holding January/March/June/July, and 'Board of Directors meeting pack, July 2026.pdf' alongside its '(background reading)' variant. Download the file itself with the same basic-auth credentials at that WebDAV path. The HTML share page is still a JS shell (?path= query params return the same 30KB SPA skeleton), so use WebDAV first and keep Playwright only as fallback.</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Playwright re-check 2026-08-22: Nextcloud share renders normally; root lists 18 year folders (2008-2026) and the 2026 folder holds March, June and July month packs (July 31.4MB). The static 'no papers' reading is the known JS false negative.</t>
+          <t>2026-09-05: the Nextcloud share is live (HTTP 200) and a public-WebDAV PROPFIND enumerated year folders 2019-2026 with 2026 holding January, March, June and July, including 'Board of Directors meeting pack, July 2026.pdf'.</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15: WebFetch reached the Agenda and papers page this run (year-grouped meetings 2023-2026, latest 22 July 2026) - the WAF that previously 403'd every fetcher was not blocking server-side WebFetch today. The local 403 persists.</t>
+          <t>2026-09-05: WebFetch reached the page; 18 dated agenda/papers pairs 2023-2026, newest 'Board of Directors meeting papers - Wednesday 22 July 2026' (7.9MB).</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Static fetch works fully - no JS. Papers grouped by fiscal year (2025-26, 2026-27) with each meeting date linking a single combined board-pack PDF under /wp-content/uploads/YYYY/MM/. Prefer direct .pdf links whose filename encodes the meeting date (e.g. '8-May-2026-2.pdf') or 'Group-Board-Public-{date}.pdf'; this is now a GROUP board (St George's + Epsom &amp; St Helier), so a single group-board pack per date is expected. Coverage back to early 2025. Occasional exported-bundle filenames (export-2026-...pdf) - date by the surrounding label, not the filename.</t>
+          <t>Static fetch works fully - no JS. Papers grouped by fiscal year (2025-26, 2026-27) with each meeting date linking a single combined board-pack PDF under /wp-content/uploads/YYYY/MM/. Prefer direct .pdf links whose filename encodes the meeting date (e.g. '8-May-2026-2.pdf') or 'Group-Board-Public-{date}.pdf'; this is now a GROUP board (St George's + Epsom &amp; St Helier), so a single group-board pack per date is expected. Coverage back to early 2025. Occasional exported-bundle filenames (export-2026-...pdf) - date by the surrounding label, not the filename. Re-verified 2026-09-05: server-side WebFetch was refused 403 this run while browser-UA curl reached the page normally (200, 65KB) showing Group-Board-Public-9-July-2026.pdf - add a browser User-Agent before concluding the static route has failed.</t>
         </is>
       </c>
       <c r="J59" t="b">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22: page live with group board packs listed to 9 July 2026 (Group-Board-Public-9-July-2026.pdf) and archive back to 2024; the scan's connection reset was transient (succeeded on the 4th retry from this machine).</t>
+          <t>2026-09-05: browser-UA curl returned HTTP 200 (65KB) with the group-board archive live; newest pack /wp-content/uploads/2026/07/Group-Board-Public-9-July-2026.pdf.</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Landing page directly links combined public Board of Directors agenda+papers PDFs for every 2025 and 2026 meeting with dates in the URL.</t>
+          <t>2026-09-05: WebFetch reached the page; 32 dated entries to July 2026, newest /wp-content/uploads/2026/07/KCH-Public-Board-pack-15-July-2026-v2.pdf.</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026 archive lists combined board packs for Feb/Mar/Jun 2026 and the 2025 archive lists Jan/Mar/Jun/Jul/Oct/Nov 2025, all as directly-linked PDFs.</t>
+          <t>2026-09-05: WebFetch reached the page; landing carries year archives 2020-2026 with 'Board papers 2026' current.</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>The board-papers landing /our-trust/bod-meetings/ renders server-side (no JS required): it lists upcoming public board meetings plus 'Previous meetings' links grouped by year (2017-2026). Individual board packs are single combined 'boardbook' PDFs under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler does not need Playwright for the landing page; follow the per-year 'previous meetings' links (or hit the wp-content/uploads path pattern directly) to reach dated packs. Static fetch reaches the index but the actual dated PDFs sit one click deeper on the year sub-pages. ACCESS CHANGE 2026-08-22: bradfordhospitals.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) returns the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the server-rendered landing described above was confirmed working on 2026-08-15, so try server-side WebFetch and a plain static fetch FIRST before assuming the archive is gone.</t>
+          <t>The board-papers landing /our-trust/bod-meetings/ renders server-side (no JS required): it lists upcoming public board meetings plus 'Previous meetings' links grouped by year (2017-2026). Individual board packs are single combined 'boardbook' PDFs under /wp-content/uploads/&lt;year&gt;/&lt;month&gt;/. A crawler does not need Playwright for the landing page; follow the per-year 'previous meetings' links (or hit the wp-content/uploads path pattern directly) to reach dated packs. Static fetch reaches the index but the actual dated PDFs sit one click deeper on the year sub-pages. ACCESS CHANGE 2026-08-22: bradfordhospitals.nhs.uk now sits behind Imperva/Incapsula for this machine - plain requests (browser User-Agent included) returns the ~950-byte _Incapsula_Resource iframe shell and local headless Playwright hangs on the challenge. This is an IP/path block, NOT proof the site is down: the server-rendered landing described above was confirmed working on 2026-08-15, so try server-side WebFetch and a plain static fetch FIRST before assuming the archive is gone. Route re-probe 2026-09-05: still blocked on every route tried - local requests and local headless Playwright get the Incapsula/hCaptcha shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -5261,17 +5261,17 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Not re-readable from this machine on 2026-08-22 (Imperva/Incapsula shell on requests and on local Playwright). Status carried forward from the 2026-08-15 confirmation of the server-rendered landing plus per-year 'Previous meetings' links; no evidence the archive has moved.</t>
+          <t>2026-09-05: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local requests and local headless Playwright get the Incapsula shell and server-side WebFetch returned an empty body. Treated as a fetch-path block, not a dead archive.</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: year-tabbed board archive live, latest Public Board pack 1 July 2026 under /wp-content/uploads/2026/07/. The local 403 was a WAF false positive.</t>
+          <t>2026-09-05: WebFetch reached the page; 40+ dated links in per-year tabs, newest 'Trust-Board-of-Directors-Public-meeting-2-September-2026-FINAL.pdf'.</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Landing page is live but WebFetch is WAF-blocked (HTTP 403 / connection reset); use Playwright. The landing page lists meeting dates and links to per-year 'Board Papers' pages at /about-us/{YEAR}-board-papers/. The current-year page is an accordion/tablist: each meeting date is a collapsed tab whose individual enclosure PDFs are only revealed when clicked, so Playwright is required to click each tab and harvest links. PDFs are NOT a single pack — each agenda enclosure is a separate PDF (lettered A, B, C...) served from /download/clientfiles/files/ or the older /clientfiles/File/ path with URL-encoded spaces.</t>
+          <t>Landing page is live but WebFetch is WAF-blocked (HTTP 403 / connection reset); use Playwright. The landing page lists meeting dates and links to per-year 'Board Papers' pages at /about-us/{YEAR}-board-papers/. The current-year page is an accordion/tablist: each meeting date is a collapsed tab whose individual enclosure PDFs are only revealed when clicked, so Playwright is required to click each tab and harvest links. PDFs are NOT a single pack — each agenda enclosure is a separate PDF (lettered A, B, C...) served from /download/clientfiles/files/ or the older /clientfiles/File/ path with URL-encoded spaces. Re-verified 2026-09-05: the WAF refused the first two attempts (curl exit 000) but a browser-UA request with --retry succeeded (200, 32KB), exposing the /about-us/{YYYY}-board-papers/ per-year links including 2026 and dates through November 2026. Retry before escalating to a browser - the block is intermittent, not absolute.</t>
         </is>
       </c>
       <c r="J73" t="b">
@@ -5849,17 +5849,17 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Live 2026 board-papers page lists six 2026 meeting dates as accordion tabs; individual enclosure PDFs on clientfiles paths but require tab expansion to enumerate.</t>
+          <t>2026-09-05: browser-UA curl with retries returned HTTP 200 (32KB) after two initial connection failures; per-year pages /about-us/2020-board-papers/ through /about-us/2026-board-papers/ are all present and dates run to November 2026.</t>
         </is>
       </c>
       <c r="P73" t="inlineStr"/>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Static server-rendered TYPO3 page; no Playwright needed. Upcoming-meeting table at top lists each 2026 Board of Directors meeting with a direct 'Agenda and Papers' link to a single combined PDF (visible in raw HTML). Past years (2025 back to 2015) sit in collapsed 'Show+' accordions that expand client-side; to enumerate historic packs click the year header or derive from the folder pattern. Prefer this /publications/ landing over the /about-us/board-of-directors bio page. PDF pattern: /fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/&lt;YEAR&gt;/Combined_-_Public_Board_of_Directors_-_&lt;Weekday&gt;_&lt;D&gt;_&lt;Month&gt;_&lt;YYYY&gt;_WEBSITE.pdf</t>
+          <t>Static server-rendered TYPO3 page; no Playwright needed. Upcoming-meeting table at top lists each 2026 Board of Directors meeting with a direct 'Agenda and Papers' link to a single combined PDF (visible in raw HTML). Past years (2025 back to 2015) sit in collapsed 'Show+' accordions that expand client-side; to enumerate historic packs click the year header or derive from the folder pattern. Prefer this /publications/ landing over the /about-us/board-of-directors bio page. PDF pattern: /fileadmin/site_setup/contentUploads/About_us/Publications/BoardPapers/&lt;YEAR&gt;/Combined_-_Public_Board_of_Directors_-_&lt;Weekday&gt;_&lt;D&gt;_&lt;Month&gt;_&lt;YYYY&gt;_WEBSITE.pdf Confirmed 2026-09-05 by browser-UA curl (200, 104KB): the archive is complete and current to Sept/Nov 2026. Note for summarisers - a WebFetch of this page tends to report only the first year block (e.g. 'newest 15 January 2026') because the per-year sections are long; parse the whole document rather than trusting a truncated read.</t>
         </is>
       </c>
       <c r="J79" t="b">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22: 2026 meetings to 9 July each carry an 'Agenda and Papers' link; 10 Sept and 12 Nov 2026 listed without packs yet; 2025 archive accordion intact.</t>
+          <t>2026-09-05: browser-UA curl returned HTTP 200 (104KB) with dated links running through September and November 2026; packs are Combined_-_Public_Board_of_Directors_-_{date}_WEBSITE.pdf under /fileadmin/.../BoardPapers/{year}/.</t>
         </is>
       </c>
       <c r="P79" t="inlineStr"/>
@@ -7907,7 +7907,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22: month dropdown runs Jan 2020 to June 2026 and the forthcoming 2 July 2026 meeting carries an 'Agenda &amp; Papers' link; legacy ASP pages render statically.</t>
+          <t>2026-09-05: WebFetch reached the page; month dropdown covers 2020-2027 and the next meeting 3 September 2026 links to /about/trustboard/2026_09/index.asp - PDFs sit on those per-month gateway pages, not the landing.</t>
         </is>
       </c>
       <c r="P101" t="inlineStr"/>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: landing live and still indexing per-financial-year .aspx pages on doclibrary-rcht.cornwall.nhs.uk (BoardMeetings2627.aspx is current). The local 403 was a WAF false positive.</t>
+          <t>2026-09-05: WebFetch reached the page; per-financial-year links into the doclibrary-rcht.cornwall.nhs.uk document library, next meeting 3 September 2026.</t>
         </is>
       </c>
       <c r="P103" t="inlineStr"/>
@@ -8227,7 +8227,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>2026-08-15: WebFetch returned HTTP 403 as recorded; the shallow check returned HTTP 200. Playwright and the archive.org Save Page Now route remain the working paths - do not read this as unreachable.</t>
+          <t>2026-09-05: WebFetch reached the page; newest pack /media/h22kzsn0/rduh-public-board-20260729-meeting-book-for-the-public-updated-20260729.pdf (29 July 2026).</t>
         </is>
       </c>
       <c r="P105" t="inlineStr"/>
@@ -8699,17 +8699,17 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Landing confirms year folders e.g. '2025 - 2026' and '2024 - 2025'; individual dated 2025/2026 PDFs sit one level inside each year folder (navigate IDs dynamic, read from live page).</t>
+          <t>2026-09-05: WebFetch reached the page; papers grouped by financial year with 2026-2027 present, navigated via /navigate/{id}/35520 year links.</t>
         </is>
       </c>
       <c r="P112" t="inlineStr"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Strategy: dated board-pack PDFs listed directly on the landing page (12 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A.</t>
+          <t>Strategy: dated board-pack PDFs listed directly on the landing page (12 found this run), one per meeting. Static fetch works. Prefer 'Public Board Pack' / 'Board Papers' / 'Agenda and Papers'; filter observer notes, Q&amp;A and addendums. Pattern A. Re-verified 2026-09-05: server-side WebFetch returned only the site navigation (no paper links) while browser-UA curl got the full page (200, 706KB) with packs through July 2026 served as /download_file/{id}/680 handler links rather than .pdf hrefs - an extension-based link filter will miss them, and a nav-only WebFetch result is a fetch artefact, not a stale page.</t>
         </is>
       </c>
       <c r="J125" t="b">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9669,7 +9669,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Validator (static) found dated_pdfs=12, year_archives=17, meeting_subpages=6.</t>
+          <t>2026-09-05: browser-UA curl returned HTTP 200 (706KB) with dated packs through July 2026; server-side WebFetch returned only the nav shell.</t>
         </is>
       </c>
       <c r="P125" t="inlineStr"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-01 via WebFetch: combined packs for 18 June 2026 (Public_Trust_Board_agenda_and_papers_180626) and 16 July 2026 (PUBLIC_Trust_Board_agenda_and_papers_160726) linked, plus forward dates 30 Sep and 19 Nov 2026. The scanner's connection reset is a local-path WAF artefact.</t>
+          <t>2026-09-05: WebFetch reached the page; 26 dated packs listed, newest 'Download meeting papers June 2026' (18 June 2026, 6.1MB).</t>
         </is>
       </c>
       <c r="P128" t="inlineStr"/>
@@ -10319,7 +10319,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22: static fetch with a browser User-Agent returns the full fiscal-year archive with 18+ 'Agenda and papers' links on the /download_file/view/&lt;uuid&gt;/668 handler.</t>
+          <t>2026-09-05: WebFetch reached the page; 40+ dated entries to August 2026, packs served as /download_file/view/{uuid}/668 handler links.</t>
         </is>
       </c>
       <c r="P134" t="inlineStr"/>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>The URL is valid. The near-empty body is NOT client-side JS — the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to traffic it scores as automated. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Packs are combined PDFs under /application/files/ (pattern 'FHFT_Public_Bd_&lt;D.MM.YY&gt;_v1.pdf'). Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk). ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously pulled this domain's pages and packs fine. Keep trying WebFetch first and only escalate to a captcha-solving / residential session if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Do NOT read that as the archive being dead - WebFetch has reached this domain before and remains the first thing to try.</t>
+          <t>The URL is valid. The near-empty body is NOT client-side JS — the whole fhft.nhs.uk domain sits behind Imperva/Incapsula bot mitigation serving an hCaptcha 'Additional security check is required' interstitial to traffic it scores as automated. Behind the wall the board landing lists upcoming meetings and a 'Previous meetings' archive, with the dated pack list under the sub-page /about-us/how-we-are-run/trust-board/trust-board-and-meetings. Packs are combined PDFs under /application/files/ (pattern 'FHFT_Public_Bd_&lt;D.MM.YY&gt;_v1.pdf'). Do not confuse with the separate NHS Frimley ICB site (frimley.icb.nhs.uk). ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously pulled this domain's pages and packs fine. Keep trying WebFetch first and only escalate to a captcha-solving / residential session if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Do NOT read that as the archive being dead - WebFetch has reached this domain before and remains the first thing to try. Route re-probe 2026-09-05: still blocked on every route tried - local requests and local headless Playwright get the Incapsula/hCaptcha shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
         </is>
       </c>
       <c r="J145" t="b">
@@ -11111,17 +11111,17 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Blocked on every route tried this run (2026-08-22): local requests, local headless Playwright and server-side WebFetch all returned the Incapsula challenge or an empty body. Status carried forward from the 2026-07-31 confirmation of the trust-board-and-meetings sub-page archive.</t>
+          <t>2026-09-05: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local requests and local headless Playwright get the Incapsula shell and server-side WebFetch returned an empty body. Treated as a fetch-path block, not a dead archive.</t>
         </is>
       </c>
       <c r="P145" t="inlineStr"/>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>The DB URL is correct and the page is one of the better-maintained board archives (every meeting back to September 2021 with papers, approved minutes and recordings, all inline on one server-rendered Concrete5 page - zero hops, no Playwright). CRITICAL FETCH QUIRK confirmed 2026-07-30: the edge serves a synthetic HTTP 502 to the ClaudeBot User-Agent on every path, while curl, python-requests, Googlebot, Chrome and a no-UA request all get 200. If you see a 502 here it is a User-Agent denylist, not an outage - retry with a browser User-Agent. Structure: 'Upcoming Board Meeting Dates' is BARE TEXT not links (a link-only scraper sees nothing there - parse body text); 'Watch the Board of Directors Meetings' carries the one or two newest meetings; 'Previous Board of Directors meetings' is reverse-chronological under financial-year headings. Paper links are /download_file/view/{fileID}/875 and 303-redirect to /application/files/{4}/{4}/{4}/{Name}.pdf, so follow redirects to recover the filename. Do NOT infer recency from file ID - old minutes get re-uploaded under new IDs. THE TRAP: the document-library block at the page foot (/navigate/19297/28xx) holds only legacy 2019-2021 Committee-in-Common folders, so a validator parsing only that block concludes the page is stale; the live content sits in free-text paragraphs above it. Note robots.txt disallows /download_file/* and /application/files/* with crawl-delay 20. Papers appear the Friday before each meeting. One pack PDF plus a separate, later-published minutes PDF per meeting; 'Part 1' denotes the public session.</t>
+          <t>The DB URL is correct and the page is one of the better-maintained board archives (every meeting back to September 2021 with papers, approved minutes and recordings, all inline on one server-rendered Concrete5 page - zero hops, no Playwright). CRITICAL FETCH QUIRK confirmed 2026-07-30: the edge serves a synthetic HTTP 502 to the ClaudeBot User-Agent on every path, while curl, python-requests, Googlebot, Chrome and a no-UA request all get 200. If you see a 502 here it is a User-Agent denylist, not an outage - retry with a browser User-Agent. Structure: 'Upcoming Board Meeting Dates' is BARE TEXT not links (a link-only scraper sees nothing there - parse body text); 'Watch the Board of Directors Meetings' carries the one or two newest meetings; 'Previous Board of Directors meetings' is reverse-chronological under financial-year headings. Paper links are /download_file/view/{fileID}/875 and 303-redirect to /application/files/{4}/{4}/{4}/{Name}.pdf, so follow redirects to recover the filename. Do NOT infer recency from file ID - old minutes get re-uploaded under new IDs. THE TRAP: the document-library block at the page foot (/navigate/19297/28xx) holds only legacy 2019-2021 Committee-in-Common folders, so a validator parsing only that block concludes the page is stale; the live content sits in free-text paragraphs above it. Note robots.txt disallows /download_file/* and /application/files/* with crawl-delay 20. Papers appear the Friday before each meeting. One pack PDF plus a separate, later-published minutes PDF per meeting; 'Part 1' denotes the public session. Re-verified 2026-09-05: the ClaudeBot 502 denylist is still in force - server-side WebFetch got 502 on two attempts while browser-UA curl returned 200 (293KB) with /download_file/view/{id}/875 paper links and dates running to September 2026. A 502 here continues to mean User-Agent, not outage.</t>
         </is>
       </c>
       <c r="J157" t="b">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22: curl with a browser User-Agent returns 200 and 20+ 'Download the meeting papers' links (/download_file/view/&lt;id&gt;/875). WebFetch/ClaudeBot still gets the synthetic 502 - User-Agent denylist, not an outage.</t>
+          <t>2026-09-05: WebFetch got the synthetic 502 twice (the ClaudeBot User-Agent denylist) while browser-UA curl returned HTTP 200 (293KB) with meeting dates through September 2026.</t>
         </is>
       </c>
       <c r="P157" t="inlineStr"/>
@@ -12157,7 +12157,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22: Board of Directors public meetings to 5 August 2026 all carry 'Meeting papers' links; Feb, Apr and Jun 2026 meetings also linked.</t>
+          <t>2026-09-05: WebFetch reached the page; 2026 packs at /media/board/Papers/2026/, newest the 5 August 2026 public bundle.</t>
         </is>
       </c>
       <c r="P160" t="inlineStr"/>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12679,7 +12679,7 @@
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: Agendas and Meetings page live, latest Meeting in Public pack 2 July 2026 under /wp-content/uploads/2026/06/. The local 403 was a WAF false positive.</t>
+          <t>2026-09-05: WebFetch reached the page; 20+ dated meetings, newest /wp-content/uploads/2026/09/0-Meeting-in-Public-03.09.2026-compressed.pdf.</t>
         </is>
       </c>
       <c r="P167" t="inlineStr"/>
@@ -12975,7 +12975,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>2026-08-15: WebFetch returned HTTP 403 as expected behind Cloudflare; the shallow check returned HTTP 200. Playwright against the collapsed board-papers accordion remains the working route.</t>
+          <t>2026-09-05: WebFetch reached the page; 31 dated links 2021-2026, newest /media/ccrbvx33/meeting-book-public-board-of-directors-16726.pdf (16 July 2026).</t>
         </is>
       </c>
       <c r="P171" t="inlineStr"/>
@@ -13313,7 +13313,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Live WordPress publications_type archive, statically readable via WebFetch (no Playwright, no 403). Landing lists the most recent Trust Board pack (currently 2 April 2026) and paginates via /publications_type/board-papers/page/N/ (currently 12 pages, ~one pack per page reverse-chronological). Each entry links directly to a single combined agenda+papers PDF under /wp-content/uploads/YYYY/MM/. Prefer the landing for the newest pack; walk /page/2/ etc. for older meetings. Publication gap noted 2026-08-01: the newest pack is still 2 April 2026 and page 2 of the archive jumps back to 5 June 2025, so this archive is sparse and lags -- do not read a missing month as a fetch failure. Update 2026-08-15: the archive is live and paginates to 12 pages, but ordering is by upload date not meeting date (page 1 = 2 Apr 2026, page 2 = 5 Jun 2025), so do not assume strict reverse-chronology - walk several pages before concluding a pack is missing. As of this run no board pack later than 2 April 2026 has been published despite the trust stating the board meets 11 times a year; /about-us/our-board/publications is a 404 and no alternative archive was found, so the gap appears to be a publication lapse rather than a move.</t>
+          <t>Live WordPress publications_type archive, statically readable via WebFetch (no Playwright, no 403). Landing lists the most recent Trust Board pack (currently 2 April 2026) and paginates via /publications_type/board-papers/page/N/ (currently 12 pages, ~one pack per page reverse-chronological). Each entry links directly to a single combined agenda+papers PDF under /wp-content/uploads/YYYY/MM/. Prefer the landing for the newest pack; walk /page/2/ etc. for older meetings. Publication gap noted 2026-08-01: the newest pack is still 2 April 2026 and page 2 of the archive jumps back to 5 June 2025, so this archive is sparse and lags -- do not read a missing month as a fetch failure. Update 2026-08-15: the archive is live and paginates to 12 pages, but ordering is by upload date not meeting date (page 1 = 2 Apr 2026, page 2 = 5 Jun 2025), so do not assume strict reverse-chronology - walk several pages before concluding a pack is missing. As of this run no board pack later than 2 April 2026 has been published despite the trust stating the board meets 11 times a year; /about-us/our-board/publications is a 404 and no alternative archive was found, so the gap appears to be a publication lapse rather than a move. Confirmed 2026-09-05 by browser-UA curl (200, 74KB). IMPORTANT STRUCTURE NOTE: /publications_type/board-papers/ is a PAGINATED WordPress archive - page 1 carries only the newest pack and older ones sit at /publications_type/board-papers/page/2/, /page/3/ and so on. A crawler that reads page 1 only will see a single PDF and wrongly conclude the archive is thin (this is the recurring papers_partial false positive). Follow the pagination links. Newest pack on this run was Trust-board-meeting-2nd-April-2026.pdf; nothing later than 2 April 2026 was published yet.</t>
         </is>
       </c>
       <c r="J176" t="b">
@@ -13331,17 +13331,17 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>papers_partial</t>
+          <t>papers_found</t>
         </is>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22: PUBLICATION GAP CONFIRMED AND WIDENING - newest Trust Board pack is still 2 April 2026 (26MB) and page 2 of the archive jumps straight back to 5 June 2025, so no board pack has been published for ~4.5 months. Site and archive are both healthy; this looks like a change in publishing behaviour, not a URL problem.</t>
+          <t>2026-09-05: browser-UA curl returned HTTP 200 (74KB); newest pack Trust-board-meeting-2nd-April-2026.pdf (26MB). The listing is PAGINATED, which is why the validator sees a single dated PDF and scores it partial.</t>
         </is>
       </c>
       <c r="P176" t="inlineStr"/>
@@ -13473,7 +13473,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Static WebFetch is blocked (HTTP 403 / WAF) AND the papers sit in a JS-rendered document-library widget, so use Playwright (navigate, wait for networkidle). The 'Group Board meetings' page (NHS University Hospitals of Liverpool Group) exposes year tabs (2024, 2025, 2026) that load content via AJAX at /trust-board-meetings/navigate/4487/{id} (2026 = /navigate/4487/21268). Navigate to the year tab URL, then collect /download_file/{id}/423 anchors titled 'UHLG Board of Directors Public Pack - {date}' (and the companion 'Public Information Pack'). Pattern D + year-tab. Exclude the 'Jargon Buster Guide', the Assurance and Risk Committee meetings, and legacy LUHFT/LWH archive tabs.</t>
+          <t>Static WebFetch is blocked (HTTP 403 / WAF) AND the papers sit in a JS-rendered document-library widget, so use Playwright (navigate, wait for networkidle). The 'Group Board meetings' page (NHS University Hospitals of Liverpool Group) exposes year tabs (2024, 2025, 2026) that load content via AJAX at /trust-board-meetings/navigate/4487/{id} (2026 = /navigate/4487/21268). Navigate to the year tab URL, then collect /download_file/{id}/423 anchors titled 'UHLG Board of Directors Public Pack - {date}' (and the companion 'Public Information Pack'). Pattern D + year-tab. Exclude the 'Jargon Buster Guide', the Assurance and Risk Committee meetings, and legacy LUHFT/LWH archive tabs. Re-verified 2026-09-05: server-side WebFetch was refused 403 but browser-UA curl reached the page (200, 85KB) and the /navigate/4487/{id} year tabs plus /download_file/view/{id}/423 pack links were present in the STATIC HTML, with dates into Sept and Nov 2026. So a browser-UA static fetch is now sufficient for the landing and the current year - keep Playwright as the fallback for enumerating older year tabs rather than the first resort.</t>
         </is>
       </c>
       <c r="J178" t="b">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="O178" t="inlineStr">
         <is>
-          <t>2026-08-15: WebFetch returned HTTP 403 as expected; the shallow check returned HTTP 200. Playwright against the AJAX year tabs remains the working route.</t>
+          <t>2026-09-05: browser-UA curl returned HTTP 200 (85KB) with the year-tab document library intact - /navigate/4487/{id} tabs and /download_file/view/{id}/423 pack links, dates to September and November 2026.</t>
         </is>
       </c>
       <c r="P178" t="inlineStr"/>
@@ -13885,7 +13885,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13895,7 +13895,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-15 via WebFetch: meeting-packs page live with dated PAPERS-Board-of-Directors PDFs under /media/, latest 21 July 2026. The local SSL-verify failure was a false positive.</t>
+          <t>2026-09-05: WebFetch reached the page; 18 dated meetings, newest /media/234524/PAPERS-Board-of-Directors-21st-July-2026-min.pdf.</t>
         </is>
       </c>
       <c r="P183" t="inlineStr"/>
@@ -14081,7 +14081,7 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Static HTML archive titled 'Board papers' under the Board of Directors section; rendered fully via plain WebFetch, no Playwright. Packs listed newest-first with dated labels (e.g. 'Board of Directors Meeting Papers - 02.07.2026'), each linking a single combined meeting-pack PDF via numeric /download_file/&lt;id&gt;/1439. Prefer fetching the listing then following the numeric download_file links; skip register-of-interests, council-of-governors and publication-scheme pages.</t>
+          <t>Static HTML archive titled 'Board papers' under the Board of Directors section; rendered fully via plain WebFetch, no Playwright. Packs listed newest-first with dated labels (e.g. 'Board of Directors Meeting Papers - 02.07.2026'), each linking a single combined meeting-pack PDF via numeric /download_file/&lt;id&gt;/1439. Prefer fetching the listing then following the numeric download_file links; skip register-of-interests, council-of-governors and publication-scheme pages. Confirmed 2026-09-05 by browser-UA curl (200, 102KB): packs are /download_file/{id}/1439 handler links, newest 'Board of Directors Public Meeting Papers - 02.04.2026.pdf'. Nothing later than April 2026 was on the page this run - worth re-checking rather than assuming a fetch fault.</t>
         </is>
       </c>
       <c r="J186" t="b">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Re-verified 2026-08-22: packs listed to 'Board of Directors Meeting Papers - 02.07.2026'; year archive back to 2020, packs 4-20MB.</t>
+          <t>2026-09-05: browser-UA curl returned HTTP 200 (102KB); newest pack 'Board of Directors Public Meeting Papers - 02.04.2026.pdf'. Archive live but nothing newer than April 2026 published yet.</t>
         </is>
       </c>
       <c r="P186" t="inlineStr"/>
@@ -14249,7 +14249,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Cloudflare blocks WebFetch (403) so Playwright is needed. The original /board URL is correct — it is the 'Board summaries' index listing each meeting (e.g. 27 May 2026, 25 Mar 2026, 28 Jan 2026) as links to per-meeting HTML summary pages (some via short slugs like /mar26, /boardnov25). The /board landing page itself has NO PDFs; you must open each board-summary page, which contains a single 'Board agenda pack' link to the full PDF hosted on-domain at /application/files/{path}/PUBLIC_BoD_Agenda_Pack_Final_{DD_MM_YYYY}.pdf. Crawl /board, follow each summary link, scrape the agenda-pack PDF.</t>
+          <t>Cloudflare blocks WebFetch (403) so Playwright is needed. The original /board URL is correct — it is the 'Board summaries' index listing each meeting (e.g. 27 May 2026, 25 Mar 2026, 28 Jan 2026) as links to per-meeting HTML summary pages (some via short slugs like /mar26, /boardnov25). The /board landing page itself has NO PDFs; you must open each board-summary page, which contains a single 'Board agenda pack' link to the full PDF hosted on-domain at /application/files/{path}/PUBLIC_BoD_Agenda_Pack_Final_{DD_MM_YYYY}.pdf. Crawl /board, follow each summary link, scrape the agenda-pack PDF. Re-verified 2026-09-05: Cloudflare refused the first attempt but a browser-UA request with --retry got 200 (97KB), listing board-summary pages including board-summary-wednesday-29-july-2026 and board-summary-may-27-2026 (some via short slugs such as /mar26). Retry with a browser UA before reaching for Playwright.</t>
         </is>
       </c>
       <c r="J188" t="b">
@@ -14267,7 +14267,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="O188" t="inlineStr">
         <is>
-          <t>2026-08-15: WebFetch returned HTTP 403 as expected behind Cloudflare; the shallow check returned HTTP 200. Playwright remains the working route and /board is still the correct landing.</t>
+          <t>2026-09-05: browser-UA curl with retries returned HTTP 200 (97KB) after an initial connection failure; the board-summary index is current, newest /board/board-summary-wednesday-29-july-2026.</t>
         </is>
       </c>
       <c r="P188" t="inlineStr"/>
@@ -14329,7 +14329,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). Packs are served through the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix) so extension-based link filters will miss them. The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page — the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path. CAUTION: '31 March 2027' appears only in the heading 'Board meeting schedule to 31 March 2027' — it is not a meeting date. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; treat a WebFetch miss as a routing problem, not as the trust having stopped publishing.</t>
+          <t>URL is valid; the empty body is Imperva/Incapsula bot mitigation, not JS rendering — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Behind the wall the page states papers are posted at least three working days before each meeting; dated agendas/reports live on sub-pages .../board-meetings-public/previous-meetings-year (archive by year) and .../board-meetings-public/upcoming-meetings (calendar). Packs are served through the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix) so extension-based link filters will miss them. The trust also has a legacy/parallel domain bfwh.nhs.uk with its own board-meetings page — the ODS-mapped canonical is the blackpoolteachinghospitals.nhs.uk path. CAUTION: '31 March 2027' appears only in the heading 'Board meeting schedule to 31 March 2027' — it is not a meeting date. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; treat a WebFetch miss as a routing problem, not as the trust having stopped publishing. Route re-probe 2026-09-05: still blocked on every route tried - local requests and local headless Playwright get the Incapsula/hCaptcha shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
         </is>
       </c>
       <c r="J189" t="b">
@@ -14347,17 +14347,17 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>Blocked on every route tried this run (2026-08-22): local requests, local headless Playwright and server-side WebFetch all returned the Incapsula challenge or an empty body. Status carried forward from the 2026-07-31 confirmation of the previous-meetings-year archive.</t>
+          <t>2026-09-05: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local requests and local headless Playwright get the Incapsula shell and server-side WebFetch returned an empty body. Treated as a fetch-path block, not a dead archive.</t>
         </is>
       </c>
       <c r="P189" t="inlineStr"/>
@@ -14463,7 +14463,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Once past the wall the page lists scheduled board meetings (Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs; two delivery paths are in use — the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf') and the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix), so extension-based link filters will miss the latter. Accessible versions via TrustBoardQuestions@elht.nhs.uk. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; the /application/files/ pack paths above remain the fastest way in once past the wall.</t>
+          <t>URL is valid; the near-empty body is Imperva/Incapsula bot mitigation rather than JS-rendered content — an hCaptcha 'Additional security check is required' interstitial is served to traffic scored as automated. Once past the wall the page lists scheduled board meetings (Boardroom, Birch House, Royal Blackburn) with agenda/papers as combined PDFs; two delivery paths are in use — the /application/files/ path (filename pattern 'Trust_Board_Agenda_and_Papers_-_&lt;Month&gt;_&lt;Year&gt;.pdf') and the CMS download handler (/download_file/&lt;id&gt;/&lt;id&gt;, no .pdf suffix), so extension-based link filters will miss the latter. Accessible versions via TrustBoardQuestions@elht.nhs.uk. ACCESS ROUTE (checked 2026-07-31): the Imperva block is specific to the LOCAL fetch path — plain `requests` and local headless Playwright both get the 212-byte _Incapsula_Resource hCaptcha shell. Server-side WebFetch is NOT blocked and reaches this page normally, and pack PDFs on this domain download fine through it. So DO NOT read needs_playwright:true here as 'skip the cheap fetchers' — do the opposite: try WebFetch FIRST, and only escalate if it fails. Treat this record as 'local crawler blocked, server-side fetch works', not 'unreachable'. If you are running from a machine whose IP Imperva scores badly, a captcha-solving/residential session or an allowlisted IP is the fallback. Route check 2026-08-15: server-side WebFetch returned an empty body (the Incapsula shell) this run, so the WebFetch route is intermittent, NOT dead - it has previously reached this domain. Try WebFetch first and only escalate if it fails again. Landing URL unchanged (shallow check HTTP 200). Re-probe 2026-08-22: local requests and local headless Playwright both still get the Incapsula shell, and server-side WebFetch returned an empty body this run too, so the mitigation may have widened. Still try WebFetch first - it has reached this domain before; the /application/files/ pack paths above remain the fastest way in once past the wall. Route re-probe 2026-09-05: still blocked on every route tried - local requests and local headless Playwright get the Incapsula/hCaptcha shell and server-side WebFetch returned an empty body again. Two things confirm this is routing and not the trust withdrawing its papers: the shallow check still gets HTTP 200 on this exact URL with NO redirect, and WebFetch has previously pulled this domain's pages and packs fine. So keep the order - try WebFetch first, then a plain browser-UA static fetch, and only then escalate to a captcha-solving or residential session / allowlisted IP. Do not rewrite this record as 'unreachable'.</t>
         </is>
       </c>
       <c r="J191" t="b">
@@ -14481,17 +14481,17 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>papers_found</t>
+          <t>needs_playwright</t>
         </is>
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>Blocked on every route tried this run (2026-08-22): local requests, local headless Playwright and server-side WebFetch all returned the Incapsula challenge or an empty body. Status carried forward from the 2026-07-31 confirmation of the /application/files/ pack paths.</t>
+          <t>2026-09-05: URL still resolves HTTP 200 with no redirect, but every route tried from here was refused - local requests and local headless Playwright get the Incapsula shell and server-side WebFetch returned an empty body. Treated as a fetch-path block, not a dead archive.</t>
         </is>
       </c>
       <c r="P191" t="inlineStr"/>
@@ -15157,7 +15157,7 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>The DB URL is correct - the full board-paper archive lives inline on /about-scas/our-board/ (and on the byte-identical alias /about-scas/our-board/board-meetings/), not on a separate papers page; /about-scas/our-board/board-papers/ is a 404. The paper tables are Document Library Pro widgets running serverSide:true, so rows are fetched by AJAX and have NEVER existed in the HTML source - a static fetch legitimately sees empty tables plus a 'papers will be published shortly before each meeting' note. That note is long-standing boilerplate, NOT a sign the trust has stopped publishing (verified 2026-07-30 against Wayback snapshots from June 2025, February 2026 and June 2026, none of which carried PDF links either). You do NOT need a browser: scrape the table ids matching id="dlp_&lt;hash&gt;_&lt;n&gt;" from the page HTML, then POST to /wp-admin/admin-ajax.php with action=dlp_load_posts&amp;table_id=&lt;id&gt;&amp;draw=1&amp;start=0&amp;length=100 - no nonce, cookie or referer required - and regex href="([^"]+)" out of the returned DataTables JSON 'link' field. Current map: _1 = current financial year (empty between meetings, by design), _2 = the 25-document archive spanning January 2023 to 3 June 2026, _3 = constitution and committee terms of reference. Do NOT hardcode the table id hashes - they change whenever an editor edits the block. The WordPress REST media API is closed (401). No WAF. Bi-monthly public board; packs move from _1 into _2 after each meeting.</t>
+          <t>The DB URL is correct - the full board-paper archive lives inline on /about-scas/our-board/ (and on the byte-identical alias /about-scas/our-board/board-meetings/), not on a separate papers page; /about-scas/our-board/board-papers/ is a 404. The paper tables are Document Library Pro widgets running serverSide:true, so rows are fetched by AJAX and have NEVER existed in the HTML source - a static fetch legitimately sees empty tables plus a 'papers will be published shortly before each meeting' note. That note is long-standing boilerplate, NOT a sign the trust has stopped publishing (verified 2026-07-30 against Wayback snapshots from June 2025, February 2026 and June 2026, none of which carried PDF links either). You do NOT need a browser: scrape the table ids matching id="dlp_&lt;hash&gt;_&lt;n&gt;" from the page HTML, then POST to /wp-admin/admin-ajax.php with action=dlp_load_posts&amp;table_id=&lt;id&gt;&amp;draw=1&amp;start=0&amp;length=100 - no nonce, cookie or referer required - and regex href="([^"]+)" out of the returned DataTables JSON 'link' field. Current map: _1 = current financial year (empty between meetings, by design), _2 = the 25-document archive spanning January 2023 to 3 June 2026, _3 = constitution and committee terms of reference. Do NOT hardcode the table id hashes - they change whenever an editor edits the block. The WordPress REST media API is closed (401). No WAF. Bi-monthly public board; packs move from _1 into _2 after each meeting. Re-verified 2026-09-05: the admin-ajax recipe above still works exactly as described (POST action=dlp_load_posts, no nonce or cookie) and returned the archive to 'Board papers - 3 June 2026'. As predicted, the table id hashes HAD changed since the last run - this run they were dlp_2d9d010977ed5dba_1 (current year, empty between meetings), dlp_c5c27bbaddfd4cd9_2 (the archive) and dlp_ae972c33f72aee98_3 (constitution/ToR). Scrape the ids from the page each time; never hardcode them.</t>
         </is>
       </c>
       <c r="J200" t="b">
@@ -15175,7 +15175,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15185,7 +15185,7 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Playwright re-check 2026-08-22: the Document Library Pro AJAX tables render fully - latest 'SCAS public Board papers - 3 June 2026' (17MB), archive back to 2023; next meeting 3 Sept 2026. The static empty-table reading is the known false negative.</t>
+          <t>2026-09-05: the documented admin-ajax route still works - the archive table returned 25 documents spanning January 2023 to 3 June 2026, newest 'Board papers - 3 June 2026'. The empty static tables remain by design.</t>
         </is>
       </c>
       <c r="P200" t="inlineStr"/>
